--- a/output/economic_index_latest.xlsx
+++ b/output/economic_index_latest.xlsx
@@ -681,7 +681,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2644239701647932</v>
+        <v>0.2644192372247186</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -690,16 +690,16 @@
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2161973231179675</v>
+        <v>0.2161917599160857</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>60.80986615589838</v>
+        <v>60.80958799580428</v>
       </c>
       <c r="L2" t="n">
-        <v>9.336743196911643</v>
+        <v>9.337185433532984</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.0005</v>
+        <v>1.0004</v>
       </c>
       <c r="O2" t="n">
         <v>4614</v>
@@ -871,7 +871,7 @@
         <v>8.452121194672523</v>
       </c>
       <c r="R2" t="n">
-        <v>1.004576741885871</v>
+        <v>1.004531044179237</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="O3" t="n">
-        <v>17671</v>
+        <v>17701</v>
       </c>
       <c r="P3" t="n">
         <v>36</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.783802709590148</v>
+        <v>9.78549199429842</v>
       </c>
       <c r="R3" t="n">
-        <v>1.000755233060518</v>
+        <v>1.000890629266691</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>8.438799123988225</v>
       </c>
       <c r="R4" t="n">
-        <v>1.002993347368097</v>
+        <v>1.002947721689309</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>8.322394113111169</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9891580314902595</v>
+        <v>0.9891130351732506</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>8.557951183888406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.017155163717697</v>
+        <v>1.017108893824781</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>9.897720957641791</v>
       </c>
       <c r="R7" t="n">
-        <v>1.012407581974609</v>
+        <v>1.012369757532101</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9752</v>
       </c>
       <c r="O8" t="n">
         <v>4176</v>
@@ -1290,7 +1290,7 @@
         <v>8.358666283188001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.993469159738146</v>
+        <v>0.9934239673100131</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.9668</v>
+        <v>0.9667</v>
       </c>
       <c r="O9" t="n">
         <v>17034</v>
@@ -1360,7 +1360,7 @@
         <v>9.745839095947058</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9968720512193749</v>
+        <v>0.9968348071980339</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.9489</v>
+        <v>0.9488</v>
       </c>
       <c r="O10" t="n">
-        <v>250598</v>
+        <v>250602</v>
       </c>
       <c r="P10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.43370610211724</v>
+        <v>12.43372999431564</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9985705529056425</v>
+        <v>0.9985177868858373</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1489,16 +1489,16 @@
         <v>0.9271</v>
       </c>
       <c r="O11" t="n">
-        <v>4804</v>
+        <v>4805</v>
       </c>
       <c r="P11" t="n">
         <v>50</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.498010371999463</v>
+        <v>8.498214224818435</v>
       </c>
       <c r="R11" t="n">
-        <v>1.010030899390851</v>
+        <v>1.010009181398926</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.9212</v>
+        <v>0.9211</v>
       </c>
       <c r="O12" t="n">
         <v>4609</v>
@@ -1568,7 +1568,7 @@
         <v>8.443331342817782</v>
       </c>
       <c r="R12" t="n">
-        <v>1.003532024171286</v>
+        <v>1.003486373988352</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.9141</v>
+        <v>0.914</v>
       </c>
       <c r="O13" t="n">
         <v>4319</v>
@@ -1638,7 +1638,7 @@
         <v>8.378390788535778</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9958135155348981</v>
+        <v>0.9957682164631619</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.907</v>
+        <v>0.9069</v>
       </c>
       <c r="O14" t="n">
         <v>4033</v>
@@ -1706,7 +1706,7 @@
         <v>8.3133619511344</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9880845140096385</v>
+        <v>0.9880395665264168</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.8818</v>
+        <v>0.8817</v>
       </c>
       <c r="O15" t="n">
         <v>417</v>
@@ -1776,7 +1776,7 @@
         <v>6.063785208687608</v>
       </c>
       <c r="R15" t="n">
-        <v>1.01980365663123</v>
+        <v>1.019754981461143</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1790,20 +1790,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>@spotuz</t>
+          <t>@kunuzofficial</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39787</v>
+        <v>173783</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-02 13:01:01</t>
+          <t>2026-09-02 16:00:12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>trade</t>
+          <t>construction_realty</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1824,29 +1824,98 @@
         <v>0.8646647167633873</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>pos</t>
+          <t>neu</t>
         </is>
       </c>
       <c r="N16" t="n">
         <v>0.8651</v>
       </c>
       <c r="O16" t="n">
+        <v>257330</v>
+      </c>
+      <c r="P16" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12.45911280610038</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.000556208908821</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>**«Тўқимачи» стадиони нега бузилмоқда? Масъуллар изоҳ берди**
+Тошкент марказидаги тарихий «Тўқимачи» стадиони бузилаётгани жамоатчиликда саволлар уйғотди. Kun.uz стадионнинг мулкдори ҳамда ваколатли давлат идоралари билан боғланиб, вазиятга ойдинлик киритди.
+Қурилиш ва уй-жой коммунал хўжалиги соҳасида назорат қилиш инспекциясининг Kun.uz’га маълум қилишича, мазкур ҳудудда қурилиш-монтаж ишларини амалга ошириш учун рухсат берилган ва бу ерда автотураргоҳ, маиший хизмат кўрсатиш объекти қурилади.
+👉 https://kun.uz/kr/54488282
+[Kun.uz расмий канали](https://t.me/kunuzofficial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>@spotuz</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>39787</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:01:01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0.8646647167633873</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="O17" t="n">
         <v>4497</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P17" t="n">
         <v>15</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q17" t="n">
         <v>8.418035619883019</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.000525501389115</v>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="R17" t="n">
+        <v>1.000479987971438</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>**Часть льгот по таможенным пошлинам будет отменена с 2029 года — указ**
 Президент поручил разработать законопроект об упорядочении таможенных льгот. Бессрочно действующие льготы будут ограничены 1 января 2029 года, при этом преференции с указанием срока действия сохраняться до его конца.
@@ -1857,75 +1926,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>@kunuzofficial</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>173783</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-09-02 16:00:12</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>construction_realty</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0.8646647167633873</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>neu</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>0.8649</v>
-      </c>
-      <c r="O17" t="n">
-        <v>256328</v>
-      </c>
-      <c r="P17" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>12.455215272713</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.000297988329799</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>**«Тўқимачи» стадиони нега бузилмоқда? Масъуллар изоҳ берди**
-Тошкент марказидаги тарихий «Тўқимачи» стадиони бузилаётгани жамоатчиликда саволлар уйғотди. Kun.uz стадионнинг мулкдори ҳамда ваколатли давлат идоралари билан боғланиб, вазиятга ойдинлик киритди.
-Қурилиш ва уй-жой коммунал хўжалиги соҳасида назорат қилиш инспекциясининг Kun.uz’га маълум қилишича, мазкур ҳудудда қурилиш-монтаж ишларини амалга ошириш учун рухсат берилган ва бу ерда автотураргоҳ, маиший хизмат кўрсатиш объекти қурилади.
-👉 https://kun.uz/kr/54488282
-[Kun.uz расмий канали](https://t.me/kunuzofficial)</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>9.759039648170255</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9982222953022512</v>
+        <v>0.9981850008345972</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>11.27269933367474</v>
       </c>
       <c r="R19" t="n">
-        <v>0.997542266837503</v>
+        <v>0.997493828094088</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>0.8612</v>
       </c>
       <c r="O20" t="n">
-        <v>16805</v>
+        <v>16806</v>
       </c>
       <c r="P20" t="n">
         <v>66</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.737314897481545</v>
+        <v>9.737373934586381</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9960001370490649</v>
+        <v>0.99596896410235</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2178,19 +2178,19 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.8603</v>
+        <v>0.8605</v>
       </c>
       <c r="O21" t="n">
-        <v>16663</v>
+        <v>16693</v>
       </c>
       <c r="P21" t="n">
         <v>53</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.727346854817254</v>
+        <v>9.729134165391351</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9949805364749567</v>
+        <v>0.9951261748200705</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.8595</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>4126</v>
@@ -2260,7 +2260,7 @@
         <v>8.36287583103188</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9939694854860166</v>
+        <v>0.9939242702983092</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2327,19 +2327,19 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.8554</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>15673</v>
+        <v>15674</v>
       </c>
       <c r="P23" t="n">
         <v>91</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.67130325656977</v>
+        <v>9.671366322189568</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9892480083475512</v>
+        <v>0.9892174997154054</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>5.834810737062605</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9812948712105604</v>
+        <v>0.9812480340625941</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.8455</v>
+        <v>0.8454</v>
       </c>
       <c r="O25" t="n">
         <v>326</v>
@@ -2485,7 +2485,7 @@
         <v>5.814130531825066</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9778168870479764</v>
+        <v>0.9777702159039949</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.7935</v>
+        <v>0.7934</v>
       </c>
       <c r="O26" t="n">
         <v>413</v>
@@ -2553,7 +2553,7 @@
         <v>6.073044534100405</v>
       </c>
       <c r="R26" t="n">
-        <v>1.021360884268578</v>
+        <v>1.021312134772104</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2612,16 +2612,16 @@
         <v>0.7801</v>
       </c>
       <c r="O27" t="n">
-        <v>84567</v>
+        <v>84568</v>
       </c>
       <c r="P27" t="n">
         <v>90</v>
       </c>
       <c r="Q27" t="n">
-        <v>11.34743742614418</v>
+        <v>11.34744922576305</v>
       </c>
       <c r="R27" t="n">
-        <v>1.004155980551871</v>
+        <v>1.004108264778836</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2680,16 +2680,16 @@
         <v>0.7793</v>
       </c>
       <c r="O28" t="n">
-        <v>265451</v>
+        <v>265452</v>
       </c>
       <c r="P28" t="n">
         <v>217</v>
       </c>
       <c r="Q28" t="n">
-        <v>12.49082292447228</v>
+        <v>12.49082668547557</v>
       </c>
       <c r="R28" t="n">
-        <v>1.00315769501845</v>
+        <v>1.003103061113409</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>9.803722464346553</v>
       </c>
       <c r="R29" t="n">
-        <v>1.002792763804491</v>
+        <v>1.002755298580092</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -2817,16 +2817,16 @@
         <v>0.7771</v>
       </c>
       <c r="O30" t="n">
-        <v>81067</v>
+        <v>81068</v>
       </c>
       <c r="P30" t="n">
         <v>24</v>
       </c>
       <c r="Q30" t="n">
-        <v>11.30363550794455</v>
+        <v>11.30364783589263</v>
       </c>
       <c r="R30" t="n">
-        <v>1.000279866812001</v>
+        <v>1.0002323860062</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.7764</v>
+        <v>0.7765</v>
       </c>
       <c r="O31" t="n">
-        <v>17448</v>
+        <v>17478</v>
       </c>
       <c r="P31" t="n">
         <v>31</v>
       </c>
       <c r="Q31" t="n">
-        <v>9.770584533871901</v>
+        <v>9.772296276843781</v>
       </c>
       <c r="R31" t="n">
-        <v>0.9994031863242749</v>
+        <v>0.9995409301453289</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -2954,16 +2954,16 @@
         <v>0.7754</v>
       </c>
       <c r="O32" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="P32" t="n">
         <v>14</v>
       </c>
       <c r="Q32" t="n">
-        <v>11.27903689211984</v>
+        <v>11.27904952707697</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9981030892483919</v>
+        <v>0.9980557413092315</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.7744</v>
+        <v>0.7743</v>
       </c>
       <c r="O33" t="n">
         <v>366</v>
@@ -3031,7 +3031,7 @@
         <v>5.926926025970411</v>
       </c>
       <c r="R33" t="n">
-        <v>0.9967867636880899</v>
+        <v>0.9967391871129835</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3090,16 +3090,16 @@
         <v>0.7739</v>
       </c>
       <c r="O34" t="n">
-        <v>243544</v>
+        <v>243545</v>
       </c>
       <c r="P34" t="n">
         <v>127</v>
       </c>
       <c r="Q34" t="n">
-        <v>12.40409939429817</v>
+        <v>12.40410349602931</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9961927914921277</v>
+        <v>0.9961385663691004</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>8.310414994188292</v>
       </c>
       <c r="R35" t="n">
-        <v>0.9877342534845924</v>
+        <v>0.9876893219345514</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>8.299285906897275</v>
       </c>
       <c r="R36" t="n">
-        <v>0.9864115059761893</v>
+        <v>0.9863666345972881</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.7557</v>
+        <v>0.7556</v>
       </c>
       <c r="O37" t="n">
         <v>318</v>
@@ -3307,7 +3307,7 @@
         <v>5.783825182329737</v>
       </c>
       <c r="R37" t="n">
-        <v>0.9727201520603082</v>
+        <v>0.9726737241831955</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3363,19 +3363,19 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.6424</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P38" t="n">
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.042632833682381</v>
+        <v>6.045005314036012</v>
       </c>
       <c r="R38" t="n">
-        <v>1.016246263248321</v>
+        <v>1.016596741110735</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3434,16 +3434,16 @@
         <v>0.6334</v>
       </c>
       <c r="O39" t="n">
-        <v>82597</v>
+        <v>82598</v>
       </c>
       <c r="P39" t="n">
         <v>93</v>
       </c>
       <c r="Q39" t="n">
-        <v>11.32399008498576</v>
+        <v>11.32400216454171</v>
       </c>
       <c r="R39" t="n">
-        <v>1.0020810814387</v>
+        <v>1.002033491189748</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.6332</v>
+        <v>0.6333</v>
       </c>
       <c r="O40" t="n">
-        <v>17848</v>
+        <v>17878</v>
       </c>
       <c r="P40" t="n">
         <v>27</v>
       </c>
       <c r="Q40" t="n">
-        <v>9.792723575551273</v>
+        <v>9.794397869948424</v>
       </c>
       <c r="R40" t="n">
-        <v>1.001667721134841</v>
+        <v>1.001801549993896</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -3571,16 +3571,16 @@
         <v>0.6321</v>
       </c>
       <c r="O41" t="n">
-        <v>255668</v>
+        <v>255669</v>
       </c>
       <c r="P41" t="n">
         <v>48</v>
       </c>
       <c r="Q41" t="n">
-        <v>12.45201433312036</v>
+        <v>12.45201824295183</v>
       </c>
       <c r="R41" t="n">
-        <v>1.000040915821202</v>
+        <v>0.9999864645523602</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0.6321</v>
+        <v>0.632</v>
       </c>
       <c r="O42" t="n">
         <v>363</v>
@@ -3655,7 +3655,7 @@
         <v>5.945420608606575</v>
       </c>
       <c r="R42" t="n">
-        <v>0.9998971711895309</v>
+        <v>0.9998494461548528</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -3711,19 +3711,19 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0.6317</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>253225</v>
+        <v>253226</v>
       </c>
       <c r="P43" t="n">
         <v>71</v>
       </c>
       <c r="Q43" t="n">
-        <v>12.44259825633764</v>
+        <v>12.44260220315818</v>
       </c>
       <c r="R43" t="n">
-        <v>0.9992846958396531</v>
+        <v>0.9992302889541865</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -3781,19 +3781,19 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6315</v>
       </c>
       <c r="O44" t="n">
-        <v>252188</v>
+        <v>252190</v>
       </c>
       <c r="P44" t="n">
         <v>314</v>
       </c>
       <c r="Q44" t="n">
-        <v>12.44042118582932</v>
+        <v>12.44042909665845</v>
       </c>
       <c r="R44" t="n">
-        <v>0.9991098518725078</v>
+        <v>0.999055772900374</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -3854,16 +3854,16 @@
         <v>0.6314</v>
       </c>
       <c r="O45" t="n">
-        <v>79741</v>
+        <v>79742</v>
       </c>
       <c r="P45" t="n">
         <v>36</v>
       </c>
       <c r="Q45" t="n">
-        <v>11.28745420664684</v>
+        <v>11.28746673569858</v>
       </c>
       <c r="R45" t="n">
-        <v>0.9988479531683286</v>
+        <v>0.9988005596886901</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>9.734180932819669</v>
       </c>
       <c r="R46" t="n">
-        <v>0.9956795733961894</v>
+        <v>0.9956423739268743</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>5.905361848054571</v>
       </c>
       <c r="R47" t="n">
-        <v>0.9931601135456487</v>
+        <v>0.9931127100703457</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>5.902633333401366</v>
       </c>
       <c r="R48" t="n">
-        <v>0.9927012336340509</v>
+        <v>0.9926538520610599</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>5.902633333401366</v>
       </c>
       <c r="R49" t="n">
-        <v>0.9927012336340509</v>
+        <v>0.9926538520610599</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>0.6267</v>
       </c>
       <c r="O50" t="n">
-        <v>229564</v>
+        <v>229565</v>
       </c>
       <c r="P50" t="n">
         <v>175</v>
       </c>
       <c r="Q50" t="n">
-        <v>12.34546495438189</v>
+        <v>12.34546930380591</v>
       </c>
       <c r="R50" t="n">
-        <v>0.9914837671187312</v>
+        <v>0.9914298197675971</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0.6194</v>
+        <v>0.6193</v>
       </c>
       <c r="O51" t="n">
         <v>330</v>
@@ -4274,7 +4274,7 @@
         <v>5.82600010738045</v>
       </c>
       <c r="R51" t="n">
-        <v>0.9798131049444644</v>
+        <v>0.9797663385211171</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>5.820082930352362</v>
       </c>
       <c r="R52" t="n">
-        <v>0.9788179577612275</v>
+        <v>0.9787712388361982</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>6.049733455231958</v>
       </c>
       <c r="R53" t="n">
-        <v>1.017440441401307</v>
+        <v>1.017391879027347</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -4469,16 +4469,16 @@
         <v>0.6326000000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>81566</v>
+        <v>81567</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>11.30922908562858</v>
+        <v>11.30924134481224</v>
       </c>
       <c r="R54" t="n">
-        <v>1.00077485297259</v>
+        <v>1.000727342046413</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.6324</v>
+        <v>0.6323</v>
       </c>
       <c r="O55" t="n">
         <v>4500</v>
@@ -4546,7 +4546,7 @@
         <v>8.416930769477844</v>
       </c>
       <c r="R55" t="n">
-        <v>1.000394184410248</v>
+        <v>1.000348676966116</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -4601,19 +4601,19 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.6291</v>
+        <v>0.6292</v>
       </c>
       <c r="O56" t="n">
-        <v>16802</v>
+        <v>16832</v>
       </c>
       <c r="P56" t="n">
         <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>9.73014555852275</v>
+        <v>9.731927878386204</v>
       </c>
       <c r="R56" t="n">
-        <v>0.9952668073107653</v>
+        <v>0.9954119244951035</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>81850</v>
+        <v>81851</v>
       </c>
       <c r="P57" t="n">
         <v>32</v>
       </c>
       <c r="Q57" t="n">
-        <v>11.31343740325436</v>
+        <v>11.3134496109562</v>
       </c>
       <c r="R57" t="n">
-        <v>1.001147254877381</v>
+        <v>1.001099721312579</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>83556</v>
+        <v>83857</v>
       </c>
       <c r="P58" t="n">
         <v>19</v>
       </c>
       <c r="Q58" t="n">
-        <v>11.33373898867175</v>
+        <v>11.33733321551424</v>
       </c>
       <c r="R58" t="n">
-        <v>1.002943780176087</v>
+        <v>1.003213123562926</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -4807,16 +4807,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>80449</v>
+        <v>80450</v>
       </c>
       <c r="P59" t="n">
         <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>11.2954408715077</v>
+        <v>11.29545330089325</v>
       </c>
       <c r="R59" t="n">
-        <v>0.9995547080931203</v>
+        <v>0.999507271475596</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -4875,16 +4875,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>83364</v>
+        <v>83365</v>
       </c>
       <c r="P60" t="n">
         <v>55</v>
       </c>
       <c r="Q60" t="n">
-        <v>11.33230246481186</v>
+        <v>11.33231444437472</v>
       </c>
       <c r="R60" t="n">
-        <v>1.002816659490513</v>
+        <v>1.002769024675153</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -4943,16 +4943,16 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>80660</v>
+        <v>80661</v>
       </c>
       <c r="P61" t="n">
         <v>15</v>
       </c>
       <c r="Q61" t="n">
-        <v>11.29838232387519</v>
+        <v>11.29839471675424</v>
       </c>
       <c r="R61" t="n">
-        <v>0.9998150027195988</v>
+        <v>0.9997675502322938</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -5011,16 +5011,16 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="P62" t="n">
         <v>12</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.29312631490641</v>
+        <v>11.29313877309362</v>
       </c>
       <c r="R62" t="n">
-        <v>0.999349888646559</v>
+        <v>0.999302464523264</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -5079,16 +5079,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>80659</v>
+        <v>80960</v>
       </c>
       <c r="P63" t="n">
         <v>55</v>
       </c>
       <c r="Q63" t="n">
-        <v>11.29936088843634</v>
+        <v>11.3030805929248</v>
       </c>
       <c r="R63" t="n">
-        <v>0.9999015977295146</v>
+        <v>1.000182192051523</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -5147,16 +5147,16 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>80433</v>
+        <v>80734</v>
       </c>
       <c r="P64" t="n">
         <v>22</v>
       </c>
       <c r="Q64" t="n">
-        <v>11.29573913413014</v>
+        <v>11.29947230973897</v>
       </c>
       <c r="R64" t="n">
-        <v>0.9995811019109364</v>
+        <v>0.9998629038223834</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -5215,16 +5215,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>81113</v>
+        <v>81114</v>
       </c>
       <c r="P65" t="n">
         <v>11</v>
       </c>
       <c r="Q65" t="n">
-        <v>11.3038820380348</v>
+        <v>11.30389436294406</v>
       </c>
       <c r="R65" t="n">
-        <v>1.000301682721198</v>
+        <v>1.000254200587161</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -5283,16 +5283,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>81485</v>
+        <v>81486</v>
       </c>
       <c r="P66" t="n">
         <v>21</v>
       </c>
       <c r="Q66" t="n">
-        <v>11.30870179850853</v>
+        <v>11.30871406415796</v>
       </c>
       <c r="R66" t="n">
-        <v>1.000728192348241</v>
+        <v>1.000680684259955</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -5351,16 +5351,16 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>81221</v>
+        <v>81222</v>
       </c>
       <c r="P67" t="n">
         <v>43</v>
       </c>
       <c r="Q67" t="n">
-        <v>11.30599969167885</v>
+        <v>11.306011990516</v>
       </c>
       <c r="R67" t="n">
-        <v>1.000489077856465</v>
+        <v>1.000441584315821</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -5419,16 +5419,16 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>81352</v>
+        <v>81353</v>
       </c>
       <c r="P68" t="n">
         <v>11</v>
       </c>
       <c r="Q68" t="n">
-        <v>11.30682337951087</v>
+        <v>11.30683566822185</v>
       </c>
       <c r="R68" t="n">
-        <v>1.000561967534687</v>
+        <v>1.000514469558619</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -5487,16 +5487,16 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>79925</v>
+        <v>79926</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>11.28888150841285</v>
+        <v>11.28889401959472</v>
       </c>
       <c r="R69" t="n">
-        <v>0.9989742577735511</v>
+        <v>0.9989268565795411</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -5555,16 +5555,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>79534</v>
+        <v>79535</v>
       </c>
       <c r="P70" t="n">
         <v>30</v>
       </c>
       <c r="Q70" t="n">
-        <v>11.28470655578924</v>
+        <v>11.28471911931356</v>
       </c>
       <c r="R70" t="n">
-        <v>0.9986048084002619</v>
+        <v>0.998557429777663</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -5623,16 +5623,16 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="P71" t="n">
         <v>27</v>
       </c>
       <c r="Q71" t="n">
-        <v>11.28986940982812</v>
+        <v>11.28988190865635</v>
       </c>
       <c r="R71" t="n">
-        <v>0.9990616790191661</v>
+        <v>0.9990142724870045</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -5691,16 +5691,16 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>81935</v>
+        <v>81936</v>
       </c>
       <c r="P72" t="n">
         <v>33</v>
       </c>
       <c r="Q72" t="n">
-        <v>11.31449891619286</v>
+        <v>11.31451111094302</v>
       </c>
       <c r="R72" t="n">
-        <v>1.001241190144489</v>
+        <v>1.001193650872307</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -5759,16 +5759,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>80628</v>
+        <v>80629</v>
       </c>
       <c r="P73" t="n">
         <v>60</v>
       </c>
       <c r="Q73" t="n">
-        <v>11.29910085710729</v>
+        <v>11.2991132410849</v>
       </c>
       <c r="R73" t="n">
-        <v>0.9998785870704214</v>
+        <v>0.9998311307079151</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>11.26009560328566</v>
       </c>
       <c r="R74" t="n">
-        <v>0.9964269391408458</v>
+        <v>0.9963785545556093</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -5895,16 +5895,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>78497</v>
+        <v>78498</v>
       </c>
       <c r="P75" t="n">
         <v>35</v>
       </c>
       <c r="Q75" t="n">
-        <v>11.27171977083761</v>
+        <v>11.27173249858474</v>
       </c>
       <c r="R75" t="n">
-        <v>0.9974555834882768</v>
+        <v>0.9974082752015182</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -5963,16 +5963,16 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>80774</v>
+        <v>80775</v>
       </c>
       <c r="P76" t="n">
         <v>28</v>
       </c>
       <c r="Q76" t="n">
-        <v>11.30011583429555</v>
+        <v>11.30012820571016</v>
       </c>
       <c r="R76" t="n">
-        <v>0.9999684043018755</v>
+        <v>0.9999209424663469</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -6031,16 +6031,16 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>81915</v>
+        <v>82216</v>
       </c>
       <c r="P77" t="n">
         <v>13</v>
       </c>
       <c r="Q77" t="n">
-        <v>11.31376695890648</v>
+        <v>11.31743355862289</v>
       </c>
       <c r="R77" t="n">
-        <v>1.001176417873974</v>
+        <v>1.001452251180655</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6099,16 +6099,16 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>81510</v>
+        <v>81810</v>
       </c>
       <c r="P78" t="n">
         <v>14</v>
       </c>
       <c r="Q78" t="n">
-        <v>11.30883671237849</v>
+        <v>11.31250918158702</v>
       </c>
       <c r="R78" t="n">
-        <v>1.000740131129157</v>
+        <v>1.001016504998212</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>11.29151790594907</v>
       </c>
       <c r="R79" t="n">
-        <v>0.9992075575269387</v>
+        <v>0.9991590379201948</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>11.29603730781853</v>
       </c>
       <c r="R80" t="n">
-        <v>0.9996074878588106</v>
+        <v>0.9995589488322152</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>11.28838093274039</v>
       </c>
       <c r="R81" t="n">
-        <v>0.9989299608952034</v>
+        <v>0.9988814547680206</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>11.28269435615412</v>
       </c>
       <c r="R82" t="n">
-        <v>0.9984267450876582</v>
+        <v>0.998378263395672</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>11.31543747709451</v>
       </c>
       <c r="R83" t="n">
-        <v>1.001324245155689</v>
+        <v>1.001275622766644</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>9.906881785604144</v>
       </c>
       <c r="R84" t="n">
-        <v>1.013344615027565</v>
+        <v>1.013306755576674</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>9.940638818166921</v>
       </c>
       <c r="R85" t="n">
-        <v>1.016797518565438</v>
+        <v>1.016759530111017</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>9.838095333769076</v>
       </c>
       <c r="R86" t="n">
-        <v>1.006308659409804</v>
+        <v>1.006271062828436</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>9.777470711952642</v>
       </c>
       <c r="R87" t="n">
-        <v>1.000107552403053</v>
+        <v>1.000070187500526</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -6784,16 +6784,16 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>17101</v>
+        <v>17102</v>
       </c>
       <c r="P88" t="n">
         <v>24</v>
       </c>
       <c r="Q88" t="n">
-        <v>9.749753452594087</v>
+        <v>9.749811759932081</v>
       </c>
       <c r="R88" t="n">
-        <v>0.9972724387798005</v>
+        <v>0.9972411436559402</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -6852,16 +6852,16 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>16513</v>
+        <v>16514</v>
       </c>
       <c r="P89" t="n">
         <v>37</v>
       </c>
       <c r="Q89" t="n">
-        <v>9.716434821366272</v>
+        <v>9.716495104092274</v>
       </c>
       <c r="R89" t="n">
-        <v>0.9938643779726294</v>
+        <v>0.9938334122257786</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>9.742496866444002</v>
       </c>
       <c r="R90" t="n">
-        <v>0.9965301847933487</v>
+        <v>0.9964929535444396</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>9.740497924041666</v>
       </c>
       <c r="R91" t="n">
-        <v>0.996325719093344</v>
+        <v>0.9962884954834542</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>9.749986661550366</v>
       </c>
       <c r="R92" t="n">
-        <v>0.9972962930101362</v>
+        <v>0.9972590331387468</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>9.756146964637418</v>
       </c>
       <c r="R93" t="n">
-        <v>0.9979264115575558</v>
+        <v>0.9978891281443801</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>9.762499859235151</v>
       </c>
       <c r="R94" t="n">
-        <v>0.9985762297011218</v>
+        <v>0.9985389220101657</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>9.751617603198001</v>
       </c>
       <c r="R95" t="n">
-        <v>0.9974631170393132</v>
+        <v>0.9974258509352305</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>9.801676286389442</v>
       </c>
       <c r="R96" t="n">
-        <v>1.002583466524166</v>
+        <v>1.002546009119299</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>9.739438040529622</v>
       </c>
       <c r="R97" t="n">
-        <v>0.9962173068529712</v>
+        <v>0.9961800872934585</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>9.734240155229445</v>
       </c>
       <c r="R98" t="n">
-        <v>0.9956856310752185</v>
+        <v>0.995648431379583</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -7537,16 +7537,16 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>17335</v>
+        <v>17365</v>
       </c>
       <c r="P99" t="n">
         <v>111</v>
       </c>
       <c r="Q99" t="n">
-        <v>9.773264965486154</v>
+        <v>9.7749721303007</v>
       </c>
       <c r="R99" t="n">
-        <v>0.9996773594698757</v>
+        <v>0.999814624779373</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>9.881293067026359</v>
       </c>
       <c r="R100" t="n">
-        <v>1.010727223325775</v>
+        <v>1.010689461662952</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>289570</v>
+        <v>290572</v>
       </c>
       <c r="P101" t="n">
         <v>70</v>
       </c>
       <c r="Q101" t="n">
-        <v>12.57663915335071</v>
+        <v>12.58009180518932</v>
       </c>
       <c r="R101" t="n">
-        <v>1.010049731746326</v>
+        <v>1.010271691108062</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -7743,16 +7743,16 @@
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>274477</v>
+        <v>274479</v>
       </c>
       <c r="P102" t="n">
         <v>1224</v>
       </c>
       <c r="Q102" t="n">
-        <v>12.53150560146465</v>
+        <v>12.53151282358456</v>
       </c>
       <c r="R102" t="n">
-        <v>1.006424984990104</v>
+        <v>1.006370450110925</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -7811,16 +7811,16 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>265240</v>
+        <v>265241</v>
       </c>
       <c r="P103" t="n">
         <v>370</v>
       </c>
       <c r="Q103" t="n">
-        <v>12.49118015664127</v>
+        <v>12.49118391630124</v>
       </c>
       <c r="R103" t="n">
-        <v>1.003186384897523</v>
+        <v>1.00313174931346</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -7880,16 +7880,16 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>269689</v>
+        <v>269690</v>
       </c>
       <c r="P104" t="n">
         <v>190</v>
       </c>
       <c r="Q104" t="n">
-        <v>12.5064364636379</v>
+        <v>12.50644016637477</v>
       </c>
       <c r="R104" t="n">
-        <v>1.004411642981299</v>
+        <v>1.004356935727076</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -7949,16 +7949,16 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>251575</v>
+        <v>251577</v>
       </c>
       <c r="P105" t="n">
         <v>187</v>
       </c>
       <c r="Q105" t="n">
-        <v>12.43698593410874</v>
+        <v>12.43699387216019</v>
       </c>
       <c r="R105" t="n">
-        <v>0.9988339613872568</v>
+        <v>0.998779899709865</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>259816</v>
+        <v>259817</v>
       </c>
       <c r="P106" t="n">
         <v>36</v>
       </c>
       <c r="Q106" t="n">
-        <v>12.46800989576314</v>
+        <v>12.4680137435523</v>
       </c>
       <c r="R106" t="n">
-        <v>1.001325544692196</v>
+        <v>1.00127101809076</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -8086,16 +8086,16 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>262016</v>
+        <v>262017</v>
       </c>
       <c r="P107" t="n">
         <v>83</v>
       </c>
       <c r="Q107" t="n">
-        <v>12.47679801220674</v>
+        <v>12.47680182632929</v>
       </c>
       <c r="R107" t="n">
-        <v>1.002031332188218</v>
+        <v>1.001976764232061</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -8155,16 +8155,16 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>250996</v>
+        <v>250997</v>
       </c>
       <c r="P108" t="n">
         <v>162</v>
       </c>
       <c r="Q108" t="n">
-        <v>12.4344862854999</v>
+        <v>12.43449026446707</v>
       </c>
       <c r="R108" t="n">
-        <v>0.9986332106639482</v>
+        <v>0.9985788420373803</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -8223,16 +8223,16 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>249491</v>
+        <v>249492</v>
       </c>
       <c r="P109" t="n">
         <v>102</v>
       </c>
       <c r="Q109" t="n">
-        <v>12.42799945691649</v>
+        <v>12.42800346177839</v>
       </c>
       <c r="R109" t="n">
-        <v>0.9981122432265697</v>
+        <v>0.9980579052092819</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -8296,16 +8296,16 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>253587</v>
+        <v>254588</v>
       </c>
       <c r="P110" t="n">
         <v>758</v>
       </c>
       <c r="Q110" t="n">
-        <v>12.44942658413241</v>
+        <v>12.45334279562062</v>
       </c>
       <c r="R110" t="n">
-        <v>0.9998330896174572</v>
+        <v>1.00009283564133</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>236845</v>
+        <v>236846</v>
       </c>
       <c r="P111" t="n">
         <v>34</v>
       </c>
       <c r="Q111" t="n">
-        <v>12.375452485066</v>
+        <v>12.37545670599802</v>
       </c>
       <c r="R111" t="n">
-        <v>0.9938921130173373</v>
+        <v>0.9938380234590886</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -8440,16 +8440,16 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>260801</v>
+        <v>261803</v>
       </c>
       <c r="P112" t="n">
         <v>1391</v>
       </c>
       <c r="Q112" t="n">
-        <v>12.48212738174098</v>
+        <v>12.4859216192103</v>
       </c>
       <c r="R112" t="n">
-        <v>1.00245934226331</v>
+        <v>1.002709149076235</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -8508,16 +8508,16 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>248585</v>
+        <v>248586</v>
       </c>
       <c r="P113" t="n">
         <v>239</v>
       </c>
       <c r="Q113" t="n">
-        <v>12.42546517053323</v>
+        <v>12.42546918555745</v>
       </c>
       <c r="R113" t="n">
-        <v>0.9979087106889521</v>
+        <v>0.9978543846338273</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -8576,16 +8576,16 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>243605</v>
+        <v>243606</v>
       </c>
       <c r="P114" t="n">
         <v>156</v>
       </c>
       <c r="Q114" t="n">
-        <v>12.40458738221888</v>
+        <v>12.40459148194891</v>
       </c>
       <c r="R114" t="n">
-        <v>0.9962319825719061</v>
+        <v>0.9961777551419543</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -8644,16 +8644,16 @@
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>246545</v>
+        <v>246546</v>
       </c>
       <c r="P115" t="n">
         <v>548</v>
       </c>
       <c r="Q115" t="n">
-        <v>12.41973943384026</v>
+        <v>12.41974347191934</v>
       </c>
       <c r="R115" t="n">
-        <v>0.9974488677420196</v>
+        <v>0.9973945687207525</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -8714,16 +8714,16 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>247083</v>
+        <v>247084</v>
       </c>
       <c r="P116" t="n">
         <v>121</v>
       </c>
       <c r="Q116" t="n">
-        <v>12.41846258344616</v>
+        <v>12.41846662668455</v>
       </c>
       <c r="R116" t="n">
-        <v>0.9973463218724665</v>
+        <v>0.9972920288812496</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -8783,16 +8783,16 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>255005</v>
+        <v>255006</v>
       </c>
       <c r="P117" t="n">
         <v>111</v>
       </c>
       <c r="Q117" t="n">
-        <v>12.44991254230255</v>
+        <v>12.44991646036028</v>
       </c>
       <c r="R117" t="n">
-        <v>0.999872117684765</v>
+        <v>0.9998176763204473</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -8852,16 +8852,16 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>254932</v>
+        <v>254933</v>
       </c>
       <c r="P118" t="n">
         <v>440</v>
       </c>
       <c r="Q118" t="n">
-        <v>12.45220198778941</v>
+        <v>12.45220589688725</v>
       </c>
       <c r="R118" t="n">
-        <v>1.000055986663723</v>
+        <v>1.000001534510641</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -8920,16 +8920,16 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>255356</v>
+        <v>256357</v>
       </c>
       <c r="P119" t="n">
         <v>44</v>
       </c>
       <c r="Q119" t="n">
-        <v>12.45076240126537</v>
+        <v>12.4546733951134</v>
       </c>
       <c r="R119" t="n">
-        <v>0.9999403711988362</v>
+        <v>1.00019969233368</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -8988,16 +8988,16 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>267877</v>
+        <v>267878</v>
       </c>
       <c r="P120" t="n">
         <v>178</v>
       </c>
       <c r="Q120" t="n">
-        <v>12.49961501286131</v>
+        <v>12.49961874094252</v>
       </c>
       <c r="R120" t="n">
-        <v>1.003863801507675</v>
+        <v>1.003809126290235</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>8.555066843844319</v>
       </c>
       <c r="R121" t="n">
-        <v>1.016812345523632</v>
+        <v>1.016766091225349</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -9126,16 +9126,16 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>4837</v>
+        <v>4838</v>
       </c>
       <c r="P122" t="n">
         <v>80</v>
       </c>
       <c r="Q122" t="n">
-        <v>8.516793111394898</v>
+        <v>8.516993171413571</v>
       </c>
       <c r="R122" t="n">
-        <v>1.01226332160901</v>
+        <v>1.012241051292567</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -9196,16 +9196,16 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>4469</v>
+        <v>4500</v>
       </c>
       <c r="P123" t="n">
         <v>14</v>
       </c>
       <c r="Q123" t="n">
-        <v>8.411388132519262</v>
+        <v>8.418256443556213</v>
       </c>
       <c r="R123" t="n">
-        <v>0.9997354143750032</v>
+        <v>1.000506232771992</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>8.340217320947035</v>
       </c>
       <c r="R124" t="n">
-        <v>0.9912764085988359</v>
+        <v>0.9912313159178843</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>8.464635940677562</v>
       </c>
       <c r="R125" t="n">
-        <v>1.006064181840612</v>
+        <v>1.006018416471059</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>6.107022887742255</v>
       </c>
       <c r="R126" t="n">
-        <v>1.027075342828327</v>
+        <v>1.027026320581074</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>6.030685260261263</v>
       </c>
       <c r="R127" t="n">
-        <v>1.014236927718879</v>
+        <v>1.014188518248443</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>5.924255797414532</v>
       </c>
       <c r="R128" t="n">
-        <v>0.9963376862963933</v>
+        <v>0.9962901311557251</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>5.808142489980444</v>
       </c>
       <c r="R129" t="n">
-        <v>0.9768098218635999</v>
+        <v>0.976763198786782</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>5.855071922202427</v>
       </c>
       <c r="R130" t="n">
-        <v>0.9847023848315359</v>
+        <v>0.9846553850431398</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>5.883322388488279</v>
       </c>
       <c r="R131" t="n">
-        <v>0.9894535308283586</v>
+        <v>0.9894063042680363</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>5.89440283426485</v>
       </c>
       <c r="R132" t="n">
-        <v>0.9913170333653322</v>
+        <v>0.9912697178601406</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>5.916202062607435</v>
       </c>
       <c r="R133" t="n">
-        <v>0.9949832141435788</v>
+        <v>0.9949357236517888</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>6.045005314036012</v>
       </c>
       <c r="R134" t="n">
-        <v>1.016645265530997</v>
+        <v>1.016596741110735</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>6.126869184114185</v>
       </c>
       <c r="R135" t="n">
-        <v>1.030413080712197</v>
+        <v>1.030363899154906</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>5.981414211254481</v>
       </c>
       <c r="R136" t="n">
-        <v>1.005950553084239</v>
+        <v>1.005902539121989</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>6.052089168924417</v>
       </c>
       <c r="R137" t="n">
-        <v>1.017836623877247</v>
+        <v>1.01778804259352</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -10219,16 +10219,16 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P138" t="n">
         <v>1</v>
       </c>
       <c r="Q138" t="n">
-        <v>5.968707559985366</v>
+        <v>5.971261839790462</v>
       </c>
       <c r="R138" t="n">
-        <v>1.003813556310472</v>
+        <v>1.004195201045561</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -10287,16 +10287,16 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P139" t="n">
         <v>4</v>
       </c>
       <c r="Q139" t="n">
-        <v>6.021023349349527</v>
+        <v>6.023447592961033</v>
       </c>
       <c r="R139" t="n">
-        <v>1.012611993500609</v>
+        <v>1.012971349923781</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -10355,16 +10355,16 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P140" t="n">
         <v>4</v>
       </c>
       <c r="Q140" t="n">
-        <v>5.983936280687191</v>
+        <v>5.986452005284438</v>
       </c>
       <c r="R140" t="n">
-        <v>1.006374713165976</v>
+        <v>1.006749751775608</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -10423,16 +10423,16 @@
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P141" t="n">
         <v>3</v>
       </c>
       <c r="Q141" t="n">
-        <v>5.942799375126701</v>
+        <v>5.945420608606575</v>
       </c>
       <c r="R141" t="n">
-        <v>0.9994563337594996</v>
+        <v>0.9998494461548528</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>5.983936280687191</v>
       </c>
       <c r="R142" t="n">
-        <v>1.006374713165976</v>
+        <v>1.006326678958591</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>5.87493073085203</v>
       </c>
       <c r="R143" t="n">
-        <v>0.9880422270225473</v>
+        <v>0.9879950678236747</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>5.905361848054571</v>
       </c>
       <c r="R144" t="n">
-        <v>0.9931601135456487</v>
+        <v>0.9931127100703457</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>5.886104031450156</v>
       </c>
       <c r="R145" t="n">
-        <v>0.9899213458261426</v>
+        <v>0.9898740969370373</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>5.857933154483459</v>
       </c>
       <c r="R146" t="n">
-        <v>0.9851835851119296</v>
+        <v>0.9851365623558717</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>5.852202479774474</v>
       </c>
       <c r="R147" t="n">
-        <v>0.9842198037736966</v>
+        <v>0.9841728270188668</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>5.84354441703136</v>
       </c>
       <c r="R148" t="n">
-        <v>0.9827636961213146</v>
+        <v>0.9827167888664196</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>5.921578419643816</v>
       </c>
       <c r="R149" t="n">
-        <v>0.9958874065541544</v>
+        <v>0.9958398729053125</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>5.940171252720432</v>
       </c>
       <c r="R150" t="n">
-        <v>0.9990143377540758</v>
+        <v>0.9989666548569869</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>6.021023349349527</v>
       </c>
       <c r="R151" t="n">
-        <v>1.012611993500609</v>
+        <v>1.01256366158819</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>5.971261839790462</v>
       </c>
       <c r="R152" t="n">
-        <v>1.004243133512772</v>
+        <v>1.004195201045561</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>5.996452088619021</v>
       </c>
       <c r="R153" t="n">
-        <v>1.008479614024979</v>
+        <v>1.008431479350796</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>6.054439346269371</v>
       </c>
       <c r="R154" t="n">
-        <v>1.018231875253678</v>
+        <v>1.018183275104626</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>6.084499413075172</v>
       </c>
       <c r="R155" t="n">
-        <v>1.023287358749897</v>
+        <v>1.023238517302907</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>0.176</v>
       </c>
       <c r="E2" t="n">
-        <v>142.296</v>
+        <v>142.302</v>
       </c>
       <c r="F2" t="n">
         <v>33.3</v>
@@ -11567,7 +11567,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>30.561</v>
+        <v>30.567</v>
       </c>
       <c r="F7" t="n">
         <v>5.9</v>
@@ -11633,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>9.727</v>
+        <v>9.728999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>

--- a/output/economic_index_latest.xlsx
+++ b/output/economic_index_latest.xlsx
@@ -681,22 +681,22 @@
         <v>0.5064935064935064</v>
       </c>
       <c r="F2" t="n">
-        <v>0.382287760015228</v>
+        <v>0.3822881547757291</v>
       </c>
       <c r="G2" t="n">
-        <v>1.074316382522989</v>
+        <v>1.074340739798703</v>
       </c>
       <c r="H2" t="n">
-        <v>133.0057476026592</v>
+        <v>133.0042907638103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3556614853131846</v>
+        <v>0.3556621365032934</v>
       </c>
       <c r="J2" t="n">
-        <v>1.104827223740937</v>
+        <v>1.104849557912769</v>
       </c>
       <c r="K2" t="n">
-        <v>67.78307426565924</v>
+        <v>67.78310682516468</v>
       </c>
       <c r="L2" t="n">
         <v>9.347047788671311</v>
@@ -719,22 +719,22 @@
         <v>0.5089820359281437</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3669924079416162</v>
+        <v>0.3669927054861098</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9011027307246849</v>
+        <v>0.9011164901151221</v>
       </c>
       <c r="H3" t="n">
-        <v>127.684181101771</v>
+        <v>127.682754223205</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3607058561007723</v>
+        <v>0.3607053645771116</v>
       </c>
       <c r="J3" t="n">
-        <v>1.183729489184226</v>
+        <v>1.183740519048633</v>
       </c>
       <c r="K3" t="n">
-        <v>68.03529280503862</v>
+        <v>68.03526822885557</v>
       </c>
       <c r="L3" t="n">
         <v>9.139674667392365</v>
@@ -757,22 +757,22 @@
         <v>0.4759036144578313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3203951613944023</v>
+        <v>0.3203944971317322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3734078336510992</v>
+        <v>0.3733817681109429</v>
       </c>
       <c r="H4" t="n">
-        <v>111.4720439070287</v>
+        <v>111.4704767157468</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2090093944160564</v>
+        <v>0.209008363655057</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.189052962912079</v>
+        <v>-1.189247977406295</v>
       </c>
       <c r="K4" t="n">
-        <v>60.45046972080282</v>
+        <v>60.45041818275286</v>
       </c>
       <c r="L4" t="n">
         <v>9.147281541776893</v>
@@ -795,22 +795,22 @@
         <v>0.3145161290322581</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2067381412481483</v>
+        <v>0.2067381968257412</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.913711770873129</v>
+        <v>-0.9138002537783347</v>
       </c>
       <c r="H5" t="n">
-        <v>71.92843692824171</v>
+        <v>71.92759414355383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2769990985031205</v>
+        <v>0.2769964138848711</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1255820355789048</v>
+        <v>-0.1257143537280899</v>
       </c>
       <c r="K5" t="n">
-        <v>63.84995492515603</v>
+        <v>63.84982069424355</v>
       </c>
       <c r="L5" t="n">
         <v>9.008044950284411</v>
@@ -833,25 +833,25 @@
         <v>0.2063492063492063</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1606964547448569</v>
+        <v>0.1607135962671269</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.435115176025645</v>
+        <v>-1.435038744246432</v>
       </c>
       <c r="H6" t="n">
-        <v>55.90959046029933</v>
+        <v>55.91488415368416</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2227631412726554</v>
+        <v>0.2227922241826409</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9739217144341791</v>
+        <v>-0.9736277458270156</v>
       </c>
       <c r="K6" t="n">
-        <v>61.13815706363277</v>
+        <v>61.13961120913204</v>
       </c>
       <c r="L6" t="n">
-        <v>9.899668813322018</v>
+        <v>9.901573434974267</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1023,7 @@
         <v>8.434897948689407</v>
       </c>
       <c r="R2" t="n">
-        <v>1.001445470484738</v>
+        <v>1.001442356939799</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>9.777470711952642</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9989961528271561</v>
+        <v>0.9989904365186676</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>6.077642243349034</v>
       </c>
       <c r="R4" t="n">
-        <v>1.034819716883472</v>
+        <v>1.034775397563495</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.931</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>422</v>
@@ -1228,7 +1228,7 @@
         <v>6.075346031088684</v>
       </c>
       <c r="R5" t="n">
-        <v>1.034428748539825</v>
+        <v>1.034384445964264</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.9288</v>
       </c>
       <c r="O6" t="n">
         <v>414</v>
@@ -1296,7 +1296,7 @@
         <v>6.061456918928017</v>
       </c>
       <c r="R6" t="n">
-        <v>1.032063896095673</v>
+        <v>1.032019694802152</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>8.682877107057168</v>
       </c>
       <c r="R7" t="n">
-        <v>1.030887155070927</v>
+        <v>1.030883949990293</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.9238</v>
+        <v>0.9237</v>
       </c>
       <c r="O8" t="n">
         <v>398</v>
@@ -1435,7 +1435,7 @@
         <v>6.028278520230698</v>
       </c>
       <c r="R8" t="n">
-        <v>1.026414721667189</v>
+        <v>1.026370762316844</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.9238</v>
+        <v>0.9237</v>
       </c>
       <c r="O9" t="n">
         <v>396</v>
@@ -1503,7 +1503,7 @@
         <v>6.028278520230698</v>
       </c>
       <c r="R9" t="n">
-        <v>1.026414721667189</v>
+        <v>1.026370762316844</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.9223</v>
+        <v>0.9222</v>
       </c>
       <c r="O10" t="n">
         <v>402</v>
@@ -1571,7 +1571,7 @@
         <v>6.018593214496234</v>
       </c>
       <c r="R10" t="n">
-        <v>1.024765637213586</v>
+        <v>1.024721748490327</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>6.003887067106539</v>
       </c>
       <c r="R11" t="n">
-        <v>1.022261670927168</v>
+        <v>1.022217889443926</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>5.996452088619021</v>
       </c>
       <c r="R12" t="n">
-        <v>1.020995742130206</v>
+        <v>1.020952014864237</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.9174</v>
+        <v>0.9173</v>
       </c>
       <c r="O13" t="n">
         <v>389</v>
@@ -1775,7 +1775,7 @@
         <v>5.986452005284438</v>
       </c>
       <c r="R13" t="n">
-        <v>1.019293061552647</v>
+        <v>1.019249407209182</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>8.562740006372207</v>
       </c>
       <c r="R14" t="n">
-        <v>1.016623703864998</v>
+        <v>1.01662054313016</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>5.968707559985366</v>
       </c>
       <c r="R15" t="n">
-        <v>1.016271774493388</v>
+        <v>1.016228249545784</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>5.968707559985366</v>
       </c>
       <c r="R16" t="n">
-        <v>1.016271774493388</v>
+        <v>1.016228249545784</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.9127</v>
+        <v>0.9126</v>
       </c>
       <c r="O17" t="n">
         <v>375</v>
@@ -2049,7 +2049,7 @@
         <v>5.955837369464831</v>
       </c>
       <c r="R17" t="n">
-        <v>1.014080410412149</v>
+        <v>1.014036979316415</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.9123</v>
+        <v>0.9122</v>
       </c>
       <c r="O18" t="n">
         <v>366</v>
@@ -2117,7 +2117,7 @@
         <v>5.953243334287785</v>
       </c>
       <c r="R18" t="n">
-        <v>1.013638732761505</v>
+        <v>1.013595320581967</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.9123</v>
+        <v>0.9122</v>
       </c>
       <c r="O19" t="n">
         <v>382</v>
@@ -2185,7 +2185,7 @@
         <v>5.953243334287785</v>
       </c>
       <c r="R19" t="n">
-        <v>1.013638732761505</v>
+        <v>1.013595320581967</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.9119</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>381</v>
@@ -2253,7 +2253,7 @@
         <v>5.950642552587727</v>
       </c>
       <c r="R20" t="n">
-        <v>1.013195906403064</v>
+        <v>1.01315251318892</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.9115</v>
+        <v>0.9114</v>
       </c>
       <c r="O21" t="n">
         <v>374</v>
@@ -2321,7 +2321,7 @@
         <v>5.948034989180646</v>
       </c>
       <c r="R21" t="n">
-        <v>1.012751925346162</v>
+        <v>1.012708551146865</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.9111</v>
+        <v>0.911</v>
       </c>
       <c r="O22" t="n">
         <v>371</v>
@@ -2389,7 +2389,7 @@
         <v>5.945420608606575</v>
       </c>
       <c r="R22" t="n">
-        <v>1.012306783553151</v>
+        <v>1.012263428418413</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>9.905585350618274</v>
       </c>
       <c r="R23" t="n">
-        <v>1.012086044366422</v>
+        <v>1.012080253156886</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.9099</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="O24" t="n">
         <v>370</v>
@@ -2526,7 +2526,7 @@
         <v>5.937536205082426</v>
       </c>
       <c r="R24" t="n">
-        <v>1.010964332665788</v>
+        <v>1.010921035025617</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.9095</v>
+        <v>0.9094</v>
       </c>
       <c r="O25" t="n">
         <v>373</v>
@@ -2594,7 +2594,7 @@
         <v>5.934894195619588</v>
       </c>
       <c r="R25" t="n">
-        <v>1.010514486594752</v>
+        <v>1.010471208220614</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.9087</v>
+        <v>0.9086</v>
       </c>
       <c r="O26" t="n">
         <v>369</v>
@@ -2662,7 +2662,7 @@
         <v>5.929589143389895</v>
       </c>
       <c r="R26" t="n">
-        <v>1.009611213182699</v>
+        <v>1.009567973494009</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>5.924255797414532</v>
       </c>
       <c r="R27" t="n">
-        <v>1.008703122289671</v>
+        <v>1.008659921492751</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>5.921578419643816</v>
       </c>
       <c r="R28" t="n">
-        <v>1.008247254175731</v>
+        <v>1.008204072902757</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>9.861988245358098</v>
       </c>
       <c r="R29" t="n">
-        <v>1.007631585569008</v>
+        <v>1.007625819848119</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>8.481151420068972</v>
       </c>
       <c r="R30" t="n">
-        <v>1.006936980837208</v>
+        <v>1.006933850218885</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.9062</v>
+        <v>0.9061</v>
       </c>
       <c r="O31" t="n">
         <v>357</v>
@@ -3006,7 +3006,7 @@
         <v>5.91350300563827</v>
       </c>
       <c r="R31" t="n">
-        <v>1.006872280575716</v>
+        <v>1.006829158190193</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3020,20 +3020,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>@uzdaily</t>
+          <t>@spotuz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>84079</v>
+        <v>39856</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-02 06:30:04</t>
+          <t>2026-09-05 14:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>trade</t>
+          <t>prices_inflation</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -3054,165 +3054,29 @@
         <v>0.9</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>pos</t>
+          <t>neg</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0.9058</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>354</v>
+        <v>4753</v>
       </c>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.910796644040527</v>
+        <v>8.47595444339964</v>
       </c>
       <c r="R32" t="n">
-        <v>1.006411477482967</v>
+        <v>1.006316833558297</v>
       </c>
       <c r="S32" t="inlineStr">
-        <is>
-          <t>**Узбекистан реформирует систему таможенного администрирования**
-В Узбекистане утвердили стратегию «Новая таможня — 2030» и отменили ряд требований для бизнеса с сентября 2026 года.
-[Читать далее](https://www.uzdaily.uz/ru/uzbekistan-reformiruet-sistemu-tamozhennogo-administrirovaniia/)
-[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>@uzdaily</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>84108</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:10:05</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>trade</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>0.9058</v>
-      </c>
-      <c r="O33" t="n">
-        <v>362</v>
-      </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.910796644040527</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.006411477482967</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>**Узбекистан и Индия нацелились на товарооборот в $5 млрд**
-Узбекистан и Индия планируют увеличить взаимный товарооборот до $5 млрд за четыре-пять лет и подготовят совместную дорожную карту. 
-[Читать далее](https://www.uzdaily.uz/ru/uzbekistan-i-indiia-natselilis-na-tovarooborot-v-5-mlrd/)
-[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>@spotuz</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>39856</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-09-05 14:30:00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>prices_inflation</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>neg</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>0.9056999999999999</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4753</v>
-      </c>
-      <c r="P34" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>8.47595444339964</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.006319962258279</v>
-      </c>
-      <c r="S34" t="inlineStr">
         <is>
           <t>**Морковь, арбузы, бензин и пропан: что сильнее всего подорожало в Узбекистане в августе**
 В августе потребительские цены выросли на 0,2%, а годовая инфляция замедлилась до 6,2%. Продовольствие за месяц подорожало на 0,4%, непродовольственные товары — на 0,2%, услуги — на 0,1%.
@@ -3223,6 +3087,142 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>@uzdaily</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>84079</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-02 06:30:04</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9056999999999999</v>
+      </c>
+      <c r="O33" t="n">
+        <v>354</v>
+      </c>
+      <c r="P33" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.910796644040527</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.006368374832746</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>**Узбекистан реформирует систему таможенного администрирования**
+В Узбекистане утвердили стратегию «Новая таможня — 2030» и отменили ряд требований для бизнеса с сентября 2026 года.
+[Читать далее](https://www.uzdaily.uz/ru/uzbekistan-reformiruet-sistemu-tamozhennogo-administrirovaniia/)
+[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>@uzdaily</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>84108</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:10:05</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0.9056999999999999</v>
+      </c>
+      <c r="O34" t="n">
+        <v>362</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.910796644040527</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.006368374832746</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>**Узбекистан и Индия нацелились на товарооборот в $5 млрд**
+Узбекистан и Индия планируют увеличить взаимный товарооборот до $5 млрд за четыре-пять лет и подготовят совместную дорожную карту. 
+[Читать далее](https://www.uzdaily.uz/ru/uzbekistan-i-indiia-natselilis-na-tovarooborot-v-5-mlrd/)
+[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>9.835422821621998</v>
       </c>
       <c r="R35" t="n">
-        <v>1.004917309362775</v>
+        <v>1.004911559173118</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>11.31299782670602</v>
       </c>
       <c r="R36" t="n">
-        <v>1.004706225432676</v>
+        <v>1.004687047202611</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3407,16 +3407,16 @@
         <v>0.9039</v>
       </c>
       <c r="O37" t="n">
-        <v>4686</v>
+        <v>4689</v>
       </c>
       <c r="P37" t="n">
         <v>15</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.458928283284262</v>
+        <v>8.459564078579602</v>
       </c>
       <c r="R37" t="n">
-        <v>1.004298506749153</v>
+        <v>1.004370869816195</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="O38" t="n">
         <v>355</v>
@@ -3486,7 +3486,7 @@
         <v>5.897153867636741</v>
       </c>
       <c r="R38" t="n">
-        <v>1.004088567800167</v>
+        <v>1.004045564635659</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="O39" t="n">
         <v>357</v>
@@ -3554,7 +3554,7 @@
         <v>5.897153867636741</v>
       </c>
       <c r="R39" t="n">
-        <v>1.004088567800167</v>
+        <v>1.004045564635659</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>11.30262409866931</v>
       </c>
       <c r="R40" t="n">
-        <v>1.003784935665006</v>
+        <v>1.003765775020884</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>8.454892165218858</v>
       </c>
       <c r="R41" t="n">
-        <v>1.003819312788594</v>
+        <v>1.003816191863259</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>9.820323311275359</v>
       </c>
       <c r="R42" t="n">
-        <v>1.003374543018569</v>
+        <v>1.003368801656702</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>9.810659290224933</v>
       </c>
       <c r="R43" t="n">
-        <v>1.002387138388615</v>
+        <v>1.002381402676729</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>8.442685139241176</v>
       </c>
       <c r="R44" t="n">
-        <v>1.002370015956812</v>
+        <v>1.002366899537415</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>8.442254104751743</v>
       </c>
       <c r="R45" t="n">
-        <v>1.002318840763029</v>
+        <v>1.002315724502738</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>11.28493267508069</v>
       </c>
       <c r="R46" t="n">
-        <v>1.002213762074368</v>
+        <v>1.00219463142143</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>9.80493712880685</v>
       </c>
       <c r="R47" t="n">
-        <v>1.001802486446316</v>
+        <v>1.001796754079839</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>12.50087803679753</v>
       </c>
       <c r="R48" t="n">
-        <v>1.001754439821594</v>
+        <v>1.001738155024378</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>8.434246270595311</v>
       </c>
       <c r="R49" t="n">
-        <v>1.001368099059557</v>
+        <v>1.00136498575517</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>5.8805329864007</v>
       </c>
       <c r="R50" t="n">
-        <v>1.001258586217448</v>
+        <v>1.001215704255558</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>9.796904067133344</v>
       </c>
       <c r="R51" t="n">
-        <v>1.000981722268782</v>
+        <v>1.000975994598761</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>12.48825839081144</v>
       </c>
       <c r="R52" t="n">
-        <v>1.000743167944664</v>
+        <v>1.000726899586963</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>8.427706024914702</v>
       </c>
       <c r="R53" t="n">
-        <v>1.000591598922561</v>
+        <v>1.000588488032353</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -4575,19 +4575,19 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.9</v>
+        <v>0.9001</v>
       </c>
       <c r="O54" t="n">
-        <v>77636</v>
+        <v>77729</v>
       </c>
       <c r="P54" t="n">
         <v>19</v>
       </c>
       <c r="Q54" t="n">
-        <v>11.26028873426125</v>
+        <v>11.26148531450091</v>
       </c>
       <c r="R54" t="n">
-        <v>1.000025136111581</v>
+        <v>1.000112313381027</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>9.785998223743661</v>
       </c>
       <c r="R55" t="n">
-        <v>0.9998674365899397</v>
+        <v>0.9998617152959197</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>5.872117789475416</v>
       </c>
       <c r="R56" t="n">
-        <v>0.9998257589217524</v>
+        <v>0.9997829383250749</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>9.779793330189797</v>
       </c>
       <c r="R57" t="n">
-        <v>0.999233462326899</v>
+        <v>0.9992277446605131</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>9.768183160505229</v>
       </c>
       <c r="R58" t="n">
-        <v>0.9980472133275157</v>
+        <v>0.9980415024489089</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>5.860786223465865</v>
       </c>
       <c r="R59" t="n">
-        <v>0.9978963712644446</v>
+        <v>0.9978536332996958</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>11.23520692460461</v>
       </c>
       <c r="R60" t="n">
-        <v>0.997797623060385</v>
+        <v>0.9977785767044561</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>12.44941482415358</v>
       </c>
       <c r="R61" t="n">
-        <v>0.9976304493625391</v>
+        <v>0.9976142316060523</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>12.44427819332104</v>
       </c>
       <c r="R62" t="n">
-        <v>0.997218826856738</v>
+        <v>0.9972026157917007</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>8.398184404834035</v>
       </c>
       <c r="R63" t="n">
-        <v>0.9970866018388973</v>
+        <v>0.9970835018459036</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>9.757999245787522</v>
       </c>
       <c r="R64" t="n">
-        <v>0.9970066894616377</v>
+        <v>0.9970009845369632</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>9.756957759840232</v>
       </c>
       <c r="R65" t="n">
-        <v>0.9969002774369722</v>
+        <v>0.9968945731211928</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>8.392083380373393</v>
       </c>
       <c r="R66" t="n">
-        <v>0.9963622488771194</v>
+        <v>0.996359151136176</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>8.389814262086407</v>
       </c>
       <c r="R67" t="n">
-        <v>0.9960928445234072</v>
+        <v>0.9960897476200555</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>9.745019231764333</v>
       </c>
       <c r="R68" t="n">
-        <v>0.9956804789870866</v>
+        <v>0.995674781651058</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>9.740380214665977</v>
       </c>
       <c r="R69" t="n">
-        <v>0.9952064954415781</v>
+        <v>0.9952008008177083</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>8.38160253710989</v>
       </c>
       <c r="R70" t="n">
-        <v>0.9951178955871397</v>
+        <v>0.9951148017149539</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.8955</v>
+        <v>0.8954</v>
       </c>
       <c r="O71" t="n">
         <v>16932</v>
@@ -5761,7 +5761,7 @@
         <v>9.737846105993372</v>
       </c>
       <c r="R71" t="n">
-        <v>0.9949475772725178</v>
+        <v>0.9949418841301915</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.8955</v>
+        <v>0.8954</v>
       </c>
       <c r="O72" t="n">
         <v>338</v>
@@ -5828,7 +5828,7 @@
         <v>5.84354441703136</v>
       </c>
       <c r="R72" t="n">
-        <v>0.9949606668352082</v>
+        <v>0.994918054600982</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>12.41021277010235</v>
       </c>
       <c r="R73" t="n">
-        <v>0.9944890034912689</v>
+        <v>0.994472836802995</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>8.375399185798351</v>
       </c>
       <c r="R74" t="n">
-        <v>0.9943813937218466</v>
+        <v>0.9943783021394826</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>8.374707543119483</v>
       </c>
       <c r="R75" t="n">
-        <v>0.9942992774434802</v>
+        <v>0.9942961861164199</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>8.373322820996535</v>
       </c>
       <c r="R76" t="n">
-        <v>0.9941348743047177</v>
+        <v>0.9941317834887952</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>8.371936178759098</v>
       </c>
       <c r="R77" t="n">
-        <v>0.9939702431975826</v>
+        <v>0.9939671528935066</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6187,20 +6187,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>@spotuz</t>
+          <t>@uzdaily</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>39853</v>
+        <v>84273</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-05 11:23:28</t>
+          <t>2026-09-06 12:10:03</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>prices_inflation</t>
+          <t>banking_finance</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -6229,21 +6229,89 @@
         </is>
       </c>
       <c r="N78" t="n">
+        <v>0.8927</v>
+      </c>
+      <c r="O78" t="n">
+        <v>330</v>
+      </c>
+      <c r="P78" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5.82600010738045</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.9919309719022819</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>**Международные инвесторы изучили финансовый рынок Узбекистана**
+Представители крупных институциональных инвесторов обсудили в Минэкономфине реформы, рынок облигаций и перспективы повышения суверенного рейтинга Узбекистана.
+[Читать далее](https://www.uzdaily.uz/ru/mezhdunarodnye-investory-izuchili-finansovyi-rynok-uzbekistana/)
+[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>@spotuz</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>39853</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-09-05 11:23:28</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>prices_inflation</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
         <v>0.8925</v>
       </c>
-      <c r="O78" t="n">
+      <c r="O79" t="n">
         <v>4219</v>
       </c>
-      <c r="P78" t="n">
+      <c r="P79" t="n">
         <v>10</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q79" t="n">
         <v>8.352318548226004</v>
       </c>
-      <c r="R78" t="n">
-        <v>0.9916411116113418</v>
-      </c>
-      <c r="S78" t="inlineStr">
+      <c r="R79" t="n">
+        <v>0.9916380285486545</v>
+      </c>
+      <c r="S79" t="inlineStr">
         <is>
           <t>**Месячная и годовая инфляция в Узбекистане снизились до минимума с мая**
 Годовая инфляция в августе замедлилась с 6,4% до 6,2%, следует из данных Национального комитета по статистике. Это минимальный показатель с мая. В августе 2025 года годовой рост цен составлял 8,8%.
@@ -6254,74 +6322,6 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>@uzdaily</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>84273</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2026-09-06 12:10:03</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>banking_finance</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>0.8923</v>
-      </c>
-      <c r="O79" t="n">
-        <v>329</v>
-      </c>
-      <c r="P79" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>5.823045895483019</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.99147045246986</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>**Международные инвесторы изучили финансовый рынок Узбекистана**
-Представители крупных институциональных инвесторов обсудили в Минэкономфине реформы, рынок облигаций и перспективы повышения суверенного рейтинга Узбекистана.
-[Читать далее](https://www.uzdaily.uz/ru/mezhdunarodnye-investory-izuchili-finansovyi-rynok-uzbekistana/)
-[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>12.36230686756081</v>
       </c>
       <c r="R80" t="n">
-        <v>0.9906500771035879</v>
+        <v>0.990633972821963</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>8.343791731996841</v>
       </c>
       <c r="R81" t="n">
-        <v>0.9906287530099344</v>
+        <v>0.9906256730947213</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>9.663642809498507</v>
       </c>
       <c r="R82" t="n">
-        <v>0.9873659838411162</v>
+        <v>0.9873603340810658</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>5.793013608384144</v>
       </c>
       <c r="R83" t="n">
-        <v>0.9863569558886767</v>
+        <v>0.9863147121346912</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>9.64445772265751</v>
       </c>
       <c r="R84" t="n">
-        <v>0.985405780787541</v>
+        <v>0.9854001422438756</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>5.771441123130016</v>
       </c>
       <c r="R85" t="n">
-        <v>0.9826838813329014</v>
+        <v>0.9826417948895702</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -6782,19 +6782,19 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0.8808</v>
+        <v>0.8809</v>
       </c>
       <c r="O86" t="n">
-        <v>61026</v>
+        <v>61122</v>
       </c>
       <c r="P86" t="n">
         <v>23</v>
       </c>
       <c r="Q86" t="n">
-        <v>11.01982514896675</v>
+        <v>11.02139580422003</v>
       </c>
       <c r="R86" t="n">
-        <v>0.9786695887282945</v>
+        <v>0.9787903945719389</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>5.746203190540153</v>
       </c>
       <c r="R87" t="n">
-        <v>0.9783867033794037</v>
+        <v>0.9783448009758636</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.8751</v>
+        <v>0.875</v>
       </c>
       <c r="O88" t="n">
         <v>295</v>
@@ -6930,7 +6930,7 @@
         <v>5.71042701737487</v>
       </c>
       <c r="R88" t="n">
-        <v>0.9722952146237787</v>
+        <v>0.972253573106879</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0.8751</v>
+        <v>0.875</v>
       </c>
       <c r="O89" t="n">
         <v>299</v>
@@ -6998,7 +6998,7 @@
         <v>5.71042701737487</v>
       </c>
       <c r="R89" t="n">
-        <v>0.9722952146237787</v>
+        <v>0.972253573106879</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>8.477620416296414</v>
       </c>
       <c r="R90" t="n">
-        <v>1.006517757302341</v>
+        <v>1.006514627987405</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>8.451907724717607</v>
       </c>
       <c r="R91" t="n">
-        <v>1.003464980769393</v>
+        <v>1.003461860945695</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>9.798682438170001</v>
       </c>
       <c r="R92" t="n">
-        <v>1.001163424252481</v>
+        <v>1.001157695542751</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>8.418256443556213</v>
       </c>
       <c r="R93" t="n">
-        <v>0.9994696836952514</v>
+        <v>0.9994665762931348</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>8.376781037699493</v>
       </c>
       <c r="R94" t="n">
-        <v>0.99454545608937</v>
+        <v>0.9945423639969276</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -7408,19 +7408,19 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0.8247</v>
+        <v>0.8253</v>
       </c>
       <c r="O95" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P95" t="n">
         <v>9</v>
       </c>
       <c r="Q95" t="n">
-        <v>6.054439346269371</v>
+        <v>6.059123195581797</v>
       </c>
       <c r="R95" t="n">
-        <v>1.030869037586228</v>
+        <v>1.031622356589948</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.8244</v>
+        <v>0.8243</v>
       </c>
       <c r="O96" t="n">
         <v>418</v>
@@ -7488,7 +7488,7 @@
         <v>6.052089168924417</v>
       </c>
       <c r="R96" t="n">
-        <v>1.030468880789011</v>
+        <v>1.0304247478069</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>6.018593214496234</v>
       </c>
       <c r="R97" t="n">
-        <v>1.024765637213586</v>
+        <v>1.024721748490327</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0.8175</v>
+        <v>0.8174</v>
       </c>
       <c r="O98" t="n">
         <v>399</v>
@@ -7624,7 +7624,7 @@
         <v>6.00141487796115</v>
       </c>
       <c r="R98" t="n">
-        <v>1.021840739590792</v>
+        <v>1.021796976135221</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>5.996452088619021</v>
       </c>
       <c r="R99" t="n">
-        <v>1.020995742130206</v>
+        <v>1.020952014864237</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0.8165</v>
+        <v>0.8164</v>
       </c>
       <c r="O100" t="n">
         <v>392</v>
@@ -7760,7 +7760,7 @@
         <v>5.993961427306569</v>
       </c>
       <c r="R100" t="n">
-        <v>1.020571665600032</v>
+        <v>1.020527956496437</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>5.986452005284438</v>
       </c>
       <c r="R101" t="n">
-        <v>1.019293061552647</v>
+        <v>1.019249407209182</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>5.983936280687191</v>
       </c>
       <c r="R102" t="n">
-        <v>1.018864717581212</v>
+        <v>1.018821081582888</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>5.968707559985366</v>
       </c>
       <c r="R103" t="n">
-        <v>1.016271774493388</v>
+        <v>1.016228249545784</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>8.557182839632397</v>
       </c>
       <c r="R104" t="n">
-        <v>1.01596392119849</v>
+        <v>1.015960762514949</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>8.532081803909987</v>
       </c>
       <c r="R105" t="n">
-        <v>1.012983764392611</v>
+        <v>1.01298061497453</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>8.509362612301048</v>
       </c>
       <c r="R106" t="n">
-        <v>1.010286395477391</v>
+        <v>1.010283254445567</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0.8072</v>
+        <v>0.8071</v>
       </c>
       <c r="O107" t="n">
         <v>85831</v>
@@ -8241,7 +8241,7 @@
         <v>11.36072954003082</v>
       </c>
       <c r="R107" t="n">
-        <v>1.008945274203179</v>
+        <v>1.008926015056473</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>8.49596955496461</v>
       </c>
       <c r="R108" t="n">
-        <v>1.008696285355477</v>
+        <v>1.008693149267387</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>5.921578419643816</v>
       </c>
       <c r="R109" t="n">
-        <v>1.008247254175731</v>
+        <v>1.008204072902757</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>5.921578419643816</v>
       </c>
       <c r="R110" t="n">
-        <v>1.008247254175731</v>
+        <v>1.008204072902757</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0.8052</v>
+        <v>0.8051</v>
       </c>
       <c r="O111" t="n">
         <v>83317</v>
@@ -8514,7 +8514,7 @@
         <v>11.33264981388319</v>
       </c>
       <c r="R111" t="n">
-        <v>1.006451516482978</v>
+        <v>1.006432304938106</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>8.473241303887054</v>
       </c>
       <c r="R112" t="n">
-        <v>1.00599784084173</v>
+        <v>1.005994713143241</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>8.470520783217808</v>
       </c>
       <c r="R113" t="n">
-        <v>1.005674843086671</v>
+        <v>1.005671716392398</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>12.5414120979364</v>
       </c>
       <c r="R114" t="n">
-        <v>1.005002625716244</v>
+        <v>1.004986288115619</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>8.461891875631148</v>
       </c>
       <c r="R115" t="n">
-        <v>1.004650363541043</v>
+        <v>1.00464724003193</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>11.3098173569857</v>
       </c>
       <c r="R116" t="n">
-        <v>1.004423768229311</v>
+        <v>1.004404595390901</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>12.53336718131419</v>
       </c>
       <c r="R117" t="n">
-        <v>1.004357948524724</v>
+        <v>1.00434162140415</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>11.30817423321009</v>
       </c>
       <c r="R118" t="n">
-        <v>1.004277842568244</v>
+        <v>1.004258672515321</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -9013,20 +9013,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>@uzdaily</t>
+          <t>@spotuz</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>84196</v>
+        <v>39859</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-09-04 09:20:04</t>
+          <t>2026-09-06 11:00:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>banking_finance</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -9047,165 +9047,29 @@
         <v>0.8</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>neu</t>
+          <t>neg</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0.8033</v>
+        <v>0.8032</v>
       </c>
       <c r="O119" t="n">
-        <v>355</v>
+        <v>4673</v>
       </c>
       <c r="P119" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Q119" t="n">
-        <v>5.897153867636741</v>
+        <v>8.456168489578463</v>
       </c>
       <c r="R119" t="n">
-        <v>1.004088567800167</v>
+        <v>1.003967724849512</v>
       </c>
       <c r="S119" t="inlineStr">
-        <is>
-          <t>**Центробанк Узбекистана продал тонну золота в июле**
-Узбекистан сократил золотые резервы на 1 тонну в июле, при этом с начала года купил 40 тонн золота — таковы данные Всемирного золотого совета.
-[Читать далее](https://www.uzdaily.uz/ru/tsentrobank-uzbekistana-prodal-tonnu-zolota-v-iiule/)
-[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>@daryo</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>136323</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2026-09-04 06:55:23</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>energy_utility</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L120" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>neg</t>
-        </is>
-      </c>
-      <c r="N120" t="n">
-        <v>0.8032</v>
-      </c>
-      <c r="O120" t="n">
-        <v>81158</v>
-      </c>
-      <c r="P120" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>11.30448578002122</v>
-      </c>
-      <c r="R120" t="n">
-        <v>1.003950271402949</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>**Avgustda 71,9 mlrd so‘mlik gaz va elektr energiyasi talon-toroj qilindi**
-“O‘zenergoinspeksiya” tomonidan bir oy davomida o‘tkazilgan nazorat tadbirlarida energiya resurslaridan noqonuniy foydalanish bilan bog‘liq 321 ta holat aniqlandi.
-Batafsil — https://daryo.uz/XfBxD8QDR
-👉 Obuna bo‘ling — @daryo</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>@spotuz</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>39859</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2026-09-06 11:00:00</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>banking_finance</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="n">
-        <v>1</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L121" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>neg</t>
-        </is>
-      </c>
-      <c r="N121" t="n">
-        <v>0.8031</v>
-      </c>
-      <c r="O121" t="n">
-        <v>4670</v>
-      </c>
-      <c r="P121" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>8.455530531024131</v>
-      </c>
-      <c r="R121" t="n">
-        <v>1.003895103693012</v>
-      </c>
-      <c r="S121" t="inlineStr">
         <is>
           <t>**ЦБ допускает «некоторые проблемы» с оценкой качества активов после перехода банков на МСФО**
 Требования к валютным рискам усилят на фоне либерализации финансового рынка, заявил глава регулятора Тимур Ишметов. Узбекистан уже внедрил соответствующие мировому уровню критерии достаточности капитала и ликвидности.
@@ -9217,6 +9081,142 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>@uzdaily</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>84196</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:20:04</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0.8032</v>
+      </c>
+      <c r="O120" t="n">
+        <v>355</v>
+      </c>
+      <c r="P120" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>5.897153867636741</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1.004045564635659</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>**Центробанк Узбекистана продал тонну золота в июле**
+Узбекистан сократил золотые резервы на 1 тонну в июле, при этом с начала года купил 40 тонн золота — таковы данные Всемирного золотого совета.
+[Читать далее](https://www.uzdaily.uz/ru/tsentrobank-uzbekistana-prodal-tonnu-zolota-v-iiule/)
+[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>@daryo</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>136323</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:55:23</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>energy_utility</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0.8031</v>
+      </c>
+      <c r="O121" t="n">
+        <v>81158</v>
+      </c>
+      <c r="P121" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>11.30448578002122</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1.003931107602833</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>**Avgustda 71,9 mlrd so‘mlik gaz va elektr energiyasi talon-toroj qilindi**
+“O‘zenergoinspeksiya” tomonidan bir oy davomida o‘tkazilgan nazorat tadbirlarida energiya resurslaridan noqonuniy foydalanish bilan bog‘liq 321 ta holat aniqlandi.
+Batafsil — https://daryo.uz/XfBxD8QDR
+👉 Obuna bo‘ling — @daryo</t>
+        </is>
+      </c>
+    </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>11.29708021613713</v>
       </c>
       <c r="R122" t="n">
-        <v>1.003292584002036</v>
+        <v>1.003273432756118</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>11.29514251989811</v>
       </c>
       <c r="R123" t="n">
-        <v>1.003120497389437</v>
+        <v>1.003101349428376</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>8.448485993406447</v>
       </c>
       <c r="R124" t="n">
-        <v>1.003058730765704</v>
+        <v>1.003055612205057</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>8.445697189711167</v>
       </c>
       <c r="R125" t="n">
-        <v>1.002727626009523</v>
+        <v>1.002724508478298</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>12.50988516991127</v>
       </c>
       <c r="R126" t="n">
-        <v>1.002476223968291</v>
+        <v>1.002459927437552</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>11.28668963749443</v>
       </c>
       <c r="R127" t="n">
-        <v>1.002369797733702</v>
+        <v>1.002350664102294</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -9631,20 +9631,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>@uzdaily</t>
+          <t>@daryo</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>84094</v>
+        <v>136261</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-09-02 11:50:05</t>
+          <t>2026-09-02 13:55:01</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>construction_realty</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -9665,29 +9665,97 @@
         <v>0.8</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0.8017</v>
+      </c>
+      <c r="O128" t="n">
+        <v>79439</v>
+      </c>
+      <c r="P128" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>11.28363807889553</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1.002079660656076</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>**Jizzaxda 200 gektar maydonda atomchilar shaharchasi quriladi**
+Loyiha doirasida qariyb 10 mingta xonadon, jumladan, birinchi bosqichda 3 mingta xonadonli turar joylar quriladi. Shaharchada energiya samarador ko‘p qavatli uylar, maktab va bog‘chalar boʻladi.
+Batafsil — https://daryo.uz/YXC4j-QDg
+👉 Obuna bo‘ling — @daryo</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>@uzdaily</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>84094</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:50:05</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
           <t>neu</t>
         </is>
       </c>
-      <c r="N128" t="n">
-        <v>0.8018</v>
-      </c>
-      <c r="O128" t="n">
+      <c r="N129" t="n">
+        <v>0.8017</v>
+      </c>
+      <c r="O129" t="n">
         <v>353</v>
       </c>
-      <c r="P128" t="n">
+      <c r="P129" t="n">
         <v>3</v>
       </c>
-      <c r="Q128" t="n">
+      <c r="Q129" t="n">
         <v>5.886104031450156</v>
       </c>
-      <c r="R128" t="n">
-        <v>1.002207149332878</v>
-      </c>
-      <c r="S128" t="inlineStr">
+      <c r="R129" t="n">
+        <v>1.002164226745871</v>
+      </c>
+      <c r="S129" t="inlineStr">
         <is>
           <t>**Узбекистан внедрит новую модель управления данными**
 Узбекистан обновит статистическую систему, проведет перепись бизнеса и запустит Национальную платформу данных до июля 2027 года.
@@ -9696,66 +9764,66 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>@uzdaily</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="B130" t="n">
         <v>84146</v>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>2026-09-03 13:00:06</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>trade</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" t="n">
-        <v>1</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="n">
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="n">
         <v>0.8</v>
       </c>
-      <c r="L129" t="n">
+      <c r="L130" t="n">
         <v>0.5</v>
       </c>
-      <c r="M129" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="N129" t="n">
-        <v>0.8018</v>
-      </c>
-      <c r="O129" t="n">
+      <c r="N130" t="n">
+        <v>0.8017</v>
+      </c>
+      <c r="O130" t="n">
         <v>355</v>
       </c>
-      <c r="P129" t="n">
+      <c r="P130" t="n">
         <v>2</v>
       </c>
-      <c r="Q129" t="n">
+      <c r="Q130" t="n">
         <v>5.886104031450156</v>
       </c>
-      <c r="R129" t="n">
-        <v>1.002207149332878</v>
-      </c>
-      <c r="S129" t="inlineStr">
+      <c r="R130" t="n">
+        <v>1.002164226745871</v>
+      </c>
+      <c r="S130" t="inlineStr">
         <is>
           <t>**Узбекистан расширит импорт мяса из Индии и посевы джута**
 Узбекистан планирует увеличить импорт мяса из Индии, расширить сотрудничество в семеноводстве и выращивать джут минимум на 50 тысячах гектаров.
@@ -9764,74 +9832,6 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>@daryo</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>136261</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:55:01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>construction_realty</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N130" t="n">
-        <v>0.8017</v>
-      </c>
-      <c r="O130" t="n">
-        <v>79439</v>
-      </c>
-      <c r="P130" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>11.28363807889553</v>
-      </c>
-      <c r="R130" t="n">
-        <v>1.002098789114365</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>**Jizzaxda 200 gektar maydonda atomchilar shaharchasi quriladi**
-Loyiha doirasida qariyb 10 mingta xonadon, jumladan, birinchi bosqichda 3 mingta xonadonli turar joylar quriladi. Shaharchada energiya samarador ko‘p qavatli uylar, maktab va bog‘chalar boʻladi.
-Batafsil — https://daryo.uz/YXC4j-QDg
-👉 Obuna bo‘ling — @daryo</t>
-        </is>
-      </c>
-    </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>11.28322295060864</v>
       </c>
       <c r="R131" t="n">
-        <v>1.002061921611995</v>
+        <v>1.002042793857447</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>8.439231649946526</v>
       </c>
       <c r="R132" t="n">
-        <v>1.001959995440555</v>
+        <v>1.001956880295933</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>8.429017500512511</v>
       </c>
       <c r="R133" t="n">
-        <v>1.000747305761584</v>
+        <v>1.000744194387276</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>8.427049641563272</v>
       </c>
       <c r="R134" t="n">
-        <v>1.000513668858891</v>
+        <v>1.000510558210971</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>11.26337376787972</v>
       </c>
       <c r="R135" t="n">
-        <v>1.000299117644118</v>
+        <v>1.00028002353867</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>5.87493073085203</v>
       </c>
       <c r="R136" t="n">
-        <v>1.000304708995219</v>
+        <v>1.00026186788604</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>8.422662707570003</v>
       </c>
       <c r="R137" t="n">
-        <v>0.9999928237694067</v>
+        <v>0.999989714740821</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>8.422442854870427</v>
       </c>
       <c r="R138" t="n">
-        <v>0.9999667214393603</v>
+        <v>0.9999636124919281</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>12.47468657088914</v>
       </c>
       <c r="R139" t="n">
-        <v>0.9996555938699788</v>
+        <v>0.9996393431921829</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>12.46866380733144</v>
       </c>
       <c r="R140" t="n">
-        <v>0.9991729613607933</v>
+        <v>0.9991567185288049</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>11.24709620433107</v>
       </c>
       <c r="R141" t="n">
-        <v>0.9988535088247124</v>
+        <v>0.9988344423136182</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>12.46304934618068</v>
       </c>
       <c r="R142" t="n">
-        <v>0.99872304805323</v>
+        <v>0.9987068125351568</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>12.46133482672584</v>
       </c>
       <c r="R143" t="n">
-        <v>0.9985856555060036</v>
+        <v>0.9985694222214218</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>11.24339760309849</v>
       </c>
       <c r="R144" t="n">
-        <v>0.9985250364126523</v>
+        <v>0.9985059761715696</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>9.771840098470129</v>
       </c>
       <c r="R145" t="n">
-        <v>0.9984208546367753</v>
+        <v>0.9984151416201733</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>12.45449010386504</v>
       </c>
       <c r="R146" t="n">
-        <v>0.9980371555130452</v>
+        <v>0.9980209311450309</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -10931,20 +10931,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>@daryo</t>
+          <t>@gazetauz</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>136290</v>
+        <v>63975</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-09-03 09:23:46</t>
+          <t>2026-09-03 08:59:50</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>labour_income</t>
+          <t>fiscal</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -10965,7 +10965,7 @@
         <v>0.8</v>
       </c>
       <c r="L147" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -10976,18 +10976,86 @@
         <v>0.7983</v>
       </c>
       <c r="O147" t="n">
+        <v>17369</v>
+      </c>
+      <c r="P147" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>9.76663636978693</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.9978834626878704</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>За последние три года на предпринимательские проекты в махаллях направили 314 трлн сумов, но их влияние на сокращение бедности различается по районам, заявил президент. 
+При одинаковых объёмах финансирования в одних районах из бедности удалось вывести в несколько раз больше людей, чем в других.
+https://www.gazeta.uz/ru/2026/09/03/poverty/
+[Telegram](https://t.me/gazetauz)  |  [Instagram](https://instagram.com/gazetauzb)  |  [YouTube](https://youtube.com/@GazetaUzb)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>@daryo</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>136290</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:23:46</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>labour_income</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="O148" t="n">
         <v>75729</v>
       </c>
-      <c r="P147" t="n">
+      <c r="P148" t="n">
         <v>23</v>
       </c>
-      <c r="Q147" t="n">
+      <c r="Q148" t="n">
         <v>11.23553689880362</v>
       </c>
-      <c r="R147" t="n">
-        <v>0.9978269280365777</v>
-      </c>
-      <c r="S147" t="inlineStr">
+      <c r="R148" t="n">
+        <v>0.9978078811212638</v>
+      </c>
+      <c r="S148" t="inlineStr">
         <is>
           <t>**Shavkat Mirziyoyev 2026-yil oxirigacha 230 ming oilani kambag‘allikdan chiqarishni topshirdi**
 Viloyat va tuman hokimlari shtablar faoliyatini samarali tashkil etishi lozim. Ular sentyabr-dekabr oylarida 350 ming odamni doimiy ishga joylashtirish va yana 1 mln aholining daromadini ko‘paytirish majburiyatini oladi.
@@ -10996,74 +11064,6 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>@gazetauz</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>63975</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026-09-03 08:59:50</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>fiscal</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L148" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N148" t="n">
-        <v>0.7983</v>
-      </c>
-      <c r="O148" t="n">
-        <v>17369</v>
-      </c>
-      <c r="P148" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>9.76663636978693</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.9978891726621603</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>За последние три года на предпринимательские проекты в махаллях направили 314 трлн сумов, но их влияние на сокращение бедности различается по районам, заявил президент. 
-При одинаковых объёмах финансирования в одних районах из бедности удалось вывести в несколько раз больше людей, чем в других.
-https://www.gazeta.uz/ru/2026/09/03/poverty/
-[Telegram](https://t.me/gazetauz)  |  [Instagram](https://instagram.com/gazetauzb)  |  [YouTube](https://youtube.com/@GazetaUzb)</t>
-        </is>
-      </c>
-    </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>0.7982</v>
+        <v>0.7981</v>
       </c>
       <c r="O149" t="n">
         <v>75657</v>
@@ -11121,7 +11121,7 @@
         <v>11.23397846379058</v>
       </c>
       <c r="R149" t="n">
-        <v>0.9976885235761932</v>
+        <v>0.9976694793027985</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>5.857933154483459</v>
       </c>
       <c r="R150" t="n">
-        <v>0.9974105887984146</v>
+        <v>0.9973678716387858</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>9.758692967632895</v>
       </c>
       <c r="R151" t="n">
-        <v>0.9970775692908979</v>
+        <v>0.9970718639606452</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>9.757710052922787</v>
       </c>
       <c r="R152" t="n">
-        <v>0.9969771416810504</v>
+        <v>0.9969714369254499</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>9.757247170313121</v>
       </c>
       <c r="R153" t="n">
-        <v>0.9969298474512962</v>
+        <v>0.9969241429663156</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>8.396154863039181</v>
       </c>
       <c r="R154" t="n">
-        <v>0.9968456415510574</v>
+        <v>0.9968425423072215</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -11478,20 +11478,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>@kunuzofficial</t>
+          <t>@spotuz</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>173798</v>
+        <v>39816</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-09-03 07:15:24</t>
+          <t>2026-09-03 16:10:01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>banking_finance</t>
+          <t>construction_realty</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -11523,87 +11523,18 @@
         <v>0.7971</v>
       </c>
       <c r="O155" t="n">
-        <v>250378</v>
+        <v>4363</v>
       </c>
       <c r="P155" t="n">
-        <v>301</v>
+        <v>25</v>
       </c>
       <c r="Q155" t="n">
-        <v>12.43313251803759</v>
+        <v>8.392536586816682</v>
       </c>
       <c r="R155" t="n">
-        <v>0.9963256712186185</v>
+        <v>0.9964129585599893</v>
       </c>
       <c r="S155" t="inlineStr">
-        <is>
-          <t>**Пискентда ҳар бир одамни камбағалликдан чиқаришга 250 миллион сўм кредит тўғри келмоқда**
-Президент камбағалликни қисқартириш мавзусида йиғилиш ўтказмоқда. Йиғилишда [айтилишича](https://kun.uz/kr/36467612), **эҳтиёжманд аҳоли сони** йил бошидаги 2,2 млн нафардан ҳозир 1,5 млн нафаргача камайган. 49 та туман ва 3429 та маҳалла **ишсизлик ва камбағалликдан холи** ҳудудга айланмоқда.
-“Ўтган уч йилда маҳаллалардаги тадбиркорлик лойиҳаларига **314 триллион сўм** ресурс ажратилди. Лекин кредитларнинг камбағалликни қисқартиришга таъсири барча туманда бирдек сезилмаяпти”, деди Шавкат Мирзиёев.
-[Масалан](https://kun.uz/kr/37556328), Пискентда **ҳар бир одамни камбағалликдан чиқаришга 250 миллион сўм** кредит тўғри келяпти. Ваҳоланки, бошқа ҳудудда шунча пулга саноатда юқори даромадли доимий иш ўрни яратилмоқда.
-[Kun.uz расмий канали](https://t.me/kunuzofficial)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>@spotuz</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>39816</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2026-09-03 16:10:01</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>construction_realty</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L156" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N156" t="n">
-        <v>0.7971</v>
-      </c>
-      <c r="O156" t="n">
-        <v>4363</v>
-      </c>
-      <c r="P156" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>8.392536586816682</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.9964160564682234</v>
-      </c>
-      <c r="S156" t="inlineStr">
         <is>
           <t>**В Джизакской области создадут промзону на 200 га по производству стройматериалов для АЭС**
 В Фаришском районе планируется создать специализированную промышленную зону площадью 200 га для производства строительных материалов для атомной отрасли. На ее территории хотят разместить не менее 100 совместных предприятий и локализовать выпуск продукции по 15 направлениям за счет трансфера технологий.
@@ -11614,66 +11545,66 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>@gazetauz</t>
         </is>
       </c>
-      <c r="B157" t="n">
+      <c r="B156" t="n">
         <v>63954</v>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>2026-09-02 12:50:00</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>trade</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="n">
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="n">
         <v>0.8</v>
       </c>
-      <c r="L157" t="n">
+      <c r="L156" t="n">
         <v>0.5</v>
       </c>
-      <c r="M157" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="N157" t="n">
+      <c r="N156" t="n">
         <v>0.797</v>
       </c>
-      <c r="O157" t="n">
+      <c r="O156" t="n">
         <v>17046</v>
       </c>
-      <c r="P157" t="n">
+      <c r="P156" t="n">
         <v>61</v>
       </c>
-      <c r="Q157" t="n">
+      <c r="Q156" t="n">
         <v>9.750860711077213</v>
       </c>
-      <c r="R157" t="n">
-        <v>0.996277322028841</v>
-      </c>
-      <c r="S157" t="inlineStr">
+      <c r="R156" t="n">
+        <v>0.9962716212776452</v>
+      </c>
+      <c r="S156" t="inlineStr">
         <is>
           <t>В Узбекистане планируют создать отдельный механизм временного ввоза автомобилей, зарегистрированных за рубежом, для граждан страны. 
 Сейчас такой упрощённый порядок предусмотрен для иностранных физлиц, а для узбекистанцев общего механизма нет.
@@ -11682,6 +11613,75 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>@kunuzofficial</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>173798</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-09-03 07:15:24</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>banking_finance</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="O157" t="n">
+        <v>250378</v>
+      </c>
+      <c r="P157" t="n">
+        <v>301</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>12.43313251803759</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.9963094746729662</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>**Пискентда ҳар бир одамни камбағалликдан чиқаришга 250 миллион сўм кредит тўғри келмоқда**
+Президент камбағалликни қисқартириш мавзусида йиғилиш ўтказмоқда. Йиғилишда [айтилишича](https://kun.uz/kr/36467612), **эҳтиёжманд аҳоли сони** йил бошидаги 2,2 млн нафардан ҳозир 1,5 млн нафаргача камайган. 49 та туман ва 3429 та маҳалла **ишсизлик ва камбағалликдан холи** ҳудудга айланмоқда.
+“Ўтган уч йилда маҳаллалардаги тадбиркорлик лойиҳаларига **314 триллион сўм** ресурс ажратилди. Лекин кредитларнинг камбағалликни қисқартиришга таъсири барча туманда бирдек сезилмаяпти”, деди Шавкат Мирзиёев.
+[Масалан](https://kun.uz/kr/37556328), Пискентда **ҳар бир одамни камбағалликдан чиқаришга 250 миллион сўм** кредит тўғри келяпти. Ваҳоланки, бошқа ҳудудда шунча пулга саноатда юқори даромадли доимий иш ўрни яратилмоқда.
+[Kun.uz расмий канали](https://t.me/kunuzofficial)</t>
+        </is>
+      </c>
+    </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>9.745604917619191</v>
       </c>
       <c r="R158" t="n">
-        <v>0.9957403204259418</v>
+        <v>0.9957346227474975</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -11754,15 +11754,15 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>@gazetauz</t>
+          <t>@uzdaily</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>64004</v>
+        <v>84272</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-09-04 04:55:17</t>
+          <t>2026-09-06 11:50:05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11788,29 +11788,97 @@
         <v>0.8</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="O159" t="n">
+        <v>333</v>
+      </c>
+      <c r="P159" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>5.846438775057724</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.9954108461075403</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>**Пятизвездочный Hadith Hotel открылся у комплекса Имама Бухари**
+В Самаркандской области открылся пятизвездочный Hadith Hotel на 120 номеров, построенный при участии индонезийских инвесторов.
+[Читать далее](https://www.uzdaily.uz/ru/piatizvezdochnyi-hadith-hotel-otkrylsia-u-kompleksa-imama-bukhari/)
+[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>@gazetauz</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>64004</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:55:17</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
           <t>neu</t>
         </is>
       </c>
-      <c r="N159" t="n">
+      <c r="N160" t="n">
         <v>0.7961</v>
       </c>
-      <c r="O159" t="n">
+      <c r="O160" t="n">
         <v>16908</v>
       </c>
-      <c r="P159" t="n">
+      <c r="P160" t="n">
         <v>31</v>
       </c>
-      <c r="Q159" t="n">
+      <c r="Q160" t="n">
         <v>9.739261284011265</v>
       </c>
-      <c r="R159" t="n">
-        <v>0.9950921706379281</v>
-      </c>
-      <c r="S159" t="inlineStr">
+      <c r="R160" t="n">
+        <v>0.9950864766682308</v>
+      </c>
+      <c r="S160" t="inlineStr">
         <is>
           <t>Между аэропортом Ургенча и Хивой запущено движение электропоезда. 
 Рейс пока выполняется раз в сутки: утром — в Хиву, вечером — обратно. Время в пути — чуть более 40 минут.
@@ -11820,66 +11888,66 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>@kunuzofficial</t>
         </is>
       </c>
-      <c r="B160" t="n">
+      <c r="B161" t="n">
         <v>173792</v>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>2026-09-03 05:02:23</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" t="n">
-        <v>1</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="n">
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="n">
         <v>0.8</v>
       </c>
-      <c r="L160" t="n">
+      <c r="L161" t="n">
         <v>0.6</v>
       </c>
-      <c r="M160" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="N160" t="n">
+      <c r="N161" t="n">
         <v>0.7961</v>
       </c>
-      <c r="O160" t="n">
+      <c r="O161" t="n">
         <v>247082</v>
       </c>
-      <c r="P160" t="n">
+      <c r="P161" t="n">
         <v>122</v>
       </c>
-      <c r="Q160" t="n">
+      <c r="Q161" t="n">
         <v>12.41846662668455</v>
       </c>
-      <c r="R160" t="n">
-        <v>0.9951504240292934</v>
-      </c>
-      <c r="S160" t="inlineStr">
+      <c r="R161" t="n">
+        <v>0.9951342465887844</v>
+      </c>
+      <c r="S161" t="inlineStr">
         <is>
           <t>**Давлат франшиза соҳасига молиявий ёрдам кўрсатмоқчи
 **
@@ -11890,74 +11958,6 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>@uzdaily</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>84272</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2026-09-06 11:50:05</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>business</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" t="n">
-        <v>1</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N161" t="n">
-        <v>0.796</v>
-      </c>
-      <c r="O161" t="n">
-        <v>332</v>
-      </c>
-      <c r="P161" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>5.84354441703136</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0.9949606668352082</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>**Пятизвездочный Hadith Hotel открылся у комплекса Имама Бухари**
-В Самаркандской области открылся пятизвездочный Hadith Hotel на 120 номеров, построенный при участии индонезийских инвесторов.
-[Читать далее](https://www.uzdaily.uz/ru/piatizvezdochnyi-hadith-hotel-otkrylsia-u-kompleksa-imama-bukhari/)
-[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
-        </is>
-      </c>
-    </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>9.736665259189097</v>
       </c>
       <c r="R162" t="n">
-        <v>0.9948269262934148</v>
+        <v>0.9948212338414597</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>8.375629627094451</v>
       </c>
       <c r="R163" t="n">
-        <v>0.9944087531983449</v>
+        <v>0.9944056615309188</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>8.373322820996535</v>
       </c>
       <c r="R164" t="n">
-        <v>0.9941348743047177</v>
+        <v>0.9941317834887952</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>8.371936178759098</v>
       </c>
       <c r="R165" t="n">
-        <v>0.9939702431975826</v>
+        <v>0.9939671528935066</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>9.724480496710003</v>
       </c>
       <c r="R166" t="n">
-        <v>0.9935819692694221</v>
+        <v>0.9935762839411765</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>8.368461137615839</v>
       </c>
       <c r="R167" t="n">
-        <v>0.9935576639068984</v>
+        <v>0.9935545748855522</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0.7948</v>
+        <v>0.7947</v>
       </c>
       <c r="O168" t="n">
         <v>333</v>
@@ -12434,7 +12434,7 @@
         <v>5.834810737062605</v>
       </c>
       <c r="R168" t="n">
-        <v>0.9934736125021717</v>
+        <v>0.9934310639555963</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>0.7948</v>
+        <v>0.7947</v>
       </c>
       <c r="O169" t="n">
         <v>331</v>
@@ -12502,7 +12502,7 @@
         <v>5.834810737062605</v>
       </c>
       <c r="R169" t="n">
-        <v>0.9934736125021717</v>
+        <v>0.9934310639555963</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -12516,20 +12516,20 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>@uzdaily</t>
+          <t>@spotuz</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>84173</v>
+        <v>39792</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-09-04 05:10:06</t>
+          <t>2026-09-02 15:40:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>labour_income</t>
+          <t>banking_finance</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -12550,7 +12550,7 @@
         <v>0.8</v>
       </c>
       <c r="L170" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -12558,89 +12558,21 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0.7936</v>
+        <v>0.7935</v>
       </c>
       <c r="O170" t="n">
-        <v>330</v>
+        <v>4192</v>
       </c>
       <c r="P170" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="Q170" t="n">
-        <v>5.82600010738045</v>
+        <v>8.354438940114811</v>
       </c>
       <c r="R170" t="n">
-        <v>0.9919734562000744</v>
+        <v>0.9918897743627331</v>
       </c>
       <c r="S170" t="inlineStr">
-        <is>
-          <t>**Узбекистан и ЮНИСЕФ обсудили стратегию социальной защиты**
-В Узбекистане при участии ЮНИСЕФ и Всемирного банка разрабатывается стратегия адаптивной социальной защиты с учётом различных рисков.
-[Читать далее](https://www.uzdaily.uz/ru/uzbekistan-i-iunisef-obsudili-strategiiu-sotsialnoi-zashchity/)
-[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>@spotuz</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>39792</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2026-09-02 15:40:00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>banking_finance</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L171" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N171" t="n">
-        <v>0.7935</v>
-      </c>
-      <c r="O171" t="n">
-        <v>4192</v>
-      </c>
-      <c r="P171" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>8.354438940114811</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0.9918928582081135</v>
-      </c>
-      <c r="S171" t="inlineStr">
         <is>
           <t>**Индийскую платежную систему UPI могут запустить в Узбекистане в течение года**
 В Узбекистане в течение года ожидается запуск платежей через индийскую систему UPI. Это станет возможным после реализации соглашения между HUMO и NIPL — международным подразделением Национальной платежной корпорацией Индии (NPCI), развивающей UPI. После его запуска индийские туристы смогут использовать в Узбекистане приложения с поддержкой UPI для проведения платежей.
@@ -12650,6 +12582,74 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>@uzdaily</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>84173</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-09-04 05:10:06</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>labour_income</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="O171" t="n">
+        <v>330</v>
+      </c>
+      <c r="P171" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>5.82600010738045</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.9919309719022819</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>**Узбекистан и ЮНИСЕФ обсудили стратегию социальной защиты**
+В Узбекистане при участии ЮНИСЕФ и Всемирного банка разрабатывается стратегия адаптивной социальной защиты с учётом различных рисков.
+[Читать далее](https://www.uzdaily.uz/ru/uzbekistan-i-iunisef-obsudili-strategiiu-sotsialnoi-zashchity/)
+[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
+        </is>
+      </c>
+    </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>12.37646921478577</v>
       </c>
       <c r="R172" t="n">
-        <v>0.9917849729220364</v>
+        <v>0.9917688501912313</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7927</v>
       </c>
       <c r="O173" t="n">
         <v>328</v>
@@ -12776,7 +12776,7 @@
         <v>5.820082930352362</v>
       </c>
       <c r="R173" t="n">
-        <v>0.9909659583560451</v>
+        <v>0.9909235172074297</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>9.695109453422392</v>
       </c>
       <c r="R174" t="n">
-        <v>0.9905810337398506</v>
+        <v>0.9905753655831159</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>8.336150816120663</v>
       </c>
       <c r="R175" t="n">
-        <v>0.9897215742104869</v>
+        <v>0.9897184971157389</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>9.682840881420505</v>
       </c>
       <c r="R176" t="n">
-        <v>0.9893275136228755</v>
+        <v>0.9893218526388488</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>8.326758814511733</v>
       </c>
       <c r="R177" t="n">
-        <v>0.9886064952223043</v>
+        <v>0.9886034215943936</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>8.314342343369789</v>
       </c>
       <c r="R178" t="n">
-        <v>0.9871323317101736</v>
+        <v>0.9871292626655124</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>5.793013608384144</v>
       </c>
       <c r="R179" t="n">
-        <v>0.9863569558886767</v>
+        <v>0.9863147121346912</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>5.765191102784844</v>
       </c>
       <c r="R180" t="n">
-        <v>0.98161971137601</v>
+        <v>0.9815776705090125</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0.7849</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="O181" t="n">
         <v>309</v>
@@ -13326,7 +13326,7 @@
         <v>5.762051382780177</v>
       </c>
       <c r="R181" t="n">
-        <v>0.9810851218038977</v>
+        <v>0.981043103832334</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>8.244334047856094</v>
       </c>
       <c r="R182" t="n">
-        <v>0.9788204954716048</v>
+        <v>0.9788174522688654</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>8.238536930171769</v>
       </c>
       <c r="R183" t="n">
-        <v>0.9781322242818227</v>
+        <v>0.9781291832189535</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -13519,19 +13519,19 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0.7823</v>
+        <v>0.7824</v>
       </c>
       <c r="O184" t="n">
-        <v>60492</v>
+        <v>60585</v>
       </c>
       <c r="P184" t="n">
         <v>4</v>
       </c>
       <c r="Q184" t="n">
-        <v>11.01041517280795</v>
+        <v>11.01195115725461</v>
       </c>
       <c r="R184" t="n">
-        <v>0.977833889670207</v>
+        <v>0.9779516324138522</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0.7823</v>
+        <v>0.7822</v>
       </c>
       <c r="O185" t="n">
         <v>301</v>
@@ -13599,7 +13599,7 @@
         <v>5.743003187809482</v>
       </c>
       <c r="R185" t="n">
-        <v>0.9778418496701544</v>
+        <v>0.9777999706016413</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0.7823</v>
+        <v>0.7822</v>
       </c>
       <c r="O186" t="n">
         <v>309</v>
@@ -13667,7 +13667,7 @@
         <v>5.743003187809482</v>
       </c>
       <c r="R186" t="n">
-        <v>0.9778418496701544</v>
+        <v>0.9777999706016413</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -13723,19 +13723,19 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>0.7816</v>
+        <v>0.7817</v>
       </c>
       <c r="O187" t="n">
-        <v>59853</v>
+        <v>59948</v>
       </c>
       <c r="P187" t="n">
         <v>49</v>
       </c>
       <c r="Q187" t="n">
-        <v>11.00129952103347</v>
+        <v>11.00288286789214</v>
       </c>
       <c r="R187" t="n">
-        <v>0.9770243295317723</v>
+        <v>0.9771462938994885</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>5.736572297479192</v>
       </c>
       <c r="R188" t="n">
-        <v>0.9767468835888287</v>
+        <v>0.9767050514155875</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>5.736572297479192</v>
       </c>
       <c r="R189" t="n">
-        <v>0.9767468835888287</v>
+        <v>0.9767050514155875</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>5.697093486505405</v>
       </c>
       <c r="R190" t="n">
-        <v>0.9700249591386855</v>
+        <v>0.9699834148524219</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>8.346879253746559</v>
       </c>
       <c r="R191" t="n">
-        <v>0.9909953234995937</v>
+        <v>0.9909922424446944</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>6.09807428216624</v>
       </c>
       <c r="R192" t="n">
-        <v>1.038298611457649</v>
+        <v>1.03825414314337</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>6.054439346269371</v>
       </c>
       <c r="R193" t="n">
-        <v>1.030869037586228</v>
+        <v>1.030824887466178</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>6.052089168924417</v>
       </c>
       <c r="R194" t="n">
-        <v>1.030468880789011</v>
+        <v>1.0304247478069</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7161</v>
       </c>
       <c r="O195" t="n">
         <v>398</v>
@@ -14278,7 +14278,7 @@
         <v>6.008813185442595</v>
       </c>
       <c r="R195" t="n">
-        <v>1.023100424538806</v>
+        <v>1.023056607133374</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>5.971261839790462</v>
       </c>
       <c r="R196" t="n">
-        <v>1.016706683130473</v>
+        <v>1.016663139556577</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>9.941409345534685</v>
       </c>
       <c r="R197" t="n">
-        <v>1.015746299063646</v>
+        <v>1.01574048690994</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -14472,19 +14472,19 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>0.7099</v>
+        <v>0.7101</v>
       </c>
       <c r="O198" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P198" t="n">
         <v>2</v>
       </c>
       <c r="Q198" t="n">
-        <v>5.955837369464831</v>
+        <v>5.958424693029782</v>
       </c>
       <c r="R198" t="n">
-        <v>1.014080410412149</v>
+        <v>1.014477495336172</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0.7071</v>
+        <v>0.707</v>
       </c>
       <c r="O199" t="n">
         <v>86926</v>
@@ -14552,7 +14552,7 @@
         <v>11.37358293462954</v>
       </c>
       <c r="R199" t="n">
-        <v>1.010086782914583</v>
+        <v>1.010067501978307</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>9.872925246953487</v>
       </c>
       <c r="R200" t="n">
-        <v>1.008749054783608</v>
+        <v>1.008743282668501</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>11.35551113188237</v>
       </c>
       <c r="R201" t="n">
-        <v>1.008481827888249</v>
+        <v>1.00846257758799</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>8.48714627006394</v>
       </c>
       <c r="R202" t="n">
-        <v>1.007648728081836</v>
+        <v>1.007645595250654</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>5.916202062607435</v>
       </c>
       <c r="R203" t="n">
-        <v>1.00733183993391</v>
+        <v>1.007288697866352</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>8.472195825485501</v>
       </c>
       <c r="R204" t="n">
-        <v>1.005873714904927</v>
+        <v>1.005870587592351</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>8.460199469896118</v>
       </c>
       <c r="R205" t="n">
-        <v>1.004449430219991</v>
+        <v>1.004446307335589</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>8.448700194970938</v>
       </c>
       <c r="R206" t="n">
-        <v>1.003084162156556</v>
+        <v>1.003081043516842</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>11.29181734076809</v>
       </c>
       <c r="R207" t="n">
-        <v>1.002825188557614</v>
+        <v>1.002806046233526</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>5.883322388488279</v>
       </c>
       <c r="R208" t="n">
-        <v>1.00173352833529</v>
+        <v>1.001690626032551</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>11.27820263178224</v>
       </c>
       <c r="R209" t="n">
-        <v>1.001616067590293</v>
+        <v>1.001596948346384</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>11.27659535185184</v>
       </c>
       <c r="R210" t="n">
-        <v>1.001473325217597</v>
+        <v>1.001454208698411</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>11.27418592603146</v>
       </c>
       <c r="R211" t="n">
-        <v>1.001259344347227</v>
+        <v>1.001240231912592</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>12.48941531638286</v>
       </c>
       <c r="R212" t="n">
-        <v>1.000835877858664</v>
+        <v>1.000819607993845</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>11.26770244632564</v>
       </c>
       <c r="R213" t="n">
-        <v>1.000683547151586</v>
+        <v>1.000664445707996</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>11.253455009396</v>
       </c>
       <c r="R214" t="n">
-        <v>0.9994182336777453</v>
+        <v>0.9993991563869596</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>11.24714838346204</v>
       </c>
       <c r="R215" t="n">
-        <v>0.9988581428482067</v>
+        <v>0.9988390762486565</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0.6989</v>
+        <v>0.6988</v>
       </c>
       <c r="O216" t="n">
         <v>347</v>
@@ -15716,7 +15716,7 @@
         <v>5.863631175598097</v>
       </c>
       <c r="R216" t="n">
-        <v>0.9983807717016775</v>
+        <v>0.998338012990998</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -15730,20 +15730,20 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>@daryo</t>
+          <t>@uzdaily</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>136285</v>
+        <v>84274</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-09-03 07:42:29</t>
+          <t>2026-09-06 12:20:05</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>labour_income</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -15772,21 +15772,89 @@
         </is>
       </c>
       <c r="N217" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="O217" t="n">
+        <v>347</v>
+      </c>
+      <c r="P217" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>5.863631175598097</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.998338012990998</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>**В Наманганской области рассчитывают собрать 254,5 тыс. тонн хлопка**
+В Наманганской области хлопчатник посеяли на 48,8 тыс. га. В уборочной кампании задействуют 178 машин, включая 57 новых агрегатов.
+[Читать далее](https://www.uzdaily.uz/ru/v-namanganskoi-oblasti-rasschityvaiut-sobrat-2545-tys-tonn-khlopka/)
+[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>@daryo</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>136285</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-09-03 07:42:29</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>labour_income</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
         <v>0.6987</v>
       </c>
-      <c r="O217" t="n">
+      <c r="O218" t="n">
         <v>76031</v>
       </c>
-      <c r="P217" t="n">
+      <c r="P218" t="n">
         <v>34</v>
       </c>
-      <c r="Q217" t="n">
+      <c r="Q218" t="n">
         <v>11.23980354384978</v>
       </c>
-      <c r="R217" t="n">
-        <v>0.998205848363908</v>
-      </c>
-      <c r="S217" t="inlineStr">
+      <c r="R218" t="n">
+        <v>0.998186794215613</v>
+      </c>
+      <c r="S218" t="inlineStr">
         <is>
           <t>**Hokimlar endi haftada 3 kun kambag‘allik va bandlik masalalari bilan shug‘ullanadi**
 O‘zbekistonda kambag‘allik bilan ishlash bo‘yicha mutlaqo yangi tizim joriy qilinishi belgilandi.
@@ -15795,66 +15863,66 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>@daryo</t>
         </is>
       </c>
-      <c r="B218" t="n">
+      <c r="B219" t="n">
         <v>136318</v>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>2026-09-04 04:43:44</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>energy_utility</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="n">
-        <v>1</v>
-      </c>
-      <c r="G218" t="n">
-        <v>1</v>
-      </c>
-      <c r="H218" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="n">
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="n">
         <v>0.7</v>
       </c>
-      <c r="L218" t="n">
+      <c r="L219" t="n">
         <v>0.5</v>
       </c>
-      <c r="M218" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="N218" t="n">
+      <c r="N219" t="n">
         <v>0.6984</v>
       </c>
-      <c r="O218" t="n">
+      <c r="O219" t="n">
         <v>75716</v>
       </c>
-      <c r="P218" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q218" t="n">
+      <c r="P219" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q219" t="n">
         <v>11.2347843986856</v>
       </c>
-      <c r="R218" t="n">
-        <v>0.9977600985750331</v>
-      </c>
-      <c r="S218" t="inlineStr">
+      <c r="R219" t="n">
+        <v>0.9977410529353864</v>
+      </c>
+      <c r="S219" t="inlineStr">
         <is>
           <t>**O‘zbekiston CIGRE 2026 da taqdim etildi: NURA Group mamlakatning global energetika hamjamiyatidagi ishtirokini qo‘llab-quvvatladi**
 Batafsil — [https://daryo.uz/NURA Group](https://daryo.uz/2026/09/03/ozbekiston-cigre-2026-da-taqdim-etildi-nura-group-mamlakatning-global-energetika-hamjamiyatidagi-ishtirokini-qollab-quvvatladi)
@@ -15862,66 +15930,66 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>@kunuzofficial</t>
         </is>
       </c>
-      <c r="B219" t="n">
+      <c r="B220" t="n">
         <v>173767</v>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>2026-09-02 10:10:31</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>banking_finance</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="n">
-        <v>1</v>
-      </c>
-      <c r="G219" t="n">
-        <v>1</v>
-      </c>
-      <c r="H219" t="n">
-        <v>0</v>
-      </c>
-      <c r="I219" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="n">
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="n">
         <v>0.7</v>
       </c>
-      <c r="L219" t="n">
+      <c r="L220" t="n">
         <v>0.3</v>
       </c>
-      <c r="M219" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="N219" t="n">
+      <c r="N220" t="n">
         <v>0.6984</v>
       </c>
-      <c r="O219" t="n">
+      <c r="O220" t="n">
         <v>254740</v>
       </c>
-      <c r="P219" t="n">
+      <c r="P220" t="n">
         <v>314</v>
       </c>
-      <c r="Q219" t="n">
+      <c r="Q220" t="n">
         <v>12.45046483698342</v>
       </c>
-      <c r="R219" t="n">
-        <v>0.9977145918532555</v>
-      </c>
-      <c r="S219" t="inlineStr">
+      <c r="R220" t="n">
+        <v>0.9976983727289251</v>
+      </c>
+      <c r="S220" t="inlineStr">
         <is>
           <t>**10 минг долларгача нақд валютани декларациясиз олиб чиқиш мумкин бўлади
 **
@@ -15932,74 +16000,6 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>@uzdaily</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>84274</v>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>2026-09-06 12:20:05</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>macro</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="n">
-        <v>1</v>
-      </c>
-      <c r="G220" t="n">
-        <v>1</v>
-      </c>
-      <c r="H220" t="n">
-        <v>0</v>
-      </c>
-      <c r="I220" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L220" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>pos</t>
-        </is>
-      </c>
-      <c r="N220" t="n">
-        <v>0.6982</v>
-      </c>
-      <c r="O220" t="n">
-        <v>345</v>
-      </c>
-      <c r="P220" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q220" t="n">
-        <v>5.857933154483459</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0.9974105887984146</v>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>**В Наманганской области рассчитывают собрать 254,5 тыс. тонн хлопка**
-В Наманганской области хлопчатник посеяли на 48,8 тыс. га. В уборочной кампании задействуют 178 машин, включая 57 новых агрегатов.
-[Читать далее](https://www.uzdaily.uz/ru/v-namanganskoi-oblasti-rasschityvaiut-sobrat-2545-tys-tonn-khlopka/)
-[English](https://t.me/UZDAILYNEWSEN) | [O'zbek tilida](https://t.me/uzdailyuzblot) | [Ўзбек тилида](https://t.me/uzdailynewsuz) | [На русском](https://t.me/UZDAILY) | [iOS](https://apps.apple.com/uz/app/uzdaily/id6523431145) |[Android](https://play.google.com/store/apps/details?id=v1.uzdaily.uz&amp;hl=en&amp;pli=1)</t>
-        </is>
-      </c>
-    </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>12.43386139120411</v>
       </c>
       <c r="R221" t="n">
-        <v>0.9963840792703155</v>
+        <v>0.9963678817751657</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>12.43207610341025</v>
       </c>
       <c r="R222" t="n">
-        <v>0.9962410157216117</v>
+        <v>0.9962248205521426</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>9.743670851082243</v>
       </c>
       <c r="R223" t="n">
-        <v>0.995542710523888</v>
+        <v>0.9955370139761779</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>12.40937260870932</v>
       </c>
       <c r="R224" t="n">
-        <v>0.9944216773880022</v>
+        <v>0.9944055117942001</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>5.834810737062605</v>
       </c>
       <c r="R225" t="n">
-        <v>0.9934736125021717</v>
+        <v>0.9934310639555963</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>9.679343500888335</v>
       </c>
       <c r="R226" t="n">
-        <v>0.9889701748182357</v>
+        <v>0.9889645158789202</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>9.675268643355135</v>
       </c>
       <c r="R227" t="n">
-        <v>0.9885538333001773</v>
+        <v>0.98854817674319</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0.6912</v>
+        <v>0.6911</v>
       </c>
       <c r="O228" t="n">
         <v>325</v>
@@ -16539,7 +16539,7 @@
         <v>5.799092654460526</v>
       </c>
       <c r="R228" t="n">
-        <v>0.9873920146314921</v>
+        <v>0.9873497265479496</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>5.780743515792329</v>
       </c>
       <c r="R229" t="n">
-        <v>0.9842677684647392</v>
+        <v>0.9842256141865962</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>5.780743515792329</v>
       </c>
       <c r="R230" t="n">
-        <v>0.9842677684647392</v>
+        <v>0.9842256141865962</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>5.768320995793772</v>
       </c>
       <c r="R231" t="n">
-        <v>0.9821526277385877</v>
+        <v>0.9821105640478167</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>5.765191102784844</v>
       </c>
       <c r="R232" t="n">
-        <v>0.98161971137601</v>
+        <v>0.9815776705090125</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>5.75890177387728</v>
       </c>
       <c r="R233" t="n">
-        <v>0.980548848482322</v>
+        <v>0.9805068534783039</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6829</v>
       </c>
       <c r="O234" t="n">
         <v>301</v>
@@ -16944,10 +16944,10 @@
         <v>3</v>
       </c>
       <c r="Q234" t="n">
-        <v>5.730099782973574</v>
+        <v>5.730099782973575</v>
       </c>
       <c r="R234" t="n">
-        <v>0.9756448302990751</v>
+        <v>0.9756030453246376</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>0.6822</v>
+        <v>0.6821</v>
       </c>
       <c r="O235" t="n">
         <v>299</v>
@@ -17015,7 +17015,7 @@
         <v>5.723585101952381</v>
       </c>
       <c r="R235" t="n">
-        <v>0.9745355974584428</v>
+        <v>0.9744938599902947</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>5.713732805509369</v>
       </c>
       <c r="R236" t="n">
-        <v>0.9728580800581768</v>
+        <v>0.972816414434843</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>5.978885764901122</v>
       </c>
       <c r="R237" t="n">
-        <v>1.018004783233879</v>
+        <v>1.017961184064874</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>5.955837369464831</v>
       </c>
       <c r="R238" t="n">
-        <v>1.014080410412149</v>
+        <v>1.014036979316415</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>5.945420608606575</v>
       </c>
       <c r="R239" t="n">
-        <v>1.012306783553151</v>
+        <v>1.012263428418413</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>9.899630122208823</v>
       </c>
       <c r="R240" t="n">
-        <v>1.011477579207536</v>
+        <v>1.01147179147967</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -17412,19 +17412,19 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0.6055</v>
+        <v>0.6057</v>
       </c>
       <c r="O241" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P241" t="n">
         <v>4</v>
       </c>
       <c r="Q241" t="n">
-        <v>5.926926025970411</v>
+        <v>5.929589143389895</v>
       </c>
       <c r="R241" t="n">
-        <v>1.009157773130831</v>
+        <v>1.009567973494009</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>5.91350300563827</v>
       </c>
       <c r="R242" t="n">
-        <v>1.006872280575716</v>
+        <v>1.006829158190193</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>11.32266044222196</v>
       </c>
       <c r="R243" t="n">
-        <v>1.005564361367248</v>
+        <v>1.005545166756744</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>12.5369183686841</v>
       </c>
       <c r="R244" t="n">
-        <v>1.004642521952604</v>
+        <v>1.004626190205926</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>11.31033181069621</v>
       </c>
       <c r="R245" t="n">
-        <v>1.004469456812794</v>
+        <v>1.004450283102262</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>8.451267041300071</v>
       </c>
       <c r="R246" t="n">
-        <v>1.003388914703104</v>
+        <v>1.003385795115899</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>8.449342524508063</v>
       </c>
       <c r="R247" t="n">
-        <v>1.003160423660776</v>
+        <v>1.003157304783961</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>11.29222891729907</v>
       </c>
       <c r="R248" t="n">
-        <v>1.002861740628892</v>
+        <v>1.002842597607082</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0.6001</v>
+        <v>0.6</v>
       </c>
       <c r="O249" t="n">
         <v>77636</v>
@@ -17972,7 +17972,7 @@
         <v>11.26113806771427</v>
       </c>
       <c r="R249" t="n">
-        <v>1.000100565332093</v>
+        <v>1.00008147501669</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>5.869296913133774</v>
       </c>
       <c r="R250" t="n">
-        <v>0.9993454577884608</v>
+        <v>0.9993026577621487</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>12.46511215836191</v>
       </c>
       <c r="R251" t="n">
-        <v>0.998888350942754</v>
+        <v>0.9988721127374713</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>12.43208009197901</v>
       </c>
       <c r="R252" t="n">
-        <v>0.9962413353444778</v>
+        <v>0.9962251401698127</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>12.43206014897611</v>
       </c>
       <c r="R253" t="n">
-        <v>0.9962397372173992</v>
+        <v>0.9962235420687137</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>12.4249229942243</v>
       </c>
       <c r="R254" t="n">
-        <v>0.9956678032748967</v>
+        <v>0.9956516174237275</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5972</v>
       </c>
       <c r="O255" t="n">
         <v>339</v>
@@ -18388,10 +18388,10 @@
         <v>3</v>
       </c>
       <c r="Q255" t="n">
-        <v>5.846438775057725</v>
+        <v>5.846438775057724</v>
       </c>
       <c r="R255" t="n">
-        <v>0.9954534794479742</v>
+        <v>0.9954108461075403</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>8.36730010184162</v>
       </c>
       <c r="R256" t="n">
-        <v>0.993419818253728</v>
+        <v>0.9934167296609511</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>5.834810737062605</v>
       </c>
       <c r="R257" t="n">
-        <v>0.9934736125021717</v>
+        <v>0.9934310639555963</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>5.777652323222656</v>
       </c>
       <c r="R258" t="n">
-        <v>0.9837414414958753</v>
+        <v>0.9836993097592949</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>5.771441123130016</v>
       </c>
       <c r="R259" t="n">
-        <v>0.9826838813329014</v>
+        <v>0.9826417948895702</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0.5851</v>
+        <v>0.585</v>
       </c>
       <c r="O260" t="n">
         <v>300</v>
@@ -18730,7 +18730,7 @@
         <v>5.726847747587197</v>
       </c>
       <c r="R260" t="n">
-        <v>0.9750911171644284</v>
+        <v>0.9750493559044495</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>5.703782474656201</v>
       </c>
       <c r="R261" t="n">
-        <v>0.9711638706684023</v>
+        <v>0.9711222776047683</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -18854,19 +18854,19 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>0.5092</v>
+        <v>0.5094</v>
       </c>
       <c r="O262" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P262" t="n">
         <v>1</v>
       </c>
       <c r="Q262" t="n">
-        <v>5.981414211254481</v>
+        <v>5.983936280687191</v>
       </c>
       <c r="R262" t="n">
-        <v>1.018435293295968</v>
+        <v>1.018821081582888</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>5.888877958332881</v>
       </c>
       <c r="R263" t="n">
-        <v>1.002679456539604</v>
+        <v>1.002636513724597</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>12.45007317008327</v>
       </c>
       <c r="R264" t="n">
-        <v>0.9976832057334167</v>
+        <v>0.9976669871193078</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>9.873079890114703</v>
       </c>
       <c r="R265" t="n">
-        <v>1.008764855181038</v>
+        <v>1.008759082975522</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>11.31123758568531</v>
       </c>
       <c r="R266" t="n">
-        <v>1.004549898600579</v>
+        <v>1.004530723354543</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>8.447628728030327</v>
       </c>
       <c r="R267" t="n">
-        <v>1.002956950692828</v>
+        <v>1.002953832448621</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0.898</v>
+        <v>0.8979</v>
       </c>
       <c r="O268" t="n">
         <v>254500</v>
@@ -19282,7 +19282,7 @@
         <v>12.45072325312881</v>
       </c>
       <c r="R268" t="n">
-        <v>0.9977352999603349</v>
+        <v>0.997719080499368</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>8.37309184744198</v>
       </c>
       <c r="R269" t="n">
-        <v>0.994107451635064</v>
+        <v>0.9941043609043998</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>8.336150816120663</v>
       </c>
       <c r="R270" t="n">
-        <v>0.9897215742104869</v>
+        <v>0.9897184971157389</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>9.683277195199359</v>
       </c>
       <c r="R271" t="n">
-        <v>0.9893720932283115</v>
+        <v>0.9893664319891978</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>9.90028242158718</v>
       </c>
       <c r="R272" t="n">
-        <v>1.011544226767899</v>
+        <v>1.011538438658672</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>9.821897815496174</v>
       </c>
       <c r="R273" t="n">
-        <v>1.003535415263093</v>
+        <v>1.003529672980707</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>8.442469645220301</v>
       </c>
       <c r="R274" t="n">
-        <v>1.002344431117205</v>
+        <v>1.002341314777352</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>9.809671256331843</v>
       </c>
       <c r="R275" t="n">
-        <v>1.002286187735104</v>
+        <v>1.002280452600863</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>8.432506383249043</v>
       </c>
       <c r="R276" t="n">
-        <v>1.001161528415469</v>
+        <v>1.001158415753321</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>9.796347676978224</v>
       </c>
       <c r="R277" t="n">
-        <v>1.00092487406736</v>
+        <v>1.000919146722627</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>11.26748517865741</v>
       </c>
       <c r="R278" t="n">
-        <v>1.000664251631318</v>
+        <v>1.000645150556049</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>11.26707607612038</v>
       </c>
       <c r="R279" t="n">
-        <v>1.000627919275201</v>
+        <v>1.000608818893458</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>11.25820094320982</v>
       </c>
       <c r="R280" t="n">
-        <v>0.999839719593439</v>
+        <v>0.9998206342571634</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>12.44895607707397</v>
       </c>
       <c r="R281" t="n">
-        <v>0.9975936877908795</v>
+        <v>0.9975774706319991</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>9.747710550964285</v>
       </c>
       <c r="R282" t="n">
-        <v>0.9959554598697699</v>
+        <v>0.9959497609602862</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>8.370779172960701</v>
       </c>
       <c r="R283" t="n">
-        <v>0.9938328760091261</v>
+        <v>0.9938297861321316</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>9.670987868797893</v>
       </c>
       <c r="R284" t="n">
-        <v>0.988116452566469</v>
+        <v>0.9881107985121972</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>9.790934566296798</v>
       </c>
       <c r="R285" t="n">
-        <v>1.000371798849352</v>
+        <v>1.000366074669345</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>9.787515376283707</v>
       </c>
       <c r="R286" t="n">
-        <v>1.000022449025713</v>
+        <v>1.000016726844703</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>11.23223224681601</v>
       </c>
       <c r="R287" t="n">
-        <v>0.9975334422182556</v>
+        <v>0.9975144009051152</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>8.323365694436081</v>
       </c>
       <c r="R288" t="n">
-        <v>0.9882036421289719</v>
+        <v>0.988200569753552</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>9.831078137017988</v>
       </c>
       <c r="R289" t="n">
-        <v>1.004473398730617</v>
+        <v>1.00446765108104</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -20754,11 +20754,11 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>136275</v>
+        <v>136277</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-09-03 04:01:57</t>
+          <t>2026-09-03 04:43:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -20795,18 +20795,85 @@
         <v>0.5999</v>
       </c>
       <c r="O290" t="n">
+        <v>77459</v>
+      </c>
+      <c r="P290" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>11.25777511752093</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0.9997828174414491</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>**Texnologiyalar, startaplar va yangi imkoniyatlar uch kunligi: Toshkentdagi FINOBOD 2026 ishtirokchilarini nimalar kutmoqda?**
+Batafsil — [https://daryo.uz/FINOBOD](https://daryo.uz/2026/09/03/texnologiyalar-startaplar-va-yangi-imkoniyatlar-uch-kunligi-toshkentdagi-finobod-2026-ishtirokchilarini-nimalar-kutmoqda)
+Reklama</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>@daryo</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>136275</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:01:57</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>1</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="O291" t="n">
         <v>77412</v>
       </c>
-      <c r="P290" t="n">
+      <c r="P291" t="n">
         <v>11</v>
       </c>
-      <c r="Q290" t="n">
+      <c r="Q291" t="n">
         <v>11.25719415375027</v>
       </c>
-      <c r="R290" t="n">
-        <v>0.9997503067204591</v>
-      </c>
-      <c r="S290" t="inlineStr">
+      <c r="R291" t="n">
+        <v>0.9997312230909318</v>
+      </c>
+      <c r="S291" t="inlineStr">
         <is>
           <t>**CAITME ko’rgazmasida to‘qimachilik va tikuvchilik uchun texnologiyalarni toping!**
 Yangi uskuna tanlayapsizmi yoki korxonangizni modernizatsiya qilmoqchimisiz? 17-Xalqaro CAITME 2026 ko‘rgazmasida zamonaviy uskunalarni ish jarayonida ko‘ring, texnologiyalarni taqqoslang, ishlab chiqaruvchilar va mutaxassislar bilan muloqot qiling va oʻz korxonangiz uchun mos yechimlarni tanlang.
@@ -20816,73 +20883,6 @@
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>@daryo</t>
-        </is>
-      </c>
-      <c r="B291" t="n">
-        <v>136277</v>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>2026-09-03 04:43:00</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>business</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="n">
-        <v>1</v>
-      </c>
-      <c r="G291" t="n">
-        <v>0</v>
-      </c>
-      <c r="H291" t="n">
-        <v>1</v>
-      </c>
-      <c r="I291" t="n">
-        <v>0</v>
-      </c>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L291" t="n">
-        <v>0</v>
-      </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>neu</t>
-        </is>
-      </c>
-      <c r="N291" t="n">
-        <v>0.5999</v>
-      </c>
-      <c r="O291" t="n">
-        <v>77459</v>
-      </c>
-      <c r="P291" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q291" t="n">
-        <v>11.25777511752093</v>
-      </c>
-      <c r="R291" t="n">
-        <v>0.9998019020558486</v>
-      </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>**Texnologiyalar, startaplar va yangi imkoniyatlar uch kunligi: Toshkentdagi FINOBOD 2026 ishtirokchilarini nimalar kutmoqda?**
-Batafsil — [https://daryo.uz/FINOBOD](https://daryo.uz/2026/09/03/texnologiyalar-startaplar-va-yangi-imkoniyatlar-uch-kunligi-toshkentdagi-finobod-2026-ishtirokchilarini-nimalar-kutmoqda)
-Reklama</t>
-        </is>
-      </c>
-    </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>9.775654181026242</v>
       </c>
       <c r="R292" t="n">
-        <v>0.9988105519227477</v>
+        <v>0.9988048366762774</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>11.2450068033594</v>
       </c>
       <c r="R293" t="n">
-        <v>0.9986679493297117</v>
+        <v>0.9986488863606505</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>9.772695262286105</v>
       </c>
       <c r="R294" t="n">
-        <v>0.9985082295200519</v>
+        <v>0.9985025160034862</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>9.663769906600864</v>
       </c>
       <c r="R295" t="n">
-        <v>0.9873789697676436</v>
+        <v>0.9873733199332871</v>
       </c>
       <c r="S295" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>11.32266044222196</v>
       </c>
       <c r="R296" t="n">
-        <v>1.005564361367248</v>
+        <v>1.005545166756744</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>11.34268266539147</v>
       </c>
       <c r="R297" t="n">
-        <v>1.007342533039651</v>
+        <v>1.007323304486703</v>
       </c>
       <c r="S297" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>11.30361085159246</v>
       </c>
       <c r="R298" t="n">
-        <v>1.003872569095157</v>
+        <v>1.003853406778254</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>11.34023735714451</v>
       </c>
       <c r="R299" t="n">
-        <v>1.007125365454502</v>
+        <v>1.007106141046935</v>
       </c>
       <c r="S299" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>11.30623334372283</v>
       </c>
       <c r="R300" t="n">
-        <v>1.004105472363583</v>
+        <v>1.00408630560093</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>11.30129043583889</v>
       </c>
       <c r="R301" t="n">
-        <v>1.003666493200075</v>
+        <v>1.00364733481683</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>11.30801468191708</v>
       </c>
       <c r="R302" t="n">
-        <v>1.004263672833589</v>
+        <v>1.004244503051143</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>11.30463357965445</v>
       </c>
       <c r="R303" t="n">
-        <v>1.003963397473854</v>
+        <v>1.003944233423183</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>11.3095845409522</v>
       </c>
       <c r="R304" t="n">
-        <v>1.004403091860251</v>
+        <v>1.00438391941652</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>11.31476716634993</v>
       </c>
       <c r="R305" t="n">
-        <v>1.004863360312606</v>
+        <v>1.004844179083088</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>11.31315658497247</v>
       </c>
       <c r="R306" t="n">
-        <v>1.004720324738721</v>
+        <v>1.004701146239523</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>11.31531563582916</v>
       </c>
       <c r="R307" t="n">
-        <v>1.004912069833167</v>
+        <v>1.004892887673862</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>11.2961242583996</v>
       </c>
       <c r="R308" t="n">
-        <v>1.003207685489293</v>
+        <v>1.003188535863952</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>11.32365179816363</v>
       </c>
       <c r="R309" t="n">
-        <v>1.005652403591023</v>
+        <v>1.005633207299934</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>11.30839510836744</v>
       </c>
       <c r="R310" t="n">
-        <v>1.004297458469267</v>
+        <v>1.004278288041907</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>11.27096854688026</v>
       </c>
       <c r="R311" t="n">
-        <v>1.000973609220932</v>
+        <v>1.000954502240522</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>11.31941352878062</v>
       </c>
       <c r="R312" t="n">
-        <v>1.005276003303548</v>
+        <v>1.005256814197337</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>11.32599329561859</v>
       </c>
       <c r="R313" t="n">
-        <v>1.005860351749934</v>
+        <v>1.005841151489449</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>11.32200706095075</v>
       </c>
       <c r="R314" t="n">
-        <v>1.00550633464075</v>
+        <v>1.005487141137884</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>11.30142635325073</v>
       </c>
       <c r="R315" t="n">
-        <v>1.003678564012066</v>
+        <v>1.003659405398409</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>11.30660215688627</v>
       </c>
       <c r="R316" t="n">
-        <v>1.00413822662439</v>
+        <v>1.004119059236511</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>11.3006600318032</v>
       </c>
       <c r="R317" t="n">
-        <v>1.003610507079606</v>
+        <v>1.003591349765046</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>11.29484407924828</v>
       </c>
       <c r="R318" t="n">
-        <v>1.003093992904649</v>
+        <v>1.003074845449516</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>11.32689704624495</v>
       </c>
       <c r="R319" t="n">
-        <v>1.005940613754263</v>
+        <v>1.005921411961705</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>11.28455578118442</v>
       </c>
       <c r="R320" t="n">
-        <v>1.002180290164473</v>
+        <v>1.002161160150459</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>11.28190094020514</v>
       </c>
       <c r="R321" t="n">
-        <v>1.001944513997954</v>
+        <v>1.00192538848453</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>11.28766717918045</v>
       </c>
       <c r="R322" t="n">
-        <v>1.00245661311479</v>
+        <v>1.002437477826215</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>11.27459213081503</v>
       </c>
       <c r="R323" t="n">
-        <v>1.001295419354144</v>
+        <v>1.001276306230895</v>
       </c>
       <c r="S323" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>11.26776633959834</v>
       </c>
       <c r="R324" t="n">
-        <v>1.000689221506857</v>
+        <v>1.000670119954953</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>11.22270684486645</v>
       </c>
       <c r="R325" t="n">
-        <v>0.9966874922070327</v>
+        <v>0.9966684670417209</v>
       </c>
       <c r="S325" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>11.22031124947289</v>
       </c>
       <c r="R326" t="n">
-        <v>0.996474739615509</v>
+        <v>0.9964557185113029</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>11.23240435815923</v>
       </c>
       <c r="R327" t="n">
-        <v>0.9975487274097367</v>
+        <v>0.9975296858048265</v>
       </c>
       <c r="S327" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>11.27143971940815</v>
       </c>
       <c r="R328" t="n">
-        <v>1.001015454006839</v>
+        <v>1.00099634622768</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>11.27475710438791</v>
       </c>
       <c r="R329" t="n">
-        <v>1.001310070640942</v>
+        <v>1.001290957238024</v>
       </c>
       <c r="S329" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>11.24713533893455</v>
       </c>
       <c r="R330" t="n">
-        <v>0.9988569843650017</v>
+        <v>0.998837917787565</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>11.24193005913637</v>
       </c>
       <c r="R331" t="n">
-        <v>0.9983947039775698</v>
+        <v>0.9983756462243241</v>
       </c>
       <c r="S331" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>11.26733178481843</v>
       </c>
       <c r="R332" t="n">
-        <v>1.00065062873955</v>
+        <v>1.00063152792432</v>
       </c>
       <c r="S332" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>11.28303419894864</v>
       </c>
       <c r="R333" t="n">
-        <v>1.002045158595615</v>
+        <v>1.002026031161047</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>11.28770475786082</v>
       </c>
       <c r="R334" t="n">
-        <v>1.002459950473701</v>
+        <v>1.002440815121421</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>11.32447315344595</v>
       </c>
       <c r="R335" t="n">
-        <v>1.005725348072943</v>
+        <v>1.005706150389461</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>11.3036971461652</v>
       </c>
       <c r="R336" t="n">
-        <v>1.003880232907683</v>
+        <v>1.003861070444491</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>11.31768886690903</v>
       </c>
       <c r="R337" t="n">
-        <v>1.005122836252188</v>
+        <v>1.005103650069691</v>
       </c>
       <c r="S337" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>11.3110785224451</v>
       </c>
       <c r="R338" t="n">
-        <v>1.004535772209845</v>
+        <v>1.004516597233458</v>
       </c>
       <c r="S338" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>11.32272091889915</v>
       </c>
       <c r="R339" t="n">
-        <v>1.005569732295007</v>
+        <v>1.005550537581981</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>11.32067477709839</v>
       </c>
       <c r="R340" t="n">
-        <v>1.005388014642725</v>
+        <v>1.005368823398398</v>
       </c>
       <c r="S340" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>11.28974441295288</v>
       </c>
       <c r="R341" t="n">
-        <v>1.002641092042021</v>
+        <v>1.002621953232039</v>
       </c>
       <c r="S341" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>11.28000931700719</v>
       </c>
       <c r="R342" t="n">
-        <v>1.001776519127605</v>
+        <v>1.001757396820933</v>
       </c>
       <c r="S342" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>11.2598766764128</v>
       </c>
       <c r="R343" t="n">
-        <v>0.9999885412945468</v>
+        <v>0.9999694531175036</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>11.27381766036807</v>
       </c>
       <c r="R344" t="n">
-        <v>1.001226638709845</v>
+        <v>1.001207526899509</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>11.27971895146018</v>
       </c>
       <c r="R345" t="n">
-        <v>1.001750731791905</v>
+        <v>1.001731609977472</v>
       </c>
       <c r="S345" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>11.2603788492867</v>
       </c>
       <c r="R346" t="n">
-        <v>1.000033139218137</v>
+        <v>1.000014050189791</v>
       </c>
       <c r="S346" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>11.26845612694127</v>
       </c>
       <c r="R347" t="n">
-        <v>1.000750481453007</v>
+        <v>1.000731378731749</v>
       </c>
       <c r="S347" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>11.26913267808817</v>
       </c>
       <c r="R348" t="n">
-        <v>1.000810565893889</v>
+        <v>1.000791462025715</v>
       </c>
       <c r="S348" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>11.26093223492695</v>
       </c>
       <c r="R349" t="n">
-        <v>1.000082285342475</v>
+        <v>1.000063195376009</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>11.27882207341968</v>
       </c>
       <c r="R350" t="n">
-        <v>1.00167108014125</v>
+        <v>1.00165195984724</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>11.24182515211013</v>
       </c>
       <c r="R351" t="n">
-        <v>0.9983853871948767</v>
+        <v>0.9983663296194734</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>11.26920923995019</v>
       </c>
       <c r="R352" t="n">
-        <v>1.000817365345333</v>
+        <v>1.000798261347368</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>11.35085349439496</v>
       </c>
       <c r="R353" t="n">
-        <v>1.008068183560628</v>
+        <v>1.008048941156175</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>11.2845934769669</v>
       </c>
       <c r="R354" t="n">
-        <v>1.00218363792321</v>
+        <v>1.002164507845294</v>
       </c>
       <c r="S354" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>11.26325825071566</v>
       </c>
       <c r="R355" t="n">
-        <v>1.000288858576128</v>
+        <v>1.00026976466651</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>11.29638506478959</v>
       </c>
       <c r="R356" t="n">
-        <v>1.003230847679163</v>
+        <v>1.003211697611692</v>
       </c>
       <c r="S356" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>11.36917056132509</v>
       </c>
       <c r="R357" t="n">
-        <v>1.009694920474951</v>
+        <v>1.009675647018701</v>
       </c>
       <c r="S357" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>11.29330071540514</v>
       </c>
       <c r="R358" t="n">
-        <v>1.002956926913382</v>
+        <v>1.002937782074619</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>11.30361085159246</v>
       </c>
       <c r="R359" t="n">
-        <v>1.003872569095157</v>
+        <v>1.003853406778254</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>11.28069071364424</v>
       </c>
       <c r="R360" t="n">
-        <v>1.001837033895991</v>
+        <v>1.001817910434189</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>11.30760955273057</v>
       </c>
       <c r="R361" t="n">
-        <v>1.004227693350341</v>
+        <v>1.004208524254686</v>
       </c>
       <c r="S361" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>11.38639805849847</v>
       </c>
       <c r="R362" t="n">
-        <v>1.011224892806234</v>
+        <v>1.011205590145266</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>11.31386458417198</v>
       </c>
       <c r="R363" t="n">
-        <v>1.004783202078065</v>
+        <v>1.004764022378639</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>11.33698748969521</v>
       </c>
       <c r="R364" t="n">
-        <v>1.006836745045645</v>
+        <v>1.006817526147379</v>
       </c>
       <c r="S364" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>11.33505399184989</v>
       </c>
       <c r="R365" t="n">
-        <v>1.006665031291978</v>
+        <v>1.006645815671451</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>11.41144629602037</v>
       </c>
       <c r="R366" t="n">
-        <v>1.013449424319443</v>
+        <v>1.013430079195737</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>11.3349106209611</v>
       </c>
       <c r="R367" t="n">
-        <v>1.006652298537431</v>
+        <v>1.006633083159952</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>11.33727361614121</v>
       </c>
       <c r="R368" t="n">
-        <v>1.006862155907201</v>
+        <v>1.006842936523882</v>
       </c>
       <c r="S368" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>11.34318049038071</v>
       </c>
       <c r="R369" t="n">
-        <v>1.007386744828032</v>
+        <v>1.007367515431152</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>11.35342550321175</v>
       </c>
       <c r="R370" t="n">
-        <v>1.008296603410935</v>
+        <v>1.008277356646314</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>11.33432497640669</v>
       </c>
       <c r="R371" t="n">
-        <v>1.006600287502097</v>
+        <v>1.006581073117425</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>11.32293860465852</v>
       </c>
       <c r="R372" t="n">
-        <v>1.005589064945908</v>
+        <v>1.005569869863853</v>
       </c>
       <c r="S372" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>11.35775593295597</v>
       </c>
       <c r="R373" t="n">
-        <v>1.008681188451033</v>
+        <v>1.008661934345301</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>11.32012923988225</v>
       </c>
       <c r="R374" t="n">
-        <v>1.005339565536162</v>
+        <v>1.00532037521665</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>11.27794968814938</v>
       </c>
       <c r="R375" t="n">
-        <v>1.001593603691112</v>
+        <v>1.001574484876002</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>11.30361085159246</v>
       </c>
       <c r="R376" t="n">
-        <v>1.003872569095157</v>
+        <v>1.003853406778254</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>11.30169813266635</v>
       </c>
       <c r="R377" t="n">
-        <v>1.003702700715263</v>
+        <v>1.003683541640875</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>11.31027058008334</v>
       </c>
       <c r="R378" t="n">
-        <v>1.004464018928081</v>
+        <v>1.004444845321349</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>11.28769223179094</v>
       </c>
       <c r="R379" t="n">
-        <v>1.002458838034666</v>
+        <v>1.002439702703621</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>11.38207618654524</v>
       </c>
       <c r="R380" t="n">
-        <v>1.010841067782712</v>
+        <v>1.010821772448348</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>11.3087631252513</v>
       </c>
       <c r="R381" t="n">
-        <v>1.004330142012563</v>
+        <v>1.004310970961327</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>11.34982989866116</v>
       </c>
       <c r="R382" t="n">
-        <v>1.007977278124082</v>
+        <v>1.007958037454869</v>
       </c>
       <c r="S382" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>11.34785032998474</v>
       </c>
       <c r="R383" t="n">
-        <v>1.007801472824432</v>
+        <v>1.007782235511059</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>11.37124668663829</v>
       </c>
       <c r="R384" t="n">
-        <v>1.009879300960028</v>
+        <v>1.009860023984249</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>11.36978231274225</v>
       </c>
       <c r="R385" t="n">
-        <v>1.009749250058202</v>
+        <v>1.009729975564887</v>
       </c>
       <c r="S385" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>11.36587452225819</v>
       </c>
       <c r="R386" t="n">
-        <v>1.009402199569272</v>
+        <v>1.009382931700594</v>
       </c>
       <c r="S386" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>11.36671980637608</v>
       </c>
       <c r="R387" t="n">
-        <v>1.009477269168728</v>
+        <v>1.009457999867092</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>11.34258781347895</v>
       </c>
       <c r="R388" t="n">
-        <v>1.00733410925062</v>
+        <v>1.007314880858468</v>
       </c>
       <c r="S388" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>11.34672919409777</v>
       </c>
       <c r="R389" t="n">
-        <v>1.007701904856467</v>
+        <v>1.007682669443687</v>
       </c>
       <c r="S389" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>11.35150005500903</v>
       </c>
       <c r="R390" t="n">
-        <v>1.008125604545235</v>
+        <v>1.008106361044708</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>11.35528871585814</v>
       </c>
       <c r="R391" t="n">
-        <v>1.00846207514299</v>
+        <v>1.008442825219779</v>
       </c>
       <c r="S391" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>11.37027836452638</v>
       </c>
       <c r="R392" t="n">
-        <v>1.009793304368412</v>
+        <v>1.00977402903417</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>11.42693175180325</v>
       </c>
       <c r="R393" t="n">
-        <v>1.014824686125999</v>
+        <v>1.014805314750752</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
@@ -27882,16 +27882,16 @@
         <v>0</v>
       </c>
       <c r="O394" t="n">
-        <v>78740</v>
+        <v>78832</v>
       </c>
       <c r="P394" t="n">
         <v>12</v>
       </c>
       <c r="Q394" t="n">
-        <v>11.27422401474007</v>
+        <v>11.27539136460808</v>
       </c>
       <c r="R394" t="n">
-        <v>1.001262727001696</v>
+        <v>1.001347284750635</v>
       </c>
       <c r="S394" t="inlineStr">
         <is>
@@ -27950,16 +27950,16 @@
         <v>0</v>
       </c>
       <c r="O395" t="n">
-        <v>69471</v>
+        <v>69534</v>
       </c>
       <c r="P395" t="n">
         <v>54</v>
       </c>
       <c r="Q395" t="n">
-        <v>11.15023244870593</v>
+        <v>11.15113747164467</v>
       </c>
       <c r="R395" t="n">
-        <v>0.9902510482049791</v>
+        <v>0.9903125193650947</v>
       </c>
       <c r="S395" t="inlineStr">
         <is>
@@ -28018,16 +28018,16 @@
         <v>0</v>
       </c>
       <c r="O396" t="n">
-        <v>66773</v>
+        <v>66836</v>
       </c>
       <c r="P396" t="n">
         <v>41</v>
       </c>
       <c r="Q396" t="n">
-        <v>11.11029633168127</v>
+        <v>11.11123821177333</v>
       </c>
       <c r="R396" t="n">
-        <v>0.9867043255759368</v>
+        <v>0.9867691376549806</v>
       </c>
       <c r="S396" t="inlineStr">
         <is>
@@ -28086,16 +28086,16 @@
         <v>0</v>
       </c>
       <c r="O397" t="n">
-        <v>63617</v>
+        <v>63711</v>
       </c>
       <c r="P397" t="n">
         <v>24</v>
       </c>
       <c r="Q397" t="n">
-        <v>11.06140594710165</v>
+        <v>11.0628813134641</v>
       </c>
       <c r="R397" t="n">
-        <v>0.9823623753251384</v>
+        <v>0.9824746482439165</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
@@ -28154,16 +28154,16 @@
         <v>0</v>
       </c>
       <c r="O398" t="n">
-        <v>62619</v>
+        <v>62682</v>
       </c>
       <c r="P398" t="n">
         <v>17</v>
       </c>
       <c r="Q398" t="n">
-        <v>11.04538280505385</v>
+        <v>11.04638782224767</v>
       </c>
       <c r="R398" t="n">
-        <v>0.9809393616542256</v>
+        <v>0.9810098908699533</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
@@ -28222,16 +28222,16 @@
         <v>0</v>
       </c>
       <c r="O399" t="n">
-        <v>62975</v>
+        <v>63067</v>
       </c>
       <c r="P399" t="n">
         <v>19</v>
       </c>
       <c r="Q399" t="n">
-        <v>11.05111220290819</v>
+        <v>11.05257113117204</v>
       </c>
       <c r="R399" t="n">
-        <v>0.9814481889147282</v>
+        <v>0.9815590194458029</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -28290,16 +28290,16 @@
         <v>0</v>
       </c>
       <c r="O400" t="n">
-        <v>63268</v>
+        <v>63330</v>
       </c>
       <c r="P400" t="n">
         <v>86</v>
       </c>
       <c r="Q400" t="n">
-        <v>11.05786561911009</v>
+        <v>11.0588424278593</v>
       </c>
       <c r="R400" t="n">
-        <v>0.9820479591440632</v>
+        <v>0.9821159620570696</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -28358,16 +28358,16 @@
         <v>0</v>
       </c>
       <c r="O401" t="n">
-        <v>61742</v>
+        <v>61804</v>
       </c>
       <c r="P401" t="n">
         <v>4</v>
       </c>
       <c r="Q401" t="n">
-        <v>11.03086544869108</v>
+        <v>11.03186897731112</v>
       </c>
       <c r="R401" t="n">
-        <v>0.9796500766620487</v>
+        <v>0.9797204982905913</v>
       </c>
       <c r="S401" t="inlineStr">
         <is>
@@ -28426,16 +28426,16 @@
         <v>0</v>
       </c>
       <c r="O402" t="n">
-        <v>60492</v>
+        <v>60554</v>
       </c>
       <c r="P402" t="n">
         <v>6</v>
       </c>
       <c r="Q402" t="n">
-        <v>11.01048128523215</v>
+        <v>11.01150546927833</v>
       </c>
       <c r="R402" t="n">
-        <v>0.9778397611081046</v>
+        <v>0.9779120516640173</v>
       </c>
       <c r="S402" t="inlineStr">
         <is>
@@ -28494,16 +28494,16 @@
         <v>0</v>
       </c>
       <c r="O403" t="n">
-        <v>60694</v>
+        <v>60756</v>
       </c>
       <c r="P403" t="n">
         <v>42</v>
       </c>
       <c r="Q403" t="n">
-        <v>11.01499961355491</v>
+        <v>11.01601918279305</v>
       </c>
       <c r="R403" t="n">
-        <v>0.9782410334025012</v>
+        <v>0.9783129064659436</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
@@ -28562,16 +28562,16 @@
         <v>0</v>
       </c>
       <c r="O404" t="n">
-        <v>59500</v>
+        <v>59592</v>
       </c>
       <c r="P404" t="n">
         <v>7</v>
       </c>
       <c r="Q404" t="n">
-        <v>10.99398366060198</v>
+        <v>10.9955282958212</v>
       </c>
       <c r="R404" t="n">
-        <v>0.9763746086856708</v>
+        <v>0.9764931475442447</v>
       </c>
       <c r="S404" t="inlineStr">
         <is>
@@ -28630,16 +28630,16 @@
         <v>0</v>
       </c>
       <c r="O405" t="n">
-        <v>59710</v>
+        <v>59774</v>
       </c>
       <c r="P405" t="n">
         <v>16</v>
       </c>
       <c r="Q405" t="n">
-        <v>10.99780730811888</v>
+        <v>10.99887798994429</v>
       </c>
       <c r="R405" t="n">
-        <v>0.9767141864459548</v>
+        <v>0.976790627871662</v>
       </c>
       <c r="S405" t="inlineStr">
         <is>
@@ -28698,16 +28698,16 @@
         <v>0</v>
       </c>
       <c r="O406" t="n">
-        <v>60115</v>
+        <v>60209</v>
       </c>
       <c r="P406" t="n">
         <v>14</v>
       </c>
       <c r="Q406" t="n">
-        <v>11.00449696580396</v>
+        <v>11.00605866139142</v>
       </c>
       <c r="R406" t="n">
-        <v>0.9773082942876752</v>
+        <v>0.9774283304243944</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -28766,16 +28766,16 @@
         <v>0</v>
       </c>
       <c r="O407" t="n">
-        <v>58309</v>
+        <v>58403</v>
       </c>
       <c r="P407" t="n">
         <v>22</v>
       </c>
       <c r="Q407" t="n">
-        <v>10.97428318720746</v>
+        <v>10.97589274903506</v>
       </c>
       <c r="R407" t="n">
-        <v>0.9746250115791709</v>
+        <v>0.9747493498503919</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
@@ -28833,16 +28833,16 @@
         <v>0</v>
       </c>
       <c r="O408" t="n">
-        <v>58677</v>
+        <v>58741</v>
       </c>
       <c r="P408" t="n">
         <v>22</v>
       </c>
       <c r="Q408" t="n">
-        <v>10.98056972265387</v>
+        <v>10.98165901029945</v>
       </c>
       <c r="R408" t="n">
-        <v>0.9751833181744841</v>
+        <v>0.9752614411715307</v>
       </c>
       <c r="S408" t="inlineStr">
         <is>
@@ -28901,16 +28901,16 @@
         <v>0</v>
       </c>
       <c r="O409" t="n">
-        <v>58051</v>
+        <v>58113</v>
       </c>
       <c r="P409" t="n">
         <v>17</v>
       </c>
       <c r="Q409" t="n">
-        <v>10.96967994994813</v>
+        <v>10.97074676354621</v>
       </c>
       <c r="R409" t="n">
-        <v>0.9742161985304598</v>
+        <v>0.9742923441084184</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
@@ -28969,16 +28969,16 @@
         <v>0</v>
       </c>
       <c r="O410" t="n">
-        <v>58851</v>
+        <v>58945</v>
       </c>
       <c r="P410" t="n">
         <v>2</v>
       </c>
       <c r="Q410" t="n">
-        <v>10.9828490616121</v>
+        <v>10.98444490596552</v>
       </c>
       <c r="R410" t="n">
-        <v>0.9753857460434081</v>
+        <v>0.9755088515691483</v>
       </c>
       <c r="S410" t="inlineStr">
         <is>
@@ -29037,16 +29037,16 @@
         <v>0</v>
       </c>
       <c r="O411" t="n">
-        <v>61471</v>
+        <v>61565</v>
       </c>
       <c r="P411" t="n">
         <v>13</v>
       </c>
       <c r="Q411" t="n">
-        <v>11.02675993294061</v>
+        <v>11.02828727095789</v>
       </c>
       <c r="R411" t="n">
-        <v>0.9792854662116361</v>
+        <v>0.9794024133731275</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -29105,16 +29105,16 @@
         <v>0</v>
       </c>
       <c r="O412" t="n">
-        <v>60639</v>
+        <v>60733</v>
       </c>
       <c r="P412" t="n">
         <v>14</v>
       </c>
       <c r="Q412" t="n">
-        <v>11.01317165517129</v>
+        <v>11.01471987256034</v>
       </c>
       <c r="R412" t="n">
-        <v>0.9780786925980571</v>
+        <v>0.9781975170544812</v>
       </c>
       <c r="S412" t="inlineStr">
         <is>
@@ -29173,16 +29173,16 @@
         <v>0</v>
       </c>
       <c r="O413" t="n">
-        <v>59004</v>
+        <v>59098</v>
       </c>
       <c r="P413" t="n">
         <v>29</v>
       </c>
       <c r="Q413" t="n">
-        <v>10.98635994980873</v>
+        <v>10.9879502055998</v>
       </c>
       <c r="R413" t="n">
-        <v>0.975697547679189</v>
+        <v>0.9758201509429368</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
@@ -29241,16 +29241,16 @@
         <v>0</v>
       </c>
       <c r="O414" t="n">
-        <v>58288</v>
+        <v>58411</v>
       </c>
       <c r="P414" t="n">
         <v>42</v>
       </c>
       <c r="Q414" t="n">
-        <v>10.9746087331423</v>
+        <v>10.97671365481382</v>
       </c>
       <c r="R414" t="n">
-        <v>0.9746539232816573</v>
+        <v>0.9748222530203142</v>
       </c>
       <c r="S414" t="inlineStr">
         <is>
@@ -29309,16 +29309,16 @@
         <v>0</v>
       </c>
       <c r="O415" t="n">
-        <v>61745</v>
+        <v>61900</v>
       </c>
       <c r="P415" t="n">
         <v>8</v>
       </c>
       <c r="Q415" t="n">
-        <v>11.03104356759401</v>
+        <v>11.03355005747749</v>
       </c>
       <c r="R415" t="n">
-        <v>0.9796658953843171</v>
+        <v>0.9798697920051602</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>9.913388377213391</v>
       </c>
       <c r="R416" t="n">
-        <v>1.012883305107832</v>
+        <v>1.012877509336328</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>9.946882234855318</v>
       </c>
       <c r="R417" t="n">
-        <v>1.016305482060684</v>
+        <v>1.016299666707304</v>
       </c>
       <c r="S417" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>9.844957610345725</v>
       </c>
       <c r="R418" t="n">
-        <v>1.005891509903349</v>
+        <v>1.005885754139265</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>9.784760321267326</v>
       </c>
       <c r="R419" t="n">
-        <v>0.9997409560462627</v>
+        <v>0.999735235475971</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>9.724301076237646</v>
       </c>
       <c r="R420" t="n">
-        <v>0.9935636372930958</v>
+        <v>0.9935579520697467</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>9.749986661550366</v>
       </c>
       <c r="R421" t="n">
-        <v>0.9961880175307326</v>
+        <v>0.9961823172905419</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>9.748061059204817</v>
       </c>
       <c r="R422" t="n">
-        <v>0.9959912724427901</v>
+        <v>0.9959855733283851</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>9.763535592108683</v>
       </c>
       <c r="R423" t="n">
-        <v>0.9975723560679102</v>
+        <v>0.9975666479064615</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>9.761059559403851</v>
       </c>
       <c r="R424" t="n">
-        <v>0.997319371710373</v>
+        <v>0.9973136649965142</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>9.810549556876859</v>
       </c>
       <c r="R425" t="n">
-        <v>1.002375926573639</v>
+        <v>1.002370190925907</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>9.786110684382555</v>
       </c>
       <c r="R426" t="n">
-        <v>0.9998789270611371</v>
+        <v>0.9998732057013681</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>9.893033094632269</v>
       </c>
       <c r="R427" t="n">
-        <v>1.010803539329205</v>
+        <v>1.01079775545823</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>9.836171845251261</v>
       </c>
       <c r="R428" t="n">
-        <v>1.00499383955612</v>
+        <v>1.004988088928553</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>9.971566673346722</v>
       </c>
       <c r="R429" t="n">
-        <v>1.018827571854056</v>
+        <v>1.018821742069146</v>
       </c>
       <c r="S429" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>9.805709329617423</v>
       </c>
       <c r="R430" t="n">
-        <v>1.001881384728059</v>
+        <v>1.001875651910122</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>9.816076095525158</v>
       </c>
       <c r="R431" t="n">
-        <v>1.002940591097906</v>
+        <v>1.002934852219134</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>9.785266921148697</v>
       </c>
       <c r="R432" t="n">
-        <v>0.999792717012613</v>
+        <v>0.9997869961461423</v>
       </c>
       <c r="S432" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>9.8001804826702</v>
       </c>
       <c r="R433" t="n">
-        <v>1.001316484357343</v>
+        <v>1.001310754771796</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>9.818256408173468</v>
       </c>
       <c r="R434" t="n">
-        <v>1.003163360770328</v>
+        <v>1.003157620616857</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>9.857967037234319</v>
       </c>
       <c r="R435" t="n">
-        <v>1.007220725586532</v>
+        <v>1.007214962216606</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>9.764512800245539</v>
       </c>
       <c r="R436" t="n">
-        <v>0.9976722006185093</v>
+        <v>0.9976664918857449</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>9.791438048727505</v>
       </c>
       <c r="R437" t="n">
-        <v>1.000423241295575</v>
+        <v>1.000417516821211</v>
       </c>
       <c r="S437" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>9.816730688609846</v>
       </c>
       <c r="R438" t="n">
-        <v>1.003007473013744</v>
+        <v>1.003001733752271</v>
       </c>
       <c r="S438" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>9.835529859352901</v>
       </c>
       <c r="R439" t="n">
-        <v>1.004928245757732</v>
+        <v>1.004922495505496</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>9.889337916931686</v>
       </c>
       <c r="R440" t="n">
-        <v>1.010425990941115</v>
+        <v>1.010420209230492</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>10.31148279049792</v>
       </c>
       <c r="R441" t="n">
-        <v>1.05355791299462</v>
+        <v>1.053551884480872</v>
       </c>
       <c r="S441" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>9.671555495188839</v>
       </c>
       <c r="R442" t="n">
-        <v>0.9881744488108459</v>
+        <v>0.9881687944247165</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>9.745019231764333</v>
       </c>
       <c r="R443" t="n">
-        <v>0.9956804789870866</v>
+        <v>0.995674781651058</v>
       </c>
       <c r="S443" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>9.681655640646714</v>
       </c>
       <c r="R444" t="n">
-        <v>0.9892064136975396</v>
+        <v>0.989200753406453</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>9.72782378340624</v>
       </c>
       <c r="R445" t="n">
-        <v>0.9939235638029917</v>
+        <v>0.9939178765201242</v>
       </c>
       <c r="S445" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>9.645493723786172</v>
       </c>
       <c r="R446" t="n">
-        <v>0.9855116324103532</v>
+        <v>0.9855059932609992</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>9.672689782285058</v>
       </c>
       <c r="R447" t="n">
-        <v>0.9882903426323368</v>
+        <v>0.988284687583057</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>9.673130546703616</v>
       </c>
       <c r="R448" t="n">
-        <v>0.9883353769741841</v>
+        <v>0.9883297216672152</v>
       </c>
       <c r="S448" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>9.626877294051397</v>
       </c>
       <c r="R449" t="n">
-        <v>0.9836095309127049</v>
+        <v>0.9836039026472756</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>9.590897844378162</v>
       </c>
       <c r="R450" t="n">
-        <v>0.9799333928946732</v>
+        <v>0.9799277856642989</v>
       </c>
       <c r="S450" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>9.674325928896355</v>
       </c>
       <c r="R451" t="n">
-        <v>0.988457513081454</v>
+        <v>0.988451857075616</v>
       </c>
       <c r="S451" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>9.650142492488797</v>
       </c>
       <c r="R452" t="n">
-        <v>0.9859866123091554</v>
+        <v>0.9859809704419416</v>
       </c>
       <c r="S452" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>9.689922976002242</v>
       </c>
       <c r="R453" t="n">
-        <v>0.9900511143831892</v>
+        <v>0.9900454492586808</v>
       </c>
       <c r="S453" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>9.699411063939143</v>
       </c>
       <c r="R454" t="n">
-        <v>0.9910205433516711</v>
+        <v>0.9910148726800392</v>
       </c>
       <c r="S454" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>9.727167947937808</v>
       </c>
       <c r="R455" t="n">
-        <v>0.9938565549487437</v>
+        <v>0.9938508680493043</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>9.757883578677337</v>
       </c>
       <c r="R456" t="n">
-        <v>0.9969948713747839</v>
+        <v>0.9969891665177332</v>
       </c>
       <c r="S456" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>9.825850282808975</v>
       </c>
       <c r="R457" t="n">
-        <v>1.003939251772144</v>
+        <v>1.003933507178984</v>
       </c>
       <c r="S457" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>9.971846890049472</v>
       </c>
       <c r="R458" t="n">
-        <v>1.018856202510823</v>
+        <v>1.018850372562087</v>
       </c>
       <c r="S458" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>9.896412583864164</v>
       </c>
       <c r="R459" t="n">
-        <v>1.011148832794217</v>
+        <v>1.011143046947455</v>
       </c>
       <c r="S459" t="inlineStr">
         <is>
@@ -32407,16 +32407,16 @@
         <v>0</v>
       </c>
       <c r="O460" t="n">
-        <v>18695</v>
+        <v>18709</v>
       </c>
       <c r="P460" t="n">
         <v>36</v>
       </c>
       <c r="Q460" t="n">
-        <v>9.839908570893257</v>
+        <v>9.840654243364559</v>
       </c>
       <c r="R460" t="n">
-        <v>1.005375633033237</v>
+        <v>1.005446067579656</v>
       </c>
       <c r="S460" t="inlineStr">
         <is>
@@ -32475,16 +32475,16 @@
         <v>0</v>
       </c>
       <c r="O461" t="n">
-        <v>19318</v>
+        <v>19344</v>
       </c>
       <c r="P461" t="n">
         <v>128</v>
       </c>
       <c r="Q461" t="n">
-        <v>9.882008520859005</v>
+        <v>9.883335864325275</v>
       </c>
       <c r="R461" t="n">
-        <v>1.00967712257885</v>
+        <v>1.009806963399343</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -32543,16 +32543,16 @@
         <v>0</v>
       </c>
       <c r="O462" t="n">
-        <v>18957</v>
+        <v>18971</v>
       </c>
       <c r="P462" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q462" t="n">
-        <v>9.855137291595081</v>
+        <v>9.855976569865076</v>
       </c>
       <c r="R462" t="n">
-        <v>1.006931601221923</v>
+        <v>1.007011590820806</v>
       </c>
       <c r="S462" t="inlineStr">
         <is>
@@ -32611,16 +32611,16 @@
         <v>0</v>
       </c>
       <c r="O463" t="n">
-        <v>19917</v>
+        <v>19933</v>
       </c>
       <c r="P463" t="n">
         <v>57</v>
       </c>
       <c r="Q463" t="n">
-        <v>9.905086273899824</v>
+        <v>9.90588467713585</v>
       </c>
       <c r="R463" t="n">
-        <v>1.012035052066226</v>
+        <v>1.01211083615092</v>
       </c>
       <c r="S463" t="inlineStr">
         <is>
@@ -32680,16 +32680,16 @@
         <v>0</v>
       </c>
       <c r="O464" t="n">
-        <v>20584</v>
+        <v>20601</v>
       </c>
       <c r="P464" t="n">
         <v>73</v>
       </c>
       <c r="Q464" t="n">
-        <v>9.939385443533112</v>
+        <v>9.940205135471292</v>
       </c>
       <c r="R464" t="n">
-        <v>1.015539510378429</v>
+        <v>1.015617449534291</v>
       </c>
       <c r="S464" t="inlineStr">
         <is>
@@ -32748,16 +32748,16 @@
         <v>0</v>
       </c>
       <c r="O465" t="n">
-        <v>20188</v>
+        <v>20211</v>
       </c>
       <c r="P465" t="n">
         <v>113</v>
       </c>
       <c r="Q465" t="n">
-        <v>9.924025203753676</v>
+        <v>9.925151192172155</v>
       </c>
       <c r="R465" t="n">
-        <v>1.013970104455545</v>
+        <v>1.014079347725471</v>
       </c>
       <c r="S465" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>12.58990885973201</v>
       </c>
       <c r="R466" t="n">
-        <v>1.008888900448524</v>
+        <v>1.008872499671542</v>
       </c>
       <c r="S466" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>12.54399739816763</v>
       </c>
       <c r="R467" t="n">
-        <v>1.005209798042642</v>
+        <v>1.005193457074167</v>
       </c>
       <c r="S467" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>12.50250011527337</v>
       </c>
       <c r="R468" t="n">
-        <v>1.00188442463627</v>
+        <v>1.001868137725985</v>
       </c>
       <c r="S468" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>12.51758598411019</v>
       </c>
       <c r="R469" t="n">
-        <v>1.003093326606306</v>
+        <v>1.003077020043776</v>
       </c>
       <c r="S469" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>12.47941108820814</v>
       </c>
       <c r="R470" t="n">
-        <v>1.000034191772173</v>
+        <v>1.000017934939785</v>
       </c>
       <c r="S470" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>12.44578221943286</v>
       </c>
       <c r="R471" t="n">
-        <v>0.9973393515775365</v>
+        <v>0.9973231385532159</v>
       </c>
       <c r="S471" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>12.44006513373118</v>
       </c>
       <c r="R472" t="n">
-        <v>0.9968812144796748</v>
+        <v>0.9968650089029576</v>
       </c>
       <c r="S472" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>12.41912141555875</v>
       </c>
       <c r="R473" t="n">
-        <v>0.995202895356503</v>
+        <v>0.9951867170630055</v>
       </c>
       <c r="S473" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>12.38959764456361</v>
       </c>
       <c r="R474" t="n">
-        <v>0.9928370160488573</v>
+        <v>0.9928208762157482</v>
       </c>
       <c r="S474" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>12.49759234486317</v>
       </c>
       <c r="R475" t="n">
-        <v>1.001491141797772</v>
+        <v>1.001474861280801</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>12.44162291424894</v>
       </c>
       <c r="R476" t="n">
-        <v>0.9970060467950809</v>
+        <v>0.9969898391890549</v>
       </c>
       <c r="S476" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>12.42077265022148</v>
       </c>
       <c r="R477" t="n">
-        <v>0.9953352165942353</v>
+        <v>0.9953190361496872</v>
       </c>
       <c r="S477" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>12.46532437878642</v>
       </c>
       <c r="R478" t="n">
-        <v>0.998905357168384</v>
+        <v>0.9988891186866433</v>
       </c>
       <c r="S478" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>12.46796756910523</v>
       </c>
       <c r="R479" t="n">
-        <v>0.9991171685011054</v>
+        <v>0.9991009265761012</v>
       </c>
       <c r="S479" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>12.46925196236761</v>
       </c>
       <c r="R480" t="n">
-        <v>0.9992200930036307</v>
+        <v>0.9992038494054574</v>
       </c>
       <c r="S480" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>12.47028903989951</v>
       </c>
       <c r="R481" t="n">
-        <v>0.9993031989277881</v>
+        <v>0.9992869539786218</v>
       </c>
       <c r="S481" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>12.51593319717612</v>
       </c>
       <c r="R482" t="n">
-        <v>1.002960880977734</v>
+        <v>1.002944576568277</v>
       </c>
       <c r="S482" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>12.52760164316564</v>
       </c>
       <c r="R483" t="n">
-        <v>1.003895928703294</v>
+        <v>1.003879609093443</v>
       </c>
       <c r="S483" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>12.41064888623027</v>
       </c>
       <c r="R484" t="n">
-        <v>0.9945239515378093</v>
+        <v>0.9945077842814103</v>
       </c>
       <c r="S484" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>12.39546084137807</v>
       </c>
       <c r="R485" t="n">
-        <v>0.9933068617207487</v>
+        <v>0.9932907142496984</v>
       </c>
       <c r="S485" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>12.39477794944918</v>
       </c>
       <c r="R486" t="n">
-        <v>0.9932521383629438</v>
+        <v>0.9932359917814915</v>
       </c>
       <c r="S486" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>12.36868882029947</v>
       </c>
       <c r="R487" t="n">
-        <v>0.991161493139475</v>
+        <v>0.9911453805441297</v>
       </c>
       <c r="S487" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>12.37875203231786</v>
       </c>
       <c r="R488" t="n">
-        <v>0.9919679058801332</v>
+        <v>0.9919517801755193</v>
       </c>
       <c r="S488" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>12.371608270224</v>
       </c>
       <c r="R489" t="n">
-        <v>0.9913954424600843</v>
+        <v>0.9913793260615941</v>
       </c>
       <c r="S489" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>12.36703010657035</v>
       </c>
       <c r="R490" t="n">
-        <v>0.9910285725688042</v>
+        <v>0.9910124621342523</v>
       </c>
       <c r="S490" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>12.43603291017131</v>
       </c>
       <c r="R491" t="n">
-        <v>0.9965580933483781</v>
+        <v>0.9965418930244073</v>
       </c>
       <c r="S491" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>12.50704722979823</v>
       </c>
       <c r="R492" t="n">
-        <v>1.002248806414114</v>
+        <v>1.002232513580338</v>
       </c>
       <c r="S492" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>12.51531315588132</v>
       </c>
       <c r="R493" t="n">
-        <v>1.002911194138289</v>
+        <v>1.002894890536554</v>
       </c>
       <c r="S493" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>12.57460402334502</v>
       </c>
       <c r="R494" t="n">
-        <v>1.00766245157379</v>
+        <v>1.007646070734301</v>
       </c>
       <c r="S494" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>12.51311239336053</v>
       </c>
       <c r="R495" t="n">
-        <v>1.002734836636063</v>
+        <v>1.002718535901245</v>
       </c>
       <c r="S495" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>12.55139489075743</v>
       </c>
       <c r="R496" t="n">
-        <v>1.005802594086533</v>
+        <v>1.005786243481402</v>
       </c>
       <c r="S496" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>12.53521450906673</v>
       </c>
       <c r="R497" t="n">
-        <v>1.004505983628536</v>
+        <v>1.004489654101463</v>
       </c>
       <c r="S497" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>12.56827876427911</v>
       </c>
       <c r="R498" t="n">
-        <v>1.007155578669852</v>
+        <v>1.007139206070228</v>
       </c>
       <c r="S498" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>12.45042959324358</v>
       </c>
       <c r="R499" t="n">
-        <v>0.9977117676058104</v>
+        <v>0.9976955485273918</v>
       </c>
       <c r="S499" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>12.44722505944343</v>
       </c>
       <c r="R500" t="n">
-        <v>0.9974549731668587</v>
+        <v>0.9974387582629616</v>
       </c>
       <c r="S500" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>12.47112943574086</v>
       </c>
       <c r="R501" t="n">
-        <v>0.9993705438185064</v>
+        <v>0.999354297774563</v>
       </c>
       <c r="S501" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>12.47126368014642</v>
       </c>
       <c r="R502" t="n">
-        <v>0.9993813014572021</v>
+        <v>0.9993650552383795</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>12.44917175362272</v>
       </c>
       <c r="R503" t="n">
-        <v>0.9976109709720806</v>
+        <v>0.99759475353224</v>
       </c>
       <c r="S503" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>12.45671851704347</v>
       </c>
       <c r="R504" t="n">
-        <v>0.9982157287931519</v>
+        <v>0.9981995015222008</v>
       </c>
       <c r="S504" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>12.45755872574471</v>
       </c>
       <c r="R505" t="n">
-        <v>0.9982830586874498</v>
+        <v>0.9982668303219654</v>
       </c>
       <c r="S505" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>12.41345260166491</v>
       </c>
       <c r="R506" t="n">
-        <v>0.9947486265067496</v>
+        <v>0.9947324555979721</v>
       </c>
       <c r="S506" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>12.40145437905871</v>
       </c>
       <c r="R507" t="n">
-        <v>0.993787152222276</v>
+        <v>0.9937709969434905</v>
       </c>
       <c r="S507" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>12.40555035694247</v>
       </c>
       <c r="R508" t="n">
-        <v>0.9941153822888673</v>
+        <v>0.994099221674283</v>
       </c>
       <c r="S508" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>12.44871681775691</v>
       </c>
       <c r="R509" t="n">
-        <v>0.9975745148109958</v>
+        <v>0.9975582979637966</v>
       </c>
       <c r="S509" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>12.42773109462579</v>
       </c>
       <c r="R510" t="n">
-        <v>0.9958928296319557</v>
+        <v>0.9958766401226958</v>
       </c>
       <c r="S510" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>12.44731148511348</v>
       </c>
       <c r="R511" t="n">
-        <v>0.9974618988642723</v>
+        <v>0.9974456838477891</v>
       </c>
       <c r="S511" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>12.46586822914455</v>
       </c>
       <c r="R512" t="n">
-        <v>0.9989489384679738</v>
+        <v>0.9989326992777636</v>
       </c>
       <c r="S512" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>12.44491630264845</v>
       </c>
       <c r="R513" t="n">
-        <v>0.9972699615730313</v>
+        <v>0.9972537496767337</v>
       </c>
       <c r="S513" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>12.47008171041767</v>
       </c>
       <c r="R514" t="n">
-        <v>0.9992865846365094</v>
+        <v>0.9992703399574298</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>12.49127414390042</v>
       </c>
       <c r="R515" t="n">
-        <v>1.000984834492998</v>
+        <v>1.000968562206699</v>
       </c>
       <c r="S515" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>12.52574381708545</v>
       </c>
       <c r="R516" t="n">
-        <v>1.00374705231887</v>
+        <v>1.003730735129194</v>
       </c>
       <c r="S516" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>12.52196673993552</v>
       </c>
       <c r="R517" t="n">
-        <v>1.003444377275297</v>
+        <v>1.00342806500599</v>
       </c>
       <c r="S517" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>12.54321251637691</v>
       </c>
       <c r="R518" t="n">
-        <v>1.005146901755175</v>
+        <v>1.005130561809159</v>
       </c>
       <c r="S518" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>12.52595444737922</v>
       </c>
       <c r="R519" t="n">
-        <v>1.003763931119809</v>
+        <v>1.003747613655747</v>
       </c>
       <c r="S519" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>12.49579762981584</v>
       </c>
       <c r="R520" t="n">
-        <v>1.001347322798691</v>
+        <v>1.001331044619682</v>
       </c>
       <c r="S520" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>12.48804721110804</v>
       </c>
       <c r="R521" t="n">
-        <v>1.000726245116935</v>
+        <v>1.000709977034336</v>
       </c>
       <c r="S521" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>12.45266706317713</v>
       </c>
       <c r="R522" t="n">
-        <v>0.9978910666465102</v>
+        <v>0.9978748446533567</v>
       </c>
       <c r="S522" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>12.45303818665026</v>
       </c>
       <c r="R523" t="n">
-        <v>0.997920806524448</v>
+        <v>0.997904584047835</v>
       </c>
       <c r="S523" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>12.48653748630827</v>
       </c>
       <c r="R524" t="n">
-        <v>1.000605263733337</v>
+        <v>1.000588997617445</v>
       </c>
       <c r="S524" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>12.46211698125285</v>
       </c>
       <c r="R525" t="n">
-        <v>0.9986483332449388</v>
+        <v>0.9986320989414502</v>
       </c>
       <c r="S525" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>12.46508514525863</v>
       </c>
       <c r="R526" t="n">
-        <v>0.9988861862551159</v>
+        <v>0.9988699480850231</v>
       </c>
       <c r="S526" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>12.47525209531347</v>
       </c>
       <c r="R527" t="n">
-        <v>0.9997009120149308</v>
+        <v>0.9996846606004306</v>
       </c>
       <c r="S527" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>12.48577420825664</v>
       </c>
       <c r="R528" t="n">
-        <v>1.000544098655589</v>
+        <v>1.000527833534014</v>
       </c>
       <c r="S528" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>12.45985014906034</v>
       </c>
       <c r="R529" t="n">
-        <v>0.9984666812676548</v>
+        <v>0.9984504499171509</v>
       </c>
       <c r="S529" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>12.56292157433266</v>
       </c>
       <c r="R530" t="n">
-        <v>1.006726281719827</v>
+        <v>1.006709916098974</v>
       </c>
       <c r="S530" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>12.482226017158</v>
       </c>
       <c r="R531" t="n">
-        <v>1.000259765333087</v>
+        <v>1.000243504833712</v>
       </c>
       <c r="S531" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>12.53090598361275</v>
       </c>
       <c r="R532" t="n">
-        <v>1.004160721120581</v>
+        <v>1.004144397206191</v>
       </c>
       <c r="S532" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>12.73481087633466</v>
       </c>
       <c r="R533" t="n">
-        <v>1.020500583887361</v>
+        <v>1.020483994347642</v>
       </c>
       <c r="S533" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>12.45706868979894</v>
       </c>
       <c r="R534" t="n">
-        <v>0.9982437897910645</v>
+        <v>0.9982275620639461</v>
       </c>
       <c r="S534" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>12.45482156347972</v>
       </c>
       <c r="R535" t="n">
-        <v>0.9980637169385427</v>
+        <v>0.9980474921387383</v>
       </c>
       <c r="S535" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>12.44590024092077</v>
       </c>
       <c r="R536" t="n">
-        <v>0.9973488091971666</v>
+        <v>0.9973325960191003</v>
       </c>
       <c r="S536" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>12.60263490731498</v>
       </c>
       <c r="R537" t="n">
-        <v>1.009908698788296</v>
+        <v>1.009892281433191</v>
       </c>
       <c r="S537" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>12.59596377300015</v>
       </c>
       <c r="R538" t="n">
-        <v>1.009374109265956</v>
+        <v>1.009357700601286</v>
       </c>
       <c r="S538" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>12.62219410582684</v>
       </c>
       <c r="R539" t="n">
-        <v>1.01147606980743</v>
+        <v>1.011459626972709</v>
       </c>
       <c r="S539" t="inlineStr">
         <is>
@@ -37955,16 +37955,16 @@
         <v>0</v>
       </c>
       <c r="O540" t="n">
-        <v>303542</v>
+        <v>303900</v>
       </c>
       <c r="P540" t="n">
         <v>35</v>
       </c>
       <c r="Q540" t="n">
-        <v>12.62350914308622</v>
+        <v>12.62468758110115</v>
       </c>
       <c r="R540" t="n">
-        <v>1.011581449958268</v>
+        <v>1.011659437683087</v>
       </c>
       <c r="S540" t="inlineStr">
         <is>
@@ -38026,16 +38026,16 @@
         <v>0</v>
       </c>
       <c r="O541" t="n">
-        <v>270097</v>
+        <v>270517</v>
       </c>
       <c r="P541" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Q541" t="n">
-        <v>12.5098667197608</v>
+        <v>12.51143008426196</v>
       </c>
       <c r="R541" t="n">
-        <v>1.002474745470533</v>
+        <v>1.002583726713633</v>
       </c>
       <c r="S541" t="inlineStr">
         <is>
@@ -38094,16 +38094,16 @@
         <v>0</v>
       </c>
       <c r="O542" t="n">
-        <v>283973</v>
+        <v>284294</v>
       </c>
       <c r="P542" t="n">
         <v>512</v>
       </c>
       <c r="Q542" t="n">
-        <v>12.56023744168231</v>
+        <v>12.56136313154916</v>
       </c>
       <c r="R542" t="n">
-        <v>1.006511189484574</v>
+        <v>1.006585032743256</v>
       </c>
       <c r="S542" t="inlineStr">
         <is>
@@ -38162,16 +38162,16 @@
         <v>0</v>
       </c>
       <c r="O543" t="n">
-        <v>274074</v>
+        <v>274494</v>
       </c>
       <c r="P543" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q543" t="n">
-        <v>12.52192299077859</v>
+        <v>12.52346035410307</v>
       </c>
       <c r="R543" t="n">
-        <v>1.003440871448582</v>
+        <v>1.003547753422765</v>
       </c>
       <c r="S543" t="inlineStr">
         <is>
@@ -38230,16 +38230,16 @@
         <v>0</v>
       </c>
       <c r="O544" t="n">
-        <v>271396</v>
+        <v>271872</v>
       </c>
       <c r="P544" t="n">
         <v>20</v>
       </c>
       <c r="Q544" t="n">
-        <v>12.51148534723081</v>
+        <v>12.5132374411731</v>
       </c>
       <c r="R544" t="n">
-        <v>1.002604453739802</v>
+        <v>1.002728556410579</v>
       </c>
       <c r="S544" t="inlineStr">
         <is>
@@ -38299,16 +38299,16 @@
         <v>0</v>
       </c>
       <c r="O545" t="n">
-        <v>270888</v>
+        <v>271388</v>
       </c>
       <c r="P545" t="n">
         <v>38</v>
       </c>
       <c r="Q545" t="n">
-        <v>12.50974494022958</v>
+        <v>12.51158849660225</v>
       </c>
       <c r="R545" t="n">
-        <v>1.002464986701131</v>
+        <v>1.002596420836799</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
@@ -38368,16 +38368,16 @@
         <v>0</v>
       </c>
       <c r="O546" t="n">
-        <v>272669</v>
+        <v>273213</v>
       </c>
       <c r="P546" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q546" t="n">
-        <v>12.5168094045377</v>
+        <v>12.51881555545215</v>
       </c>
       <c r="R546" t="n">
-        <v>1.003031095614824</v>
+        <v>1.00317554980496</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
@@ -38436,16 +38436,16 @@
         <v>0</v>
       </c>
       <c r="O547" t="n">
-        <v>273044</v>
+        <v>274073</v>
       </c>
       <c r="P547" t="n">
         <v>292</v>
       </c>
       <c r="Q547" t="n">
-        <v>12.5195284532656</v>
+        <v>12.52328196632762</v>
       </c>
       <c r="R547" t="n">
-        <v>1.003248985840394</v>
+        <v>1.003533458599591</v>
       </c>
       <c r="S547" t="inlineStr">
         <is>
@@ -38504,16 +38504,16 @@
         <v>0</v>
       </c>
       <c r="O548" t="n">
-        <v>280551</v>
+        <v>280994</v>
       </c>
       <c r="P548" t="n">
         <v>204</v>
       </c>
       <c r="Q548" t="n">
-        <v>12.54596758942889</v>
+        <v>12.54754308458641</v>
       </c>
       <c r="R548" t="n">
-        <v>1.005367678780095</v>
+        <v>1.005477585065896</v>
       </c>
       <c r="S548" t="inlineStr">
         <is>
@@ -38571,16 +38571,16 @@
         <v>0</v>
       </c>
       <c r="O549" t="n">
-        <v>267647</v>
+        <v>268084</v>
       </c>
       <c r="P549" t="n">
         <v>44</v>
       </c>
       <c r="Q549" t="n">
-        <v>12.49775669936125</v>
+        <v>12.4993875736211</v>
       </c>
       <c r="R549" t="n">
-        <v>1.001504312300489</v>
+        <v>1.001618719107309</v>
       </c>
       <c r="S549" t="inlineStr">
         <is>
@@ -38639,16 +38639,16 @@
         <v>0</v>
       </c>
       <c r="O550" t="n">
-        <v>275654</v>
+        <v>276242</v>
       </c>
       <c r="P550" t="n">
         <v>138</v>
       </c>
       <c r="Q550" t="n">
-        <v>12.52790611344408</v>
+        <v>12.53003481367772</v>
       </c>
       <c r="R550" t="n">
-        <v>1.00392032734572</v>
+        <v>1.004074587376764</v>
       </c>
       <c r="S550" t="inlineStr">
         <is>
@@ -38708,16 +38708,16 @@
         <v>0</v>
       </c>
       <c r="O551" t="n">
-        <v>278830</v>
+        <v>279227</v>
       </c>
       <c r="P551" t="n">
         <v>139</v>
       </c>
       <c r="Q551" t="n">
-        <v>12.53935766551113</v>
+        <v>12.54077903825207</v>
       </c>
       <c r="R551" t="n">
-        <v>1.00483799433617</v>
+        <v>1.004935558875774</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -38776,16 +38776,16 @@
         <v>0</v>
       </c>
       <c r="O552" t="n">
-        <v>286934</v>
+        <v>287570</v>
       </c>
       <c r="P552" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q552" t="n">
-        <v>12.56810471441687</v>
+        <v>12.57032332101321</v>
       </c>
       <c r="R552" t="n">
-        <v>1.00714163123178</v>
+        <v>1.007303043401065</v>
       </c>
       <c r="S552" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>8.520786726926367</v>
       </c>
       <c r="R553" t="n">
-        <v>1.011642740025413</v>
+        <v>1.011639594776644</v>
       </c>
       <c r="S553" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>8.572817095164234</v>
       </c>
       <c r="R554" t="n">
-        <v>1.017820120820821</v>
+        <v>1.017816956366262</v>
       </c>
       <c r="S554" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>8.339261982923576</v>
       </c>
       <c r="R555" t="n">
-        <v>0.9900909519933188</v>
+        <v>0.9900878737501564</v>
       </c>
       <c r="S555" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>8.455530531024131</v>
       </c>
       <c r="R556" t="n">
-        <v>1.003895103693012</v>
+        <v>1.003891982532039</v>
       </c>
       <c r="S556" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>8.353497098745448</v>
       </c>
       <c r="R557" t="n">
-        <v>0.9917810367279959</v>
+        <v>0.9917779532302742</v>
       </c>
       <c r="S557" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>8.527341522468053</v>
       </c>
       <c r="R558" t="n">
-        <v>1.012420967615729</v>
+        <v>1.012417819947412</v>
       </c>
       <c r="S558" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>8.432070937999402</v>
       </c>
       <c r="R559" t="n">
-        <v>1.001109829547794</v>
+        <v>1.001106717046381</v>
       </c>
       <c r="S559" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>8.460199469896118</v>
       </c>
       <c r="R560" t="n">
-        <v>1.004449430219991</v>
+        <v>1.004446307335589</v>
       </c>
       <c r="S560" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>8.208764045819667</v>
       </c>
       <c r="R561" t="n">
-        <v>0.9745973954837681</v>
+        <v>0.9745943654108615</v>
       </c>
       <c r="S561" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>8.50086053679534</v>
       </c>
       <c r="R562" t="n">
-        <v>1.009276974254194</v>
+        <v>1.009273836360711</v>
       </c>
       <c r="S562" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>8.468002947225466</v>
       </c>
       <c r="R563" t="n">
-        <v>1.005375909363313</v>
+        <v>1.00537278359844</v>
       </c>
       <c r="S563" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>8.420021279663963</v>
       </c>
       <c r="R564" t="n">
-        <v>0.9996792164171652</v>
+        <v>0.9996761083636008</v>
       </c>
       <c r="S564" t="inlineStr">
         <is>
@@ -39676,16 +39676,16 @@
         <v>0</v>
       </c>
       <c r="O565" t="n">
-        <v>4848</v>
+        <v>4852</v>
       </c>
       <c r="P565" t="n">
         <v>10</v>
       </c>
       <c r="Q565" t="n">
-        <v>8.4906438561827</v>
+        <v>8.491465042843506</v>
       </c>
       <c r="R565" t="n">
-        <v>1.008063984057376</v>
+        <v>1.008158346207188</v>
       </c>
       <c r="S565" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>6.113682179832232</v>
       </c>
       <c r="R566" t="n">
-        <v>1.040956115732689</v>
+        <v>1.04091153360266</v>
       </c>
       <c r="S566" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>6.040254711277414</v>
       </c>
       <c r="R567" t="n">
-        <v>1.02845386746289</v>
+        <v>1.028409820779889</v>
       </c>
       <c r="S567" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>5.934894195619588</v>
       </c>
       <c r="R568" t="n">
-        <v>1.010514486594752</v>
+        <v>1.010471208220614</v>
       </c>
       <c r="S568" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>5.82600010738045</v>
       </c>
       <c r="R569" t="n">
-        <v>0.9919734562000744</v>
+        <v>0.9919309719022819</v>
       </c>
       <c r="S569" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>5.866468056933297</v>
       </c>
       <c r="R570" t="n">
-        <v>0.9988637979514269</v>
+        <v>0.9988210185536707</v>
       </c>
       <c r="S570" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>5.891644211825771</v>
       </c>
       <c r="R571" t="n">
-        <v>1.003150457224035</v>
+        <v>1.003107494236982</v>
       </c>
       <c r="S571" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>5.902633333401366</v>
       </c>
       <c r="R572" t="n">
-        <v>1.005021538018581</v>
+        <v>1.004978494896769</v>
       </c>
       <c r="S572" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>6.133398042996649</v>
       </c>
       <c r="R573" t="n">
-        <v>1.044313069485642</v>
+        <v>1.044268343583799</v>
       </c>
       <c r="S573" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>6.056784013228625</v>
       </c>
       <c r="R574" t="n">
-        <v>1.031268256148594</v>
+        <v>1.031224088930787</v>
       </c>
       <c r="S574" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>6.033086221798801</v>
       </c>
       <c r="R575" t="n">
-        <v>1.027233312853764</v>
+        <v>1.027189318444748</v>
       </c>
       <c r="S575" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>5.993961427306569</v>
       </c>
       <c r="R576" t="n">
-        <v>1.020571665600032</v>
+        <v>1.020527956496437</v>
       </c>
       <c r="S576" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>5.955837369464831</v>
       </c>
       <c r="R577" t="n">
-        <v>1.014080410412149</v>
+        <v>1.014036979316415</v>
       </c>
       <c r="S577" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>5.91350300563827</v>
       </c>
       <c r="R578" t="n">
-        <v>1.006872280575716</v>
+        <v>1.006829158190193</v>
       </c>
       <c r="S578" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>5.897153867636741</v>
       </c>
       <c r="R579" t="n">
-        <v>1.004088567800167</v>
+        <v>1.004045564635659</v>
       </c>
       <c r="S579" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>5.863631175598097</v>
       </c>
       <c r="R580" t="n">
-        <v>0.9983807717016775</v>
+        <v>0.998338012990998</v>
       </c>
       <c r="S580" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>5.852202479774474</v>
       </c>
       <c r="R581" t="n">
-        <v>0.9964348460773961</v>
+        <v>0.9963921707069342</v>
       </c>
       <c r="S581" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>5.953243334287785</v>
       </c>
       <c r="R582" t="n">
-        <v>1.013638732761505</v>
+        <v>1.013595320581967</v>
       </c>
       <c r="S582" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>6.033086221798801</v>
       </c>
       <c r="R583" t="n">
-        <v>1.027233312853764</v>
+        <v>1.027189318444748</v>
       </c>
       <c r="S583" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>6.003887067106539</v>
       </c>
       <c r="R584" t="n">
-        <v>1.022261670927168</v>
+        <v>1.022217889443926</v>
       </c>
       <c r="S584" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>6.059123195581797</v>
       </c>
       <c r="R585" t="n">
-        <v>1.031666540865516</v>
+        <v>1.031622356589948</v>
       </c>
       <c r="S585" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>6.063785208687608</v>
       </c>
       <c r="R586" t="n">
-        <v>1.032460326167299</v>
+        <v>1.032416107895447</v>
       </c>
       <c r="S586" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>6.091309882077698</v>
       </c>
       <c r="R587" t="n">
-        <v>1.037146859790763</v>
+        <v>1.037102440803772</v>
       </c>
       <c r="S587" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>6.052089168924417</v>
       </c>
       <c r="R588" t="n">
-        <v>1.030468880789011</v>
+        <v>1.0304247478069</v>
       </c>
       <c r="S588" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>5.996452088619021</v>
       </c>
       <c r="R589" t="n">
-        <v>1.020995742130206</v>
+        <v>1.020952014864237</v>
       </c>
       <c r="S589" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>5.993961427306569</v>
       </c>
       <c r="R590" t="n">
-        <v>1.020571665600032</v>
+        <v>1.020527956496437</v>
       </c>
       <c r="S590" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>5.932245187448011</v>
       </c>
       <c r="R591" t="n">
-        <v>1.010063448877102</v>
+        <v>1.010020189820034</v>
       </c>
       <c r="S591" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>5.996452088619021</v>
       </c>
       <c r="R592" t="n">
-        <v>1.020995742130206</v>
+        <v>1.020952014864237</v>
       </c>
       <c r="S592" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>6.059123195581797</v>
       </c>
       <c r="R593" t="n">
-        <v>1.031666540865516</v>
+        <v>1.031622356589948</v>
       </c>
       <c r="S593" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>5.953243334287785</v>
       </c>
       <c r="R594" t="n">
-        <v>1.013638732761505</v>
+        <v>1.013595320581967</v>
       </c>
       <c r="S594" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>5.8805329864007</v>
       </c>
       <c r="R595" t="n">
-        <v>1.001258586217448</v>
+        <v>1.001215704255558</v>
       </c>
       <c r="S595" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>5.932245187448011</v>
       </c>
       <c r="R596" t="n">
-        <v>1.010063448877102</v>
+        <v>1.010020189820034</v>
       </c>
       <c r="S596" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>5.840641657373398</v>
       </c>
       <c r="R597" t="n">
-        <v>0.9944664237048693</v>
+        <v>0.9944238326381171</v>
       </c>
       <c r="S597" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>5.805134968916488</v>
       </c>
       <c r="R598" t="n">
-        <v>0.9884208192047593</v>
+        <v>0.9883784870595139</v>
       </c>
       <c r="S598" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>5.783825182329737</v>
       </c>
       <c r="R599" t="n">
-        <v>0.9847924734681078</v>
+        <v>0.984750296717868</v>
       </c>
       <c r="S599" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>5.796057750765372</v>
       </c>
       <c r="R600" t="n">
-        <v>0.9868752717800969</v>
+        <v>0.9868330058276479</v>
       </c>
       <c r="S600" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>5.789960170897253</v>
       </c>
       <c r="R601" t="n">
-        <v>0.9858370573508574</v>
+        <v>0.9857948358631173</v>
       </c>
       <c r="S601" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>5.802118375377063</v>
       </c>
       <c r="R602" t="n">
-        <v>0.9879071939620369</v>
+        <v>0.9878648838143637</v>
       </c>
       <c r="S602" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>5.726847747587197</v>
       </c>
       <c r="R603" t="n">
-        <v>0.9750911171644284</v>
+        <v>0.9750493559044495</v>
       </c>
       <c r="S603" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>5.75890177387728</v>
       </c>
       <c r="R604" t="n">
-        <v>0.980548848482322</v>
+        <v>0.9805068534783039</v>
       </c>
       <c r="S604" t="inlineStr">
         <is>
@@ -42408,7 +42408,7 @@
         <v>5.726847747587197</v>
       </c>
       <c r="R605" t="n">
-        <v>0.9750911171644284</v>
+        <v>0.9750493559044495</v>
       </c>
       <c r="S605" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>5.703782474656201</v>
       </c>
       <c r="R606" t="n">
-        <v>0.9711638706684023</v>
+        <v>0.9711222776047683</v>
       </c>
       <c r="S606" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>5.720311776607412</v>
       </c>
       <c r="R607" t="n">
-        <v>0.9739782593541055</v>
+        <v>0.9739365457556667</v>
       </c>
       <c r="S607" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>5.703782474656201</v>
       </c>
       <c r="R608" t="n">
-        <v>0.9711638706684023</v>
+        <v>0.9711222776047683</v>
       </c>
       <c r="S608" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>5.793013608384144</v>
       </c>
       <c r="R609" t="n">
-        <v>0.9863569558886767</v>
+        <v>0.9863147121346912</v>
       </c>
       <c r="S609" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>5.814130531825066</v>
       </c>
       <c r="R610" t="n">
-        <v>0.9899524634657306</v>
+        <v>0.9899100657231343</v>
       </c>
       <c r="S610" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>5.857933154483459</v>
       </c>
       <c r="R611" t="n">
-        <v>0.9974105887984146</v>
+        <v>0.9973678716387858</v>
       </c>
       <c r="S611" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>5.899897353582491</v>
       </c>
       <c r="R612" t="n">
-        <v>1.004555691930871</v>
+        <v>1.004512668760343</v>
       </c>
       <c r="S612" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>5.945420608606575</v>
       </c>
       <c r="R613" t="n">
-        <v>1.012306783553151</v>
+        <v>1.012263428418413</v>
       </c>
       <c r="S613" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>6.021023349349527</v>
       </c>
       <c r="R614" t="n">
-        <v>1.025179408106998</v>
+        <v>1.025135501662735</v>
       </c>
       <c r="S614" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>5.908082938168931</v>
       </c>
       <c r="R615" t="n">
-        <v>1.005949423905394</v>
+        <v>1.005906341044031</v>
       </c>
       <c r="S615" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>5.87493073085203</v>
       </c>
       <c r="R616" t="n">
-        <v>1.000304708995219</v>
+        <v>1.00026186788604</v>
       </c>
       <c r="S616" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>5.799092654460526</v>
       </c>
       <c r="R617" t="n">
-        <v>0.9873920146314921</v>
+        <v>0.9873497265479496</v>
       </c>
       <c r="S617" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>5.768320995793772</v>
       </c>
       <c r="R618" t="n">
-        <v>0.9821526277385877</v>
+        <v>0.9821105640478167</v>
       </c>
       <c r="S618" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>5.783825182329737</v>
       </c>
       <c r="R619" t="n">
-        <v>0.9847924734681078</v>
+        <v>0.984750296717868</v>
       </c>
       <c r="S619" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>5.780743515792329</v>
       </c>
       <c r="R620" t="n">
-        <v>0.9842677684647392</v>
+        <v>0.9842256141865962</v>
       </c>
       <c r="S620" t="inlineStr">
         <is>
@@ -43496,7 +43496,7 @@
         <v>5.6937321388027</v>
       </c>
       <c r="R621" t="n">
-        <v>0.9694526337633532</v>
+        <v>0.9694111139886746</v>
       </c>
       <c r="S621" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>5.676753802268282</v>
       </c>
       <c r="R622" t="n">
-        <v>0.9665617894684417</v>
+        <v>0.9665203935030133</v>
       </c>
       <c r="S622" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>5.765191102784844</v>
       </c>
       <c r="R623" t="n">
-        <v>0.98161971137601</v>
+        <v>0.9815776705090125</v>
       </c>
       <c r="S623" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>5.883322388488279</v>
       </c>
       <c r="R624" t="n">
-        <v>1.00173352833529</v>
+        <v>1.001690626032551</v>
       </c>
       <c r="S624" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>5.891644211825771</v>
       </c>
       <c r="R625" t="n">
-        <v>1.003150457224035</v>
+        <v>1.003107494236982</v>
       </c>
       <c r="S625" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>5.87493073085203</v>
       </c>
       <c r="R626" t="n">
-        <v>1.000304708995219</v>
+        <v>1.00026186788604</v>
       </c>
       <c r="S626" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>5.926926025970411</v>
       </c>
       <c r="R627" t="n">
-        <v>1.009157773130831</v>
+        <v>1.009114552862098</v>
       </c>
       <c r="S627" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>5.998936561946683</v>
       </c>
       <c r="R628" t="n">
-        <v>1.02141876505301</v>
+        <v>1.02137501966979</v>
       </c>
       <c r="S628" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>5.908082938168931</v>
       </c>
       <c r="R629" t="n">
-        <v>1.005949423905394</v>
+        <v>1.005906341044031</v>
       </c>
       <c r="S629" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>6.003887067106539</v>
       </c>
       <c r="R630" t="n">
-        <v>1.022261670927168</v>
+        <v>1.022217889443926</v>
       </c>
       <c r="S630" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>5.899897353582491</v>
       </c>
       <c r="R631" t="n">
-        <v>1.004555691930871</v>
+        <v>1.004512668760343</v>
       </c>
       <c r="S631" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>5.942799375126701</v>
       </c>
       <c r="R632" t="n">
-        <v>1.011860474938902</v>
+        <v>1.011817138918696</v>
       </c>
       <c r="S632" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>5.924255797414532</v>
       </c>
       <c r="R633" t="n">
-        <v>1.008703122289671</v>
+        <v>1.008659921492751</v>
       </c>
       <c r="S633" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>5.945420608606575</v>
       </c>
       <c r="R634" t="n">
-        <v>1.012306783553151</v>
+        <v>1.012263428418413</v>
       </c>
       <c r="S634" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>5.855071922202427</v>
       </c>
       <c r="R635" t="n">
-        <v>0.9969234163949656</v>
+        <v>0.9968807200999853</v>
       </c>
       <c r="S635" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>5.808142489980444</v>
       </c>
       <c r="R636" t="n">
-        <v>0.9889328997075776</v>
+        <v>0.9888905456309182</v>
       </c>
       <c r="S636" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>5.755742213586912</v>
       </c>
       <c r="R637" t="n">
-        <v>0.9800108807714498</v>
+        <v>0.9799689088075445</v>
       </c>
       <c r="S637" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>5.746203190540153</v>
       </c>
       <c r="R638" t="n">
-        <v>0.9783867033794037</v>
+        <v>0.9783448009758636</v>
       </c>
       <c r="S638" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>5.720311776607412</v>
       </c>
       <c r="R639" t="n">
-        <v>0.9739782593541055</v>
+        <v>0.9739365457556667</v>
       </c>
       <c r="S639" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>5.713732805509369</v>
       </c>
       <c r="R640" t="n">
-        <v>0.9728580800581768</v>
+        <v>0.972816414434843</v>
       </c>
       <c r="S640" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>5.720311776607412</v>
       </c>
       <c r="R641" t="n">
-        <v>0.9739782593541055</v>
+        <v>0.9739365457556667</v>
       </c>
       <c r="S641" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>5.6937321388027</v>
       </c>
       <c r="R642" t="n">
-        <v>0.9694526337633532</v>
+        <v>0.9694111139886746</v>
       </c>
       <c r="S642" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>5.720311776607412</v>
       </c>
       <c r="R643" t="n">
-        <v>0.9739782593541055</v>
+        <v>0.9739365457556667</v>
       </c>
       <c r="S643" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>5.68697535633982</v>
       </c>
       <c r="R644" t="n">
-        <v>0.9683021791239852</v>
+        <v>0.9682607086210457</v>
       </c>
       <c r="S644" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>5.69035945432406</v>
       </c>
       <c r="R645" t="n">
-        <v>0.9688783781132871</v>
+        <v>0.9688368829328635</v>
       </c>
       <c r="S645" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>5.655991810819852</v>
       </c>
       <c r="R646" t="n">
-        <v>0.9630267149687683</v>
+        <v>0.9629854704037195</v>
       </c>
       <c r="S646" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>5.6937321388027</v>
       </c>
       <c r="R647" t="n">
-        <v>0.9694526337633532</v>
+        <v>0.9694111139886746</v>
       </c>
       <c r="S647" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>5.736572297479192</v>
       </c>
       <c r="R648" t="n">
-        <v>0.9767468835888287</v>
+        <v>0.9767050514155875</v>
       </c>
       <c r="S648" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>5.771441123130016</v>
       </c>
       <c r="R649" t="n">
-        <v>0.9826838813329014</v>
+        <v>0.9826417948895702</v>
       </c>
       <c r="S649" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>5.697093486505405</v>
       </c>
       <c r="R650" t="n">
-        <v>0.9700249591386855</v>
+        <v>0.9699834148524219</v>
       </c>
       <c r="S650" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>5.736572297479192</v>
       </c>
       <c r="R651" t="n">
-        <v>0.9767468835888287</v>
+        <v>0.9767050514155875</v>
       </c>
       <c r="S651" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>5.777652323222656</v>
       </c>
       <c r="R652" t="n">
-        <v>0.9837414414958753</v>
+        <v>0.9836993097592949</v>
       </c>
       <c r="S652" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>5.723585101952381</v>
       </c>
       <c r="R653" t="n">
-        <v>0.9745355974584428</v>
+        <v>0.9744938599902947</v>
       </c>
       <c r="S653" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>5.736572297479192</v>
       </c>
       <c r="R654" t="n">
-        <v>0.9767468835888287</v>
+        <v>0.9767050514155875</v>
       </c>
       <c r="S654" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>5.69035945432406</v>
       </c>
       <c r="R655" t="n">
-        <v>0.9688783781132871</v>
+        <v>0.9688368829328635</v>
       </c>
       <c r="S655" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>5.774551545544409</v>
       </c>
       <c r="R656" t="n">
-        <v>0.9832134825027913</v>
+        <v>0.9831713733776698</v>
       </c>
       <c r="S656" t="inlineStr">
         <is>
@@ -45941,10 +45941,10 @@
         <v>1</v>
       </c>
       <c r="Q657" t="n">
-        <v>5.730099782973574</v>
+        <v>5.730099782973575</v>
       </c>
       <c r="R657" t="n">
-        <v>0.9756448302990751</v>
+        <v>0.9756030453246376</v>
       </c>
       <c r="S657" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>5.68697535633982</v>
       </c>
       <c r="R658" t="n">
-        <v>0.9683021791239852</v>
+        <v>0.9682607086210457</v>
       </c>
       <c r="S658" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>5.6937321388027</v>
       </c>
       <c r="R659" t="n">
-        <v>0.9694526337633532</v>
+        <v>0.9694111139886746</v>
       </c>
       <c r="S659" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>5.69035945432406</v>
       </c>
       <c r="R660" t="n">
-        <v>0.9688783781132871</v>
+        <v>0.9688368829328635</v>
       </c>
       <c r="S660" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>5.713732805509369</v>
       </c>
       <c r="R661" t="n">
-        <v>0.9728580800581768</v>
+        <v>0.972816414434843</v>
       </c>
       <c r="S661" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>5.736572297479192</v>
       </c>
       <c r="R662" t="n">
-        <v>0.9767468835888287</v>
+        <v>0.9767050514155875</v>
       </c>
       <c r="S662" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>5.774551545544409</v>
       </c>
       <c r="R663" t="n">
-        <v>0.9832134825027913</v>
+        <v>0.9831713733776698</v>
       </c>
       <c r="S663" t="inlineStr">
         <is>
@@ -46417,10 +46417,10 @@
         <v>1</v>
       </c>
       <c r="Q664" t="n">
-        <v>5.811140992976701</v>
+        <v>5.8111409929767</v>
       </c>
       <c r="R664" t="n">
-        <v>0.9894434447343199</v>
+        <v>0.9894010687920077</v>
       </c>
       <c r="S664" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>5.883322388488279</v>
       </c>
       <c r="R665" t="n">
-        <v>1.00173352833529</v>
+        <v>1.001690626032551</v>
       </c>
       <c r="S665" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>5.968707559985366</v>
       </c>
       <c r="R666" t="n">
-        <v>1.016271774493388</v>
+        <v>1.016228249545784</v>
       </c>
       <c r="S666" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>6.066108090103747</v>
       </c>
       <c r="R667" t="n">
-        <v>1.032855835378462</v>
+        <v>1.032811600167719</v>
       </c>
       <c r="S667" t="inlineStr">
         <is>
@@ -46683,16 +46683,16 @@
         <v>0</v>
       </c>
       <c r="O668" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P668" t="n">
         <v>2</v>
       </c>
       <c r="Q668" t="n">
-        <v>6.00141487796115</v>
+        <v>6.006353159601733</v>
       </c>
       <c r="R668" t="n">
-        <v>1.021840739590792</v>
+        <v>1.022637764740952</v>
       </c>
       <c r="S668" t="inlineStr">
         <is>
@@ -46751,16 +46751,16 @@
         <v>0</v>
       </c>
       <c r="O669" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="P669" t="n">
         <v>2</v>
       </c>
       <c r="Q669" t="n">
-        <v>5.916202062607435</v>
+        <v>5.921578419643816</v>
       </c>
       <c r="R669" t="n">
-        <v>1.00733183993391</v>
+        <v>1.008204072902757</v>
       </c>
       <c r="S669" t="inlineStr">
         <is>
@@ -46819,16 +46819,16 @@
         <v>0</v>
       </c>
       <c r="O670" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P670" t="n">
         <v>0</v>
       </c>
       <c r="Q670" t="n">
-        <v>5.837730447165939</v>
+        <v>5.840641657373398</v>
       </c>
       <c r="R670" t="n">
-        <v>0.9939707417278711</v>
+        <v>0.9944238326381171</v>
       </c>
       <c r="S670" t="inlineStr">
         <is>
@@ -46887,16 +46887,16 @@
         <v>0</v>
       </c>
       <c r="O671" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P671" t="n">
         <v>2</v>
       </c>
       <c r="Q671" t="n">
-        <v>5.855071922202427</v>
+        <v>5.857933154483459</v>
       </c>
       <c r="R671" t="n">
-        <v>0.9969234163949656</v>
+        <v>0.9973678716387858</v>
       </c>
       <c r="S671" t="inlineStr">
         <is>
@@ -46955,16 +46955,16 @@
         <v>0</v>
       </c>
       <c r="O672" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P672" t="n">
         <v>1</v>
       </c>
       <c r="Q672" t="n">
-        <v>5.937536205082426</v>
+        <v>5.940171252720432</v>
       </c>
       <c r="R672" t="n">
-        <v>1.010964332665788</v>
+        <v>1.011369676514872</v>
       </c>
       <c r="S672" t="inlineStr">
         <is>
@@ -47023,16 +47023,16 @@
         <v>0</v>
       </c>
       <c r="O673" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P673" t="n">
         <v>5</v>
       </c>
       <c r="Q673" t="n">
-        <v>6.018593214496234</v>
+        <v>6.021023349349527</v>
       </c>
       <c r="R673" t="n">
-        <v>1.024765637213586</v>
+        <v>1.025135501662735</v>
       </c>
       <c r="S673" t="inlineStr">
         <is>
@@ -47091,16 +47091,16 @@
         <v>0</v>
       </c>
       <c r="O674" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P674" t="n">
         <v>5</v>
       </c>
       <c r="Q674" t="n">
-        <v>5.968707559985366</v>
+        <v>5.973809611869261</v>
       </c>
       <c r="R674" t="n">
-        <v>1.016271774493388</v>
+        <v>1.017096921566142</v>
       </c>
       <c r="S674" t="inlineStr">
         <is>
@@ -47159,16 +47159,16 @@
         <v>0</v>
       </c>
       <c r="O675" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P675" t="n">
         <v>2</v>
       </c>
       <c r="Q675" t="n">
-        <v>5.963579343618446</v>
+        <v>5.966146739123692</v>
       </c>
       <c r="R675" t="n">
-        <v>1.015398610329317</v>
+        <v>1.015792245858971</v>
       </c>
       <c r="S675" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>0.265</v>
       </c>
       <c r="E2" t="n">
-        <v>430.639</v>
+        <v>430.645</v>
       </c>
       <c r="F2" t="n">
         <v>20.5</v>
@@ -47263,7 +47263,7 @@
         <v>0.366</v>
       </c>
       <c r="E3" t="n">
-        <v>306.418</v>
+        <v>306.419</v>
       </c>
       <c r="F3" t="n">
         <v>15.6</v>
@@ -47285,7 +47285,7 @@
         <v>0.276</v>
       </c>
       <c r="E4" t="n">
-        <v>335.023</v>
+        <v>335.027</v>
       </c>
       <c r="F4" t="n">
         <v>14.1</v>
@@ -47307,7 +47307,7 @@
         <v>0.283</v>
       </c>
       <c r="E5" t="n">
-        <v>297.349</v>
+        <v>297.354</v>
       </c>
       <c r="F5" t="n">
         <v>13.3</v>
@@ -47351,7 +47351,7 @@
         <v>0.288</v>
       </c>
       <c r="E7" t="n">
-        <v>208.455</v>
+        <v>208.459</v>
       </c>
       <c r="F7" t="n">
         <v>9.1</v>
@@ -47373,7 +47373,7 @@
         <v>0.38</v>
       </c>
       <c r="E8" t="n">
-        <v>201.107</v>
+        <v>201.111</v>
       </c>
       <c r="F8" t="n">
         <v>7.6</v>
@@ -47417,7 +47417,7 @@
         <v>0.21</v>
       </c>
       <c r="E10" t="n">
-        <v>83.679</v>
+        <v>83.685</v>
       </c>
       <c r="F10" t="n">
         <v>3.8</v>
@@ -47439,7 +47439,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>33.559</v>
+        <v>33.56</v>
       </c>
       <c r="F11" t="n">
         <v>1.5</v>
